--- a/outputs/mai-report-policy/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\AppData\Local\Temp\claude\C--Users-----Documents-Project-maiReport\de191c12-f917-427b-8479-a7229e623801\scratchpad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7E0928-5B55-4EAA-AB37-15AABC75D108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBBD519-5594-4750-BA3B-4FE80DF50806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38370" yWindow="-4030" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3633" uniqueCount="1083">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3646" uniqueCount="1090">
   <si>
     <t>maiReport 식이 참조·설정 데이터 v1.0.0 | 2026-09-22</t>
   </si>
@@ -2628,33 +2628,15 @@
     <t>출시 전 테스트에서 재조정</t>
   </si>
   <si>
-    <t>양호 경계 (좋음)</t>
-  </si>
-  <si>
     <t>좋음 비율 &gt;= 0.6</t>
   </si>
   <si>
-    <t>양호 경계 (나쁨 상한)</t>
-  </si>
-  <si>
     <t>나쁨 비율 &lt; 0.2</t>
   </si>
   <si>
-    <t>관찰 창</t>
-  </si>
-  <si>
     <t>유효 답 수 집계</t>
   </si>
   <si>
-    <t>일; 운영 초기값. 의학적 판정 기준 아님. 종전 14일→28일</t>
-  </si>
-  <si>
-    <t>관찰 중 기준</t>
-  </si>
-  <si>
-    <t>유효 응답 최소 건수. 같은 실제 끼니·질문버전 중복 제외</t>
-  </si>
-  <si>
     <t>올리기 조건</t>
   </si>
   <si>
@@ -3286,6 +3268,53 @@
   </si>
   <si>
     <t>DIET-P-0233</t>
+  </si>
+  <si>
+    <t>양호 경계 · 3단계 축 (좋음)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>양호 경계 · 3단계 축 (나쁨 상한)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>양호 경계 · 2단계 축</t>
+  </si>
+  <si>
+    <t>좋음 비율 &gt;= 0.8</t>
+  </si>
+  <si>
+    <t>기억 안 남을 빼면 좋음+나쁨=1이라 3단계 축 값을 쓸 수 없음. 출시 전 테스트에서 재조정</t>
+  </si>
+  <si>
+    <t>상태 판정 최소 건수 · 개선 필요 · 보통</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>유효 응답 최소 건수. 같은 실제 끼니·질문버전 중복 제외. 이 수에 못 미치면 관찰 중</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>관찰 창 · 개선 필요 · 보통</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>일; 운영 초기값. 의학적 판정 기준 아님. 종전 14일→28일. 양호는 이 창을 쓰지 않음</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>양호 판정 기준 · 최근 유효 응답 수</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>기간이 아니라 건수로 판정. 7건이 모이기 전에는 비율이 넘어도 보통. 잘못 붙은 양호는 그 축의 코칭을 끊으므로 개선 필요보다 문턱을 높게 둠. 종전 3건 공통</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>양호 판정 기준 · 거슬러 보는 상한</t>
+  </si>
+  <si>
+    <t>일; 이 안에 7건이 모이지 않으면 양호를 내지 않음. 회전 문항이 세션마다 최대 1개라 회전 축은 28일에 4건 안팎에 그침</t>
   </si>
 </sst>
 </file>
@@ -3801,8 +3830,8 @@
         <v>12</v>
       </c>
       <c r="C8" s="1">
-        <f>COUNTA(설정값!B2:B100)</f>
-        <v>52</v>
+        <f>COUNTA(설정값!B2:B103)</f>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="25.4" customHeight="1">
@@ -14562,13 +14591,13 @@
         <v>108</v>
       </c>
       <c r="G165" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="H165">
         <v>17</v>
       </c>
       <c r="I165" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="J165" t="s">
         <v>142</v>
@@ -14583,13 +14612,13 @@
         <v>114</v>
       </c>
       <c r="O165" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="P165" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="Q165" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="R165" t="s">
         <v>118</v>
@@ -14621,13 +14650,13 @@
         <v>120</v>
       </c>
       <c r="G166" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="H166">
         <v>14</v>
       </c>
       <c r="I166" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="J166" t="s">
         <v>142</v>
@@ -14642,13 +14671,13 @@
         <v>114</v>
       </c>
       <c r="O166" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="P166" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="Q166" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="R166" t="s">
         <v>118</v>
@@ -14680,13 +14709,13 @@
         <v>108</v>
       </c>
       <c r="G167" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="H167">
         <v>14</v>
       </c>
       <c r="I167" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="J167" t="s">
         <v>142</v>
@@ -14701,13 +14730,13 @@
         <v>114</v>
       </c>
       <c r="O167" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="P167" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="Q167" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="R167" t="s">
         <v>118</v>
@@ -14739,13 +14768,13 @@
         <v>120</v>
       </c>
       <c r="G168" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="H168">
         <v>14</v>
       </c>
       <c r="I168" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="J168" t="s">
         <v>142</v>
@@ -14760,13 +14789,13 @@
         <v>114</v>
       </c>
       <c r="O168" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="P168" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="Q168" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="R168" t="s">
         <v>118</v>
@@ -14798,19 +14827,19 @@
         <v>108</v>
       </c>
       <c r="G169" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="H169">
         <v>14</v>
       </c>
       <c r="I169" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="J169" t="s">
         <v>142</v>
       </c>
       <c r="L169" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="M169" t="s">
         <v>137</v>
@@ -14819,13 +14848,13 @@
         <v>114</v>
       </c>
       <c r="O169" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="P169" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="Q169" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="R169" t="s">
         <v>118</v>
@@ -14857,19 +14886,19 @@
         <v>120</v>
       </c>
       <c r="G170" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="H170">
         <v>15</v>
       </c>
       <c r="I170" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="J170" t="s">
         <v>142</v>
       </c>
       <c r="L170" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="M170" t="s">
         <v>137</v>
@@ -14878,13 +14907,13 @@
         <v>114</v>
       </c>
       <c r="O170" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="P170" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="Q170" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="R170" t="s">
         <v>118</v>
@@ -14916,13 +14945,13 @@
         <v>108</v>
       </c>
       <c r="G171" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="H171">
         <v>18</v>
       </c>
       <c r="I171" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="J171" t="s">
         <v>142</v>
@@ -14937,13 +14966,13 @@
         <v>114</v>
       </c>
       <c r="O171" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="P171" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="Q171" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="R171" t="s">
         <v>118</v>
@@ -14966,7 +14995,7 @@
         <v>14</v>
       </c>
       <c r="D172" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="E172" t="s">
         <v>231</v>
@@ -14975,13 +15004,13 @@
         <v>221</v>
       </c>
       <c r="G172" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="H172">
         <v>20</v>
       </c>
       <c r="I172" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="J172" t="s">
         <v>142</v>
@@ -14996,13 +15025,13 @@
         <v>114</v>
       </c>
       <c r="O172" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="P172" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="Q172" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="R172" t="s">
         <v>118</v>
@@ -16373,7 +16402,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="12.58203125" customWidth="1"/>
@@ -16398,7 +16427,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="66" customHeight="1">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>858</v>
       </c>
@@ -16415,15 +16444,15 @@
         <v>862</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="66" customHeight="1">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>858</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>863</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>864</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>861</v>
@@ -16432,15 +16461,15 @@
         <v>862</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="66" customHeight="1">
+    <row r="4" spans="1:5" ht="32">
       <c r="A4" s="1" t="s">
         <v>858</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>865</v>
+        <v>1078</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>861</v>
@@ -16449,559 +16478,559 @@
         <v>862</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="66" customHeight="1">
+    <row r="5" spans="1:5" ht="32">
       <c r="A5" s="1" t="s">
         <v>858</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="C5" s="1">
-        <v>28</v>
+        <v>1079</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1080</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="66" customHeight="1">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="32">
       <c r="A6" s="1" t="s">
         <v>858</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>870</v>
+        <v>1084</v>
       </c>
       <c r="C6" s="1">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="32">
+      <c r="A7" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C7" s="1">
         <v>3</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>861</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="66" customHeight="1">
-      <c r="A7" s="1" t="s">
+      <c r="E7" s="1" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="48">
+      <c r="A8" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="32">
+      <c r="A9" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C9" s="1">
+        <v>84</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>872</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>873</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>874</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="66" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>876</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>877</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="66" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>880</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>881</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>882</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="66" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>880</v>
-      </c>
       <c r="B10" s="1" t="s">
-        <v>885</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>886</v>
+        <v>866</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>867</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>887</v>
-      </c>
-      <c r="E10" s="1"/>
+        <v>868</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>869</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="66" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>880</v>
+        <v>43</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>888</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>889</v>
+        <v>870</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>871</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>890</v>
+        <v>872</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>891</v>
+        <v>873</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="66" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>892</v>
+        <v>874</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>893</v>
+        <v>875</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>894</v>
+        <v>876</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>895</v>
+        <v>877</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>896</v>
+        <v>878</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="66" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>897</v>
+        <v>874</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>898</v>
+        <v>879</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>899</v>
+        <v>880</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>900</v>
+        <v>881</v>
       </c>
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:5" ht="66" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>897</v>
+        <v>874</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>901</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>902</v>
+        <v>882</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>883</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>903</v>
-      </c>
-      <c r="E14" s="1"/>
+        <v>884</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>885</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="66" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>904</v>
+        <v>886</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>905</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>906</v>
+        <v>887</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>888</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>907</v>
+        <v>889</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>908</v>
+        <v>890</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="66" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>909</v>
+        <v>891</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>910</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>911</v>
+        <v>892</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>893</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>912</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>913</v>
-      </c>
+        <v>894</v>
+      </c>
+      <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:5" ht="66" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>909</v>
+        <v>891</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>914</v>
+        <v>895</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>915</v>
+        <v>896</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>912</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>916</v>
-      </c>
+        <v>897</v>
+      </c>
+      <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:5" ht="66" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>909</v>
+        <v>898</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>917</v>
+        <v>899</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>918</v>
+        <v>900</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>919</v>
+        <v>901</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>920</v>
+        <v>902</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="66" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>921</v>
+        <v>903</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>922</v>
+        <v>904</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>924</v>
+        <v>906</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>925</v>
+        <v>907</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="66" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>921</v>
+        <v>903</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>926</v>
+        <v>908</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>927</v>
+        <v>909</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>924</v>
+        <v>906</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="66" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>921</v>
+        <v>903</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>929</v>
+        <v>911</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>930</v>
+        <v>912</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>931</v>
+        <v>913</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>932</v>
+        <v>914</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="66" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>933</v>
+        <v>916</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>934</v>
+        <v>917</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>935</v>
+        <v>918</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>936</v>
+        <v>919</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="66" customHeight="1">
       <c r="A23" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>921</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>937</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>938</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>935</v>
+        <v>918</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>939</v>
+        <v>922</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="66" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>940</v>
+        <v>923</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>941</v>
+        <v>924</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>935</v>
+        <v>925</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>942</v>
+        <v>926</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="66" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>943</v>
+        <v>927</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>944</v>
+        <v>928</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>945</v>
+        <v>930</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="66" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>946</v>
+        <v>915</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>947</v>
+        <v>931</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>948</v>
+        <v>932</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>949</v>
+        <v>929</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>950</v>
+        <v>933</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="66" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>946</v>
+        <v>915</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>951</v>
+        <v>934</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>952</v>
+        <v>935</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>953</v>
+        <v>929</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>954</v>
+        <v>936</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="66" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>946</v>
+        <v>915</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>955</v>
+        <v>937</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>956</v>
+        <v>938</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>957</v>
+        <v>929</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>958</v>
+        <v>939</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="66" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>959</v>
+        <v>940</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>960</v>
+        <v>941</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>961</v>
+        <v>942</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>962</v>
+        <v>943</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>963</v>
+        <v>944</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="66" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>959</v>
+        <v>940</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>964</v>
+        <v>945</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>966</v>
+        <v>947</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>967</v>
+        <v>948</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="66" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>968</v>
+        <v>940</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>971</v>
+        <v>951</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>972</v>
+        <v>952</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="66" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>968</v>
+        <v>953</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>974</v>
+        <v>955</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>975</v>
+        <v>956</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>976</v>
+        <v>957</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="66" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>968</v>
+        <v>953</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>977</v>
+        <v>958</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>978</v>
+        <v>959</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>980</v>
+        <v>961</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="66" customHeight="1">
       <c r="A34" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="66" customHeight="1">
+      <c r="A35" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>968</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>981</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>982</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>983</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="66" customHeight="1">
-      <c r="A35" s="4" t="s">
-        <v>666</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>985</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>986</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>987</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>988</v>
+      <c r="D35" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>970</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="66" customHeight="1">
-      <c r="A36" s="4" t="s">
-        <v>666</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>989</v>
-      </c>
-      <c r="C36" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>990</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>991</v>
+      <c r="A36" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>974</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="66" customHeight="1">
-      <c r="A37" s="4" t="s">
-        <v>666</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>992</v>
-      </c>
-      <c r="C37" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>990</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>993</v>
+      <c r="A37" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>978</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="66" customHeight="1">
@@ -17009,271 +17038,322 @@
         <v>666</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>994</v>
+        <v>979</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>995</v>
+        <v>980</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>990</v>
+        <v>981</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>996</v>
+        <v>982</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="66" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>997</v>
+        <v>666</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>998</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>999</v>
+        <v>983</v>
+      </c>
+      <c r="C39" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>1000</v>
+        <v>984</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>1001</v>
+        <v>985</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="66" customHeight="1">
       <c r="A40" s="4" t="s">
-        <v>997</v>
+        <v>666</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>1003</v>
+        <v>986</v>
+      </c>
+      <c r="C40" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>1004</v>
+        <v>984</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>1005</v>
+        <v>987</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="66" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>997</v>
+        <v>666</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1006</v>
+        <v>988</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>1007</v>
+        <v>989</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>1008</v>
+        <v>984</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>1009</v>
+        <v>990</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="66" customHeight="1">
       <c r="A42" s="4" t="s">
-        <v>43</v>
+        <v>991</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C42" s="9" t="b">
-        <v>0</v>
+        <v>992</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>993</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>1011</v>
+        <v>994</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>1012</v>
+        <v>995</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="66" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>1013</v>
+        <v>991</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>1014</v>
+        <v>996</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>1015</v>
+        <v>997</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>1016</v>
+        <v>999</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="66" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>1013</v>
+        <v>991</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>1017</v>
+        <v>1000</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>1018</v>
+        <v>1001</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>1019</v>
+        <v>1002</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>1020</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="66" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>1021</v>
+        <v>43</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>1022</v>
+        <v>1004</v>
       </c>
       <c r="C45" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>1024</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="66" customHeight="1">
       <c r="A46" s="4" t="s">
-        <v>1021</v>
+        <v>1007</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>1025</v>
+        <v>1008</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>118</v>
+        <v>1009</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>1026</v>
+        <v>998</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>1027</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="66" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>1028</v>
+        <v>1007</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1029</v>
+        <v>1011</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>1030</v>
+        <v>1012</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>909</v>
+        <v>1013</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>1031</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="66" customHeight="1">
       <c r="A48" s="4" t="s">
-        <v>1028</v>
+        <v>1015</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>1033</v>
+        <v>1016</v>
+      </c>
+      <c r="C48" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>858</v>
+        <v>1017</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>1034</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="66" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>1035</v>
+        <v>1019</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>1036</v>
+        <v>118</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>1037</v>
+        <v>1020</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>1038</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="66" customHeight="1">
       <c r="A50" s="4" t="s">
-        <v>1013</v>
+        <v>1022</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>1039</v>
+        <v>1023</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>1040</v>
+        <v>1024</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>1041</v>
+        <v>903</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>1042</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="66" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>892</v>
+        <v>1022</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>1043</v>
+        <v>1026</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>1044</v>
+        <v>1027</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>1045</v>
+        <v>858</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>1046</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="66" customHeight="1">
       <c r="A52" s="4" t="s">
-        <v>1047</v>
+        <v>1007</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>1048</v>
+        <v>1029</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>1049</v>
+        <v>1030</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>1004</v>
+        <v>1031</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>1050</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="66" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>1051</v>
+        <v>1007</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="66" customHeight="1">
+      <c r="A54" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="66" customHeight="1">
+      <c r="A55" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="66" customHeight="1">
+      <c r="A56" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C53" s="9" t="b">
+      <c r="C56" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>1053</v>
+      <c r="D56" s="4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>1047</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90BE1F3-EBFD-46FC-A23A-FD815B527C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7863BAE1-3BB9-4636-89F1-3C36F6D4348C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11590" yWindow="3690" windowWidth="28800" windowHeight="15460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38370" yWindow="-4030" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4023" uniqueCount="1279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3886" uniqueCount="1236">
   <si>
     <t>maiReport 식이 참조·설정 데이터 v1.0.0 | 2026-09-22</t>
   </si>
@@ -2293,49 +2293,10 @@
     <t>위 절제 · 비만수술 상태</t>
   </si>
   <si>
-    <t>2차</t>
-  </si>
-  <si>
-    <t>비만</t>
-  </si>
-  <si>
-    <t>주상병 청구가 드물어 검진 체질량지수가 더 안정적</t>
-  </si>
-  <si>
-    <t>통풍 · 고요산혈증</t>
-  </si>
-  <si>
-    <t>미국류마티스학회 통풍 지침(2020) 조건부 권고</t>
-  </si>
-  <si>
-    <t>위식도역류</t>
-  </si>
-  <si>
-    <t>미국소화기학회 지침(2022)</t>
-  </si>
-  <si>
-    <t>만성 간질환 · 간경변</t>
-  </si>
-  <si>
-    <t>보상 · 비보상 구분이 코드로 안 되어 자동 규칙 위험</t>
-  </si>
-  <si>
-    <t>철결핍 빈혈</t>
-  </si>
-  <si>
-    <t>D50</t>
-  </si>
-  <si>
-    <t>유병 인구 대비 효과가 작아 2차</t>
-  </si>
-  <si>
     <t>인지 · 연하 장애</t>
   </si>
   <si>
     <t>투석 · 이식</t>
-  </si>
-  <si>
-    <t>갑상선질환</t>
   </si>
   <si>
     <t>설정 이름</t>
@@ -3144,9 +3105,6 @@
     <t>DIET-Q-03;DIET-Q-01</t>
   </si>
   <si>
-    <t>진료기록만으로 활성 질환·치료 필요·식품 금기를 확정하지 않는다</t>
-  </si>
-  <si>
     <t>DX-03</t>
   </si>
   <si>
@@ -3177,9 +3135,6 @@
     <t>칼륨·인·단백질·수분은 병기·검사·투석·영양상태별로 개별화한다. 정보를 확인하기 전에는 증량·감량을 자동으로 내지 않는다</t>
   </si>
   <si>
-    <t>식품 자체가 전단계 금기라는 뜻이 아니다. 투석·이식 코드는 DX-18로 분리</t>
-  </si>
-  <si>
     <t>DX-06</t>
   </si>
   <si>
@@ -3237,60 +3192,12 @@
     <t>영구 상태로 본다</t>
   </si>
   <si>
-    <t>DX-13</t>
-  </si>
-  <si>
-    <t>DIET-Q-05;DIET-Q-02;DIET-Q-04</t>
-  </si>
-  <si>
-    <t>후보 조건 미정</t>
-  </si>
-  <si>
-    <t>DX-14</t>
-  </si>
-  <si>
-    <t>DIET-Q-02;DIET-Q-07</t>
-  </si>
-  <si>
-    <t>DX-15</t>
-  </si>
-  <si>
-    <t>DIET-Q-04;DIET-Q-05</t>
-  </si>
-  <si>
-    <t>남용 코드라 12개월 3회로 강화</t>
-  </si>
-  <si>
-    <t>DX-16</t>
-  </si>
-  <si>
-    <t>복수가 있을 때만 나트륨 제한. 코드로 구분되지 않아 후보 조건 미정</t>
-  </si>
-  <si>
-    <t>DX-17</t>
-  </si>
-  <si>
     <t>DX-18</t>
   </si>
   <si>
-    <t>검토</t>
-  </si>
-  <si>
-    <t>DX-05에서 코드를 분리했다</t>
-  </si>
-  <si>
-    <t>DX-19</t>
-  </si>
-  <si>
-    <t>후보 조건이 미정이라 지금은 아무 일도 하지 않는다. E03이 DX-20과 겹친다</t>
-  </si>
-  <si>
     <t>DX-20</t>
   </si>
   <si>
-    <t>원본에서 「가져오지 않음」이었으나 상세기획은 연하장애를 보호 대상으로 적고 있어 금지 쪽으로 옮겼다. 후보 조건 확정 필요</t>
-  </si>
-  <si>
     <t>매칭</t>
   </si>
   <si>
@@ -3339,9 +3246,6 @@
     <t>I12</t>
   </si>
   <si>
-    <t>DX-05와 겹치는 코드</t>
-  </si>
-  <si>
     <t>I13</t>
   </si>
   <si>
@@ -3405,9 +3309,6 @@
     <t>E14.2</t>
   </si>
   <si>
-    <t>DX-02와 겹치는 코드</t>
-  </si>
-  <si>
     <t>I21</t>
   </si>
   <si>
@@ -3579,48 +3480,6 @@
     <t>위 수술 후 증후군</t>
   </si>
   <si>
-    <t>E66.0</t>
-  </si>
-  <si>
-    <t>후보 조건 미정 — 2차</t>
-  </si>
-  <si>
-    <t>E66.1</t>
-  </si>
-  <si>
-    <t>E66.8</t>
-  </si>
-  <si>
-    <t>E66.9</t>
-  </si>
-  <si>
-    <t>M10</t>
-  </si>
-  <si>
-    <t>E79.0</t>
-  </si>
-  <si>
-    <t>K21.0</t>
-  </si>
-  <si>
-    <t>남용 코드라 3회로 강화</t>
-  </si>
-  <si>
-    <t>K21.9</t>
-  </si>
-  <si>
-    <t>K70.3</t>
-  </si>
-  <si>
-    <t>K74.6</t>
-  </si>
-  <si>
-    <t>K73</t>
-  </si>
-  <si>
-    <t>B18</t>
-  </si>
-  <si>
     <t>Z49</t>
   </si>
   <si>
@@ -3639,21 +3498,6 @@
     <t>신장 이식 상태</t>
   </si>
   <si>
-    <t>E05</t>
-  </si>
-  <si>
-    <t>후보 조건 미정 — 검토</t>
-  </si>
-  <si>
-    <t>E06</t>
-  </si>
-  <si>
-    <t>E03</t>
-  </si>
-  <si>
-    <t>후보 조건 미정 — 검토. DX-20과 무관하나 원본에서 「가져오지 않음」에도 들어 있었다</t>
-  </si>
-  <si>
     <t>F00</t>
   </si>
   <si>
@@ -3664,9 +3508,6 @@
   </si>
   <si>
     <t>R13</t>
-  </si>
-  <si>
-    <t>연하장애. 후보 조건 미정 — 검토</t>
   </si>
   <si>
     <t>타입</t>
@@ -3902,6 +3743,46 @@
   </si>
   <si>
     <t>모든 시트의 열마다 타입·허용값·필수 여부. 구현은 이 시트를 먼저 본다</t>
+  </si>
+  <si>
+    <t>고혈압성 신장질환. 고혈압(DX-02)에서 빼고 여기만 남겼다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>고혈압성 심장·신장질환. 고혈압(DX-02)에서 빼고 여기만 남겼다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>후보 조건을 출시 전에 확정해야 한다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>연하장애. 후보 조건을 출시 전에 확정해야 한다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>진료기록만으로 활성 질환·치료 필요·식품 금기를 확정하지 않는다. I12 · I13은 만성 신장질환(DX-05)에만 둔다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>식품 자체가 전단계 금기라는 뜻이 아니다. 투석·이식 코드는 DX-18로 분리. I12 · I13은 고혈압(DX-02)에서 빼고 여기만 남겼다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>상세기획이 연하장애를 보호 대상으로 적고 있어 1차에 둔다. 후보 조건이 아직 없어 지금은 걸리지 않는다 — 출시 전 확정 필요</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DX-05에서 코드를 분리했다. 상세기획이 투석을 보호 대상으로 적고 있고 후보 조건도 완성돼 있어 1차에 둔다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4051,7 +3932,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4364,7 +4245,7 @@
     </row>
     <row r="2" spans="1:3" ht="25.4" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>998</v>
+        <v>985</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -4390,7 +4271,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1272</v>
+        <v>1219</v>
       </c>
       <c r="C5" s="1">
         <v>171</v>
@@ -4401,7 +4282,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1273</v>
+        <v>1220</v>
       </c>
       <c r="C6" s="1">
         <v>8</v>
@@ -4409,24 +4290,24 @@
     </row>
     <row r="7" spans="1:3" ht="25.4" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>1274</v>
+        <v>1221</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1275</v>
+        <v>1222</v>
       </c>
       <c r="C7" s="1">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="25.4" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>1257</v>
+        <v>1204</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1276</v>
+        <v>1223</v>
       </c>
       <c r="C8" s="1">
-        <v>81</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="25.4" customHeight="1">
@@ -4443,10 +4324,10 @@
     </row>
     <row r="10" spans="1:3" ht="25.4" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>1277</v>
+        <v>1224</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1278</v>
+        <v>1225</v>
       </c>
       <c r="C10" s="11">
         <v>42</v>
@@ -4459,7 +4340,7 @@
     </row>
     <row r="12" spans="1:3" ht="25.4" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>999</v>
+        <v>986</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -4469,7 +4350,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1000</v>
+        <v>987</v>
       </c>
       <c r="C13" s="1">
         <v>171</v>
@@ -4528,7 +4409,7 @@
     </row>
     <row r="21" spans="1:3" ht="25.4" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>997</v>
+        <v>984</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -4857,7 +4738,7 @@
         <v>86</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>1001</v>
+        <v>988</v>
       </c>
       <c r="C53" s="4"/>
     </row>
@@ -4921,7 +4802,7 @@
         <v>50</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>1003</v>
+        <v>990</v>
       </c>
       <c r="M1" s="6" t="s">
         <v>53</v>
@@ -4979,7 +4860,7 @@
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>98</v>
@@ -5037,7 +4918,7 @@
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>98</v>
@@ -5093,7 +4974,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>98</v>
@@ -5203,7 +5084,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>118</v>
@@ -5259,7 +5140,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>118</v>
@@ -5425,7 +5306,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>1005</v>
+        <v>992</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>133</v>
@@ -5481,7 +5362,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>1005</v>
+        <v>992</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>138</v>
@@ -5539,7 +5420,7 @@
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>143</v>
@@ -5595,7 +5476,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>138</v>
@@ -5651,7 +5532,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>138</v>
@@ -5977,7 +5858,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>166</v>
@@ -6033,7 +5914,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>118</v>
@@ -6089,7 +5970,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>118</v>
@@ -6145,7 +6026,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>118</v>
@@ -6201,7 +6082,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>98</v>
@@ -6367,7 +6248,7 @@
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>98</v>
@@ -6423,7 +6304,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>98</v>
@@ -6481,7 +6362,7 @@
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>98</v>
@@ -6705,7 +6586,7 @@
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>221</v>
@@ -6819,7 +6700,7 @@
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>98</v>
@@ -6877,7 +6758,7 @@
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>98</v>
@@ -6991,7 +6872,7 @@
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>118</v>
@@ -7049,7 +6930,7 @@
       </c>
       <c r="K39" s="1"/>
       <c r="L39" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>118</v>
@@ -7107,7 +6988,7 @@
       </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>118</v>
@@ -7277,7 +7158,7 @@
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1" t="s">
-        <v>1005</v>
+        <v>992</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>138</v>
@@ -7391,7 +7272,7 @@
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>143</v>
@@ -7449,7 +7330,7 @@
       </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>138</v>
@@ -7563,7 +7444,7 @@
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>143</v>
@@ -7621,7 +7502,7 @@
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>143</v>
@@ -7735,7 +7616,7 @@
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>138</v>
@@ -7849,7 +7730,7 @@
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>118</v>
@@ -7907,7 +7788,7 @@
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>221</v>
@@ -8021,7 +7902,7 @@
       </c>
       <c r="K56" s="1"/>
       <c r="L56" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>118</v>
@@ -8247,7 +8128,7 @@
       </c>
       <c r="K60" s="1"/>
       <c r="L60" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M60" s="1" t="s">
         <v>143</v>
@@ -8361,7 +8242,7 @@
       </c>
       <c r="K62" s="1"/>
       <c r="L62" s="1" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="M62" s="1" t="s">
         <v>98</v>
@@ -8419,7 +8300,7 @@
       </c>
       <c r="K63" s="1"/>
       <c r="L63" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M63" s="1" t="s">
         <v>221</v>
@@ -8477,7 +8358,7 @@
       </c>
       <c r="K64" s="1"/>
       <c r="L64" s="1" t="s">
-        <v>1005</v>
+        <v>992</v>
       </c>
       <c r="M64" s="1" t="s">
         <v>138</v>
@@ -8535,7 +8416,7 @@
       </c>
       <c r="K65" s="1"/>
       <c r="L65" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M65" s="1" t="s">
         <v>98</v>
@@ -8593,7 +8474,7 @@
       </c>
       <c r="K66" s="1"/>
       <c r="L66" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M66" s="1" t="s">
         <v>98</v>
@@ -8651,7 +8532,7 @@
       </c>
       <c r="K67" s="1"/>
       <c r="L67" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M67" s="1" t="s">
         <v>98</v>
@@ -8765,7 +8646,7 @@
       </c>
       <c r="K69" s="1"/>
       <c r="L69" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M69" s="1" t="s">
         <v>98</v>
@@ -8823,7 +8704,7 @@
       </c>
       <c r="K70" s="1"/>
       <c r="L70" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M70" s="1" t="s">
         <v>118</v>
@@ -8937,7 +8818,7 @@
       </c>
       <c r="K72" s="1"/>
       <c r="L72" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M72" s="1" t="s">
         <v>118</v>
@@ -8995,7 +8876,7 @@
       </c>
       <c r="K73" s="1"/>
       <c r="L73" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M73" s="1" t="s">
         <v>194</v>
@@ -9109,7 +8990,7 @@
       </c>
       <c r="K75" s="1"/>
       <c r="L75" s="1" t="s">
-        <v>1005</v>
+        <v>992</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>133</v>
@@ -9167,7 +9048,7 @@
       </c>
       <c r="K76" s="1"/>
       <c r="L76" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>133</v>
@@ -9225,7 +9106,7 @@
       </c>
       <c r="K77" s="1"/>
       <c r="L77" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M77" s="1" t="s">
         <v>98</v>
@@ -9283,7 +9164,7 @@
       </c>
       <c r="K78" s="1"/>
       <c r="L78" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M78" s="1" t="s">
         <v>143</v>
@@ -9341,7 +9222,7 @@
       </c>
       <c r="K79" s="1"/>
       <c r="L79" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M79" s="1" t="s">
         <v>98</v>
@@ -9399,7 +9280,7 @@
       </c>
       <c r="K80" s="1"/>
       <c r="L80" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M80" s="1" t="s">
         <v>98</v>
@@ -9457,7 +9338,7 @@
       </c>
       <c r="K81" s="1"/>
       <c r="L81" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M81" s="1" t="s">
         <v>98</v>
@@ -9571,7 +9452,7 @@
       </c>
       <c r="K83" s="1"/>
       <c r="L83" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M83" s="1" t="s">
         <v>143</v>
@@ -9629,7 +9510,7 @@
       </c>
       <c r="K84" s="1"/>
       <c r="L84" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M84" s="1" t="s">
         <v>143</v>
@@ -9743,7 +9624,7 @@
       </c>
       <c r="K86" s="1"/>
       <c r="L86" s="1" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="M86" s="1" t="s">
         <v>391</v>
@@ -9801,7 +9682,7 @@
       </c>
       <c r="K87" s="1"/>
       <c r="L87" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M87" s="1" t="s">
         <v>396</v>
@@ -9859,7 +9740,7 @@
       </c>
       <c r="K88" s="1"/>
       <c r="L88" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M88" s="1" t="s">
         <v>396</v>
@@ -9917,7 +9798,7 @@
       </c>
       <c r="K89" s="1"/>
       <c r="L89" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M89" s="1" t="s">
         <v>166</v>
@@ -9975,7 +9856,7 @@
       </c>
       <c r="K90" s="1"/>
       <c r="L90" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M90" s="1" t="s">
         <v>166</v>
@@ -10033,7 +9914,7 @@
       </c>
       <c r="K91" s="1"/>
       <c r="L91" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M91" s="1" t="s">
         <v>118</v>
@@ -10091,7 +9972,7 @@
       </c>
       <c r="K92" s="1"/>
       <c r="L92" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M92" s="1" t="s">
         <v>118</v>
@@ -10205,7 +10086,7 @@
       </c>
       <c r="K94" s="1"/>
       <c r="L94" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M94" s="1" t="s">
         <v>118</v>
@@ -10543,7 +10424,7 @@
       </c>
       <c r="K100" s="1"/>
       <c r="L100" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M100" s="1" t="s">
         <v>98</v>
@@ -10601,7 +10482,7 @@
       </c>
       <c r="K101" s="1"/>
       <c r="L101" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M101" s="1" t="s">
         <v>98</v>
@@ -10771,7 +10652,7 @@
       </c>
       <c r="K104" s="1"/>
       <c r="L104" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M104" s="1" t="s">
         <v>118</v>
@@ -10885,7 +10766,7 @@
       </c>
       <c r="K106" s="1"/>
       <c r="L106" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M106" s="1" t="s">
         <v>118</v>
@@ -10943,7 +10824,7 @@
       </c>
       <c r="K107" s="1"/>
       <c r="L107" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M107" s="1" t="s">
         <v>118</v>
@@ -11057,7 +10938,7 @@
       </c>
       <c r="K109" s="1"/>
       <c r="L109" s="1" t="s">
-        <v>1005</v>
+        <v>992</v>
       </c>
       <c r="M109" s="1" t="s">
         <v>133</v>
@@ -11115,7 +10996,7 @@
       </c>
       <c r="K110" s="1"/>
       <c r="L110" s="1" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="M110" s="1" t="s">
         <v>98</v>
@@ -11229,7 +11110,7 @@
       </c>
       <c r="K112" s="1"/>
       <c r="L112" s="1" t="s">
-        <v>1005</v>
+        <v>992</v>
       </c>
       <c r="M112" s="1" t="s">
         <v>133</v>
@@ -11287,7 +11168,7 @@
       </c>
       <c r="K113" s="1"/>
       <c r="L113" s="1" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>138</v>
@@ -11345,7 +11226,7 @@
       </c>
       <c r="K114" s="1"/>
       <c r="L114" s="1" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="M114" s="1" t="s">
         <v>143</v>
@@ -11515,7 +11396,7 @@
       </c>
       <c r="K117" s="1"/>
       <c r="L117" s="1" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>98</v>
@@ -11629,7 +11510,7 @@
       </c>
       <c r="K119" s="1"/>
       <c r="L119" s="1" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="M119" s="1" t="s">
         <v>143</v>
@@ -11687,7 +11568,7 @@
       </c>
       <c r="K120" s="1"/>
       <c r="L120" s="1" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="M120" s="1" t="s">
         <v>138</v>
@@ -11745,7 +11626,7 @@
       </c>
       <c r="K121" s="1"/>
       <c r="L121" s="1" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="M121" s="1" t="s">
         <v>396</v>
@@ -11971,7 +11852,7 @@
       </c>
       <c r="K125" s="1"/>
       <c r="L125" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M125" s="1" t="s">
         <v>396</v>
@@ -12029,7 +11910,7 @@
       </c>
       <c r="K126" s="1"/>
       <c r="L126" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M126" s="1" t="s">
         <v>166</v>
@@ -12087,7 +11968,7 @@
       </c>
       <c r="K127" s="1"/>
       <c r="L127" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M127" s="1" t="s">
         <v>118</v>
@@ -12145,7 +12026,7 @@
       </c>
       <c r="K128" s="1"/>
       <c r="L128" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M128" s="1" t="s">
         <v>118</v>
@@ -12259,7 +12140,7 @@
       </c>
       <c r="K130" s="1"/>
       <c r="L130" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M130" s="1" t="s">
         <v>118</v>
@@ -12317,7 +12198,7 @@
       </c>
       <c r="K131" s="1"/>
       <c r="L131" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M131" s="1" t="s">
         <v>118</v>
@@ -12431,7 +12312,7 @@
       </c>
       <c r="K133" s="1"/>
       <c r="L133" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M133" s="1" t="s">
         <v>98</v>
@@ -12545,7 +12426,7 @@
       </c>
       <c r="K135" s="1"/>
       <c r="L135" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M135" s="1" t="s">
         <v>98</v>
@@ -12659,7 +12540,7 @@
       </c>
       <c r="K137" s="1"/>
       <c r="L137" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M137" s="1" t="s">
         <v>98</v>
@@ -12717,7 +12598,7 @@
       </c>
       <c r="K138" s="1"/>
       <c r="L138" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M138" s="1" t="s">
         <v>98</v>
@@ -12775,7 +12656,7 @@
       </c>
       <c r="K139" s="1"/>
       <c r="L139" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M139" s="1" t="s">
         <v>118</v>
@@ -12833,7 +12714,7 @@
       </c>
       <c r="K140" s="1"/>
       <c r="L140" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M140" s="1" t="s">
         <v>138</v>
@@ -12891,7 +12772,7 @@
       </c>
       <c r="K141" s="1"/>
       <c r="L141" s="1" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="M141" s="1" t="s">
         <v>166</v>
@@ -13005,7 +12886,7 @@
       </c>
       <c r="K143" s="1"/>
       <c r="L143" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M143" s="1" t="s">
         <v>118</v>
@@ -13063,7 +12944,7 @@
       </c>
       <c r="K144" s="1"/>
       <c r="L144" s="1" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="M144" s="1" t="s">
         <v>118</v>
@@ -13233,7 +13114,7 @@
       </c>
       <c r="K147" s="1"/>
       <c r="L147" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M147" s="1" t="s">
         <v>396</v>
@@ -13291,7 +13172,7 @@
       </c>
       <c r="K148" s="1"/>
       <c r="L148" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M148" s="1" t="s">
         <v>118</v>
@@ -13349,7 +13230,7 @@
       </c>
       <c r="K149" s="1"/>
       <c r="L149" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M149" s="1" t="s">
         <v>118</v>
@@ -13407,7 +13288,7 @@
       </c>
       <c r="K150" s="1"/>
       <c r="L150" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M150" s="1" t="s">
         <v>118</v>
@@ -13465,7 +13346,7 @@
       </c>
       <c r="K151" s="1"/>
       <c r="L151" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M151" s="1" t="s">
         <v>118</v>
@@ -13523,7 +13404,7 @@
       </c>
       <c r="K152" s="1"/>
       <c r="L152" s="1" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="M152" s="1" t="s">
         <v>138</v>
@@ -13637,7 +13518,7 @@
       </c>
       <c r="K154" s="1"/>
       <c r="L154" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M154" s="1" t="s">
         <v>118</v>
@@ -13695,7 +13576,7 @@
       </c>
       <c r="K155" s="1"/>
       <c r="L155" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M155" s="1" t="s">
         <v>143</v>
@@ -13809,7 +13690,7 @@
       </c>
       <c r="K157" s="1"/>
       <c r="L157" s="1" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="M157" s="1" t="s">
         <v>138</v>
@@ -13923,7 +13804,7 @@
       </c>
       <c r="K159" s="1"/>
       <c r="L159" s="1" t="s">
-        <v>1005</v>
+        <v>992</v>
       </c>
       <c r="M159" s="1" t="s">
         <v>133</v>
@@ -14037,7 +13918,7 @@
       </c>
       <c r="K161" s="1"/>
       <c r="L161" s="1" t="s">
-        <v>1005</v>
+        <v>992</v>
       </c>
       <c r="M161" s="1" t="s">
         <v>133</v>
@@ -14095,7 +13976,7 @@
       </c>
       <c r="K162" s="1"/>
       <c r="L162" s="1" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="M162" s="1" t="s">
         <v>143</v>
@@ -14251,13 +14132,13 @@
         <v>94</v>
       </c>
       <c r="G165" t="s">
-        <v>955</v>
+        <v>942</v>
       </c>
       <c r="H165">
         <v>17</v>
       </c>
       <c r="I165" t="s">
-        <v>956</v>
+        <v>943</v>
       </c>
       <c r="J165" t="s">
         <v>125</v>
@@ -14269,13 +14150,13 @@
         <v>99</v>
       </c>
       <c r="O165" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
       <c r="P165" t="s">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="Q165" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
       <c r="R165" t="s">
         <v>103</v>
@@ -14304,13 +14185,13 @@
         <v>104</v>
       </c>
       <c r="G166" t="s">
-        <v>960</v>
+        <v>947</v>
       </c>
       <c r="H166">
         <v>14</v>
       </c>
       <c r="I166" t="s">
-        <v>961</v>
+        <v>948</v>
       </c>
       <c r="J166" t="s">
         <v>125</v>
@@ -14322,13 +14203,13 @@
         <v>99</v>
       </c>
       <c r="O166" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
       <c r="P166" t="s">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="Q166" t="s">
-        <v>962</v>
+        <v>949</v>
       </c>
       <c r="R166" t="s">
         <v>103</v>
@@ -14357,13 +14238,13 @@
         <v>94</v>
       </c>
       <c r="G167" t="s">
-        <v>963</v>
+        <v>950</v>
       </c>
       <c r="H167">
         <v>14</v>
       </c>
       <c r="I167" t="s">
-        <v>964</v>
+        <v>951</v>
       </c>
       <c r="J167" t="s">
         <v>125</v>
@@ -14375,13 +14256,13 @@
         <v>99</v>
       </c>
       <c r="O167" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
       <c r="P167" t="s">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="Q167" t="s">
-        <v>965</v>
+        <v>952</v>
       </c>
       <c r="R167" t="s">
         <v>103</v>
@@ -14410,13 +14291,13 @@
         <v>104</v>
       </c>
       <c r="G168" t="s">
-        <v>966</v>
+        <v>953</v>
       </c>
       <c r="H168">
         <v>14</v>
       </c>
       <c r="I168" t="s">
-        <v>967</v>
+        <v>954</v>
       </c>
       <c r="J168" t="s">
         <v>125</v>
@@ -14428,13 +14309,13 @@
         <v>99</v>
       </c>
       <c r="O168" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
       <c r="P168" t="s">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="Q168" t="s">
-        <v>968</v>
+        <v>955</v>
       </c>
       <c r="R168" t="s">
         <v>103</v>
@@ -14463,13 +14344,13 @@
         <v>94</v>
       </c>
       <c r="G169" t="s">
-        <v>969</v>
+        <v>956</v>
       </c>
       <c r="H169">
         <v>14</v>
       </c>
       <c r="I169" t="s">
-        <v>970</v>
+        <v>957</v>
       </c>
       <c r="J169" t="s">
         <v>125</v>
@@ -14481,13 +14362,13 @@
         <v>99</v>
       </c>
       <c r="O169" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
       <c r="P169" t="s">
+        <v>945</v>
+      </c>
+      <c r="Q169" t="s">
         <v>958</v>
-      </c>
-      <c r="Q169" t="s">
-        <v>971</v>
       </c>
       <c r="R169" t="s">
         <v>103</v>
@@ -14516,13 +14397,13 @@
         <v>104</v>
       </c>
       <c r="G170" t="s">
-        <v>972</v>
+        <v>959</v>
       </c>
       <c r="H170">
         <v>15</v>
       </c>
       <c r="I170" t="s">
-        <v>973</v>
+        <v>960</v>
       </c>
       <c r="J170" t="s">
         <v>125</v>
@@ -14534,13 +14415,13 @@
         <v>99</v>
       </c>
       <c r="O170" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
       <c r="P170" t="s">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="Q170" t="s">
-        <v>974</v>
+        <v>961</v>
       </c>
       <c r="R170" t="s">
         <v>103</v>
@@ -14569,13 +14450,13 @@
         <v>94</v>
       </c>
       <c r="G171" t="s">
-        <v>975</v>
+        <v>962</v>
       </c>
       <c r="H171">
         <v>18</v>
       </c>
       <c r="I171" t="s">
-        <v>976</v>
+        <v>963</v>
       </c>
       <c r="J171" t="s">
         <v>125</v>
@@ -14587,13 +14468,13 @@
         <v>99</v>
       </c>
       <c r="O171" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
       <c r="P171" t="s">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="Q171" t="s">
-        <v>977</v>
+        <v>964</v>
       </c>
       <c r="R171" t="s">
         <v>103</v>
@@ -14613,22 +14494,22 @@
         <v>9</v>
       </c>
       <c r="D172" t="s">
-        <v>994</v>
+        <v>981</v>
       </c>
       <c r="E172" t="s">
-        <v>995</v>
+        <v>982</v>
       </c>
       <c r="F172" t="s">
         <v>199</v>
       </c>
       <c r="G172" t="s">
-        <v>978</v>
+        <v>965</v>
       </c>
       <c r="H172">
         <v>20</v>
       </c>
       <c r="I172" t="s">
-        <v>979</v>
+        <v>966</v>
       </c>
       <c r="J172" t="s">
         <v>125</v>
@@ -14640,13 +14521,13 @@
         <v>99</v>
       </c>
       <c r="O172" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
       <c r="P172" t="s">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="Q172" t="s">
-        <v>980</v>
+        <v>967</v>
       </c>
       <c r="R172" t="s">
         <v>103</v>
@@ -15221,152 +15102,152 @@
         <v>30</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>764</v>
+        <v>751</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>78</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>766</v>
+        <v>753</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>771</v>
+        <v>758</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>981</v>
+        <v>968</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>771</v>
+        <v>758</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="32">
       <c r="A4" s="1" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>982</v>
+        <v>969</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>773</v>
+        <v>760</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>771</v>
+        <v>758</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="32">
       <c r="A5" s="1" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>983</v>
+        <v>970</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>984</v>
+        <v>971</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>985</v>
+        <v>972</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="32">
       <c r="A6" s="1" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>988</v>
+        <v>975</v>
       </c>
       <c r="C6" s="1">
         <v>28</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>989</v>
+        <v>976</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="32">
       <c r="A7" s="1" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>986</v>
+        <v>973</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>987</v>
+        <v>974</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="48">
       <c r="A8" s="1" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>990</v>
+        <v>977</v>
       </c>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>991</v>
+        <v>978</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="32">
       <c r="A9" s="1" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>992</v>
+        <v>979</v>
       </c>
       <c r="C9" s="1">
         <v>84</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>993</v>
+        <v>980</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -15374,16 +15255,16 @@
         <v>36</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>775</v>
+        <v>762</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>776</v>
+        <v>763</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>777</v>
+        <v>764</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>778</v>
+        <v>765</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="66" customHeight="1">
@@ -15391,452 +15272,452 @@
         <v>36</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>779</v>
+        <v>766</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>781</v>
+        <v>768</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="66" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>784</v>
+        <v>771</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>785</v>
+        <v>772</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>786</v>
+        <v>773</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>787</v>
+        <v>774</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="66" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>788</v>
+        <v>775</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>789</v>
+        <v>776</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>790</v>
+        <v>777</v>
       </c>
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:5" ht="66" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>791</v>
+        <v>778</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>792</v>
+        <v>779</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>793</v>
+        <v>780</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>794</v>
+        <v>781</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="66" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>795</v>
+        <v>782</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>797</v>
+        <v>784</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>798</v>
+        <v>785</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>799</v>
+        <v>786</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="66" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>800</v>
+        <v>787</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>801</v>
+        <v>788</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>802</v>
+        <v>789</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>803</v>
+        <v>790</v>
       </c>
       <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:5" ht="66" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>800</v>
+        <v>787</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>806</v>
+        <v>793</v>
       </c>
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:5" ht="66" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>808</v>
+        <v>795</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>809</v>
+        <v>796</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>810</v>
+        <v>797</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>811</v>
+        <v>798</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="66" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>812</v>
+        <v>799</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>813</v>
+        <v>800</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>814</v>
+        <v>801</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>815</v>
+        <v>802</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>816</v>
+        <v>803</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="66" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>812</v>
+        <v>799</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>817</v>
+        <v>804</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>818</v>
+        <v>805</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>815</v>
+        <v>802</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>819</v>
+        <v>806</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="66" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>812</v>
+        <v>799</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>820</v>
+        <v>807</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>821</v>
+        <v>808</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>822</v>
+        <v>809</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>823</v>
+        <v>810</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="66" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>825</v>
+        <v>812</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>826</v>
+        <v>813</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>827</v>
+        <v>814</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>828</v>
+        <v>815</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="66" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>829</v>
+        <v>816</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>830</v>
+        <v>817</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>827</v>
+        <v>814</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>831</v>
+        <v>818</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="66" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="66" customHeight="1">
       <c r="A25" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>837</v>
-      </c>
       <c r="D25" s="1" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="66" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>840</v>
+        <v>827</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>841</v>
+        <v>828</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>842</v>
+        <v>829</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="66" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>843</v>
+        <v>830</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>844</v>
+        <v>831</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="66" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>846</v>
+        <v>833</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>847</v>
+        <v>834</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>848</v>
+        <v>835</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="66" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>849</v>
+        <v>836</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>850</v>
+        <v>837</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>851</v>
+        <v>838</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>852</v>
+        <v>839</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>996</v>
+        <v>983</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="66" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>849</v>
+        <v>836</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>853</v>
+        <v>840</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>854</v>
+        <v>841</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>855</v>
+        <v>842</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>856</v>
+        <v>843</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="66" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>849</v>
+        <v>836</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>857</v>
+        <v>844</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>858</v>
+        <v>845</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>859</v>
+        <v>846</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>860</v>
+        <v>847</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="66" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>861</v>
+        <v>848</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>863</v>
+        <v>850</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>865</v>
+        <v>852</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="66" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>861</v>
+        <v>848</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>866</v>
+        <v>853</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>868</v>
+        <v>855</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>869</v>
+        <v>856</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="66" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>870</v>
+        <v>857</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>871</v>
+        <v>858</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>872</v>
+        <v>859</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="66" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>870</v>
+        <v>857</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>876</v>
+        <v>863</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>877</v>
+        <v>864</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>878</v>
+        <v>865</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="66" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>870</v>
+        <v>857</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>879</v>
+        <v>866</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>881</v>
+        <v>868</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>882</v>
+        <v>869</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="66" customHeight="1">
       <c r="A37" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>870</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>883</v>
-      </c>
       <c r="C37" s="1" t="s">
-        <v>884</v>
+        <v>871</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>886</v>
+        <v>873</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="66" customHeight="1">
@@ -15844,16 +15725,16 @@
         <v>641</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>887</v>
+        <v>874</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>888</v>
+        <v>875</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>889</v>
+        <v>876</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>890</v>
+        <v>877</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="66" customHeight="1">
@@ -15861,16 +15742,16 @@
         <v>641</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>891</v>
+        <v>878</v>
       </c>
       <c r="C39" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>892</v>
+        <v>879</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>893</v>
+        <v>880</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="66" customHeight="1">
@@ -15878,16 +15759,16 @@
         <v>641</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>894</v>
+        <v>881</v>
       </c>
       <c r="C40" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>892</v>
+        <v>879</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>895</v>
+        <v>882</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="66" customHeight="1">
@@ -15895,67 +15776,67 @@
         <v>641</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>896</v>
+        <v>883</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>897</v>
+        <v>884</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>892</v>
+        <v>879</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>898</v>
+        <v>885</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="66" customHeight="1">
       <c r="A42" s="4" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>900</v>
+        <v>887</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>901</v>
+        <v>888</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>902</v>
+        <v>889</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>903</v>
+        <v>890</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="66" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>904</v>
+        <v>891</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>905</v>
+        <v>892</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>906</v>
+        <v>893</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>907</v>
+        <v>894</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="66" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>908</v>
+        <v>895</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>909</v>
+        <v>896</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>910</v>
+        <v>897</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>911</v>
+        <v>898</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="66" customHeight="1">
@@ -15963,191 +15844,191 @@
         <v>36</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>912</v>
+        <v>899</v>
       </c>
       <c r="C45" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>913</v>
+        <v>900</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>914</v>
+        <v>901</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="66" customHeight="1">
       <c r="A46" s="4" t="s">
-        <v>915</v>
+        <v>902</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>916</v>
+        <v>903</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>917</v>
+        <v>904</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>906</v>
+        <v>893</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>918</v>
+        <v>905</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="66" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>915</v>
+        <v>902</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>919</v>
+        <v>906</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>920</v>
+        <v>907</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>921</v>
+        <v>908</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>922</v>
+        <v>909</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="66" customHeight="1">
       <c r="A48" s="4" t="s">
-        <v>923</v>
+        <v>910</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>924</v>
+        <v>911</v>
       </c>
       <c r="C48" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>925</v>
+        <v>912</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>1002</v>
+        <v>989</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="66" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>923</v>
+        <v>910</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>926</v>
+        <v>913</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>103</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>927</v>
+        <v>914</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>928</v>
+        <v>915</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="66" customHeight="1">
       <c r="A50" s="4" t="s">
-        <v>929</v>
+        <v>916</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>930</v>
+        <v>917</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>931</v>
+        <v>918</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>812</v>
+        <v>799</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>932</v>
+        <v>919</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="66" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>929</v>
+        <v>916</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>933</v>
+        <v>920</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>934</v>
+        <v>921</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>935</v>
+        <v>922</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="66" customHeight="1">
       <c r="A52" s="4" t="s">
-        <v>915</v>
+        <v>902</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>936</v>
+        <v>923</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>937</v>
+        <v>924</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>938</v>
+        <v>925</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>939</v>
+        <v>926</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="66" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>915</v>
+        <v>902</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>941</v>
+        <v>928</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>942</v>
+        <v>929</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>943</v>
+        <v>930</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="66" customHeight="1">
       <c r="A54" s="4" t="s">
-        <v>795</v>
+        <v>782</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>944</v>
+        <v>931</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>945</v>
+        <v>932</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>946</v>
+        <v>933</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>947</v>
+        <v>934</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="66" customHeight="1">
       <c r="A55" s="4" t="s">
-        <v>948</v>
+        <v>935</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>949</v>
+        <v>936</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>950</v>
+        <v>937</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>906</v>
+        <v>893</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>951</v>
+        <v>938</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="66" customHeight="1">
       <c r="A56" s="4" t="s">
-        <v>952</v>
+        <v>939</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>82</v>
@@ -16156,10 +16037,10 @@
         <v>1</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>953</v>
+        <v>940</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>954</v>
+        <v>941</v>
       </c>
     </row>
   </sheetData>
@@ -16170,7 +16051,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{216EACFD-C9FD-4000-8498-48312F82252B}">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="7.58203125" bestFit="1" customWidth="1"/>
@@ -16189,34 +16070,34 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="10" t="s">
-        <v>1008</v>
+        <v>995</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>725</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1009</v>
+        <v>996</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1010</v>
+        <v>997</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>1011</v>
+        <v>998</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>1012</v>
+        <v>999</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>727</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>1013</v>
+        <v>1000</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>1014</v>
+        <v>1001</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>1015</v>
+        <v>1002</v>
       </c>
       <c r="K1" s="10" t="s">
         <v>53</v>
@@ -16225,12 +16106,12 @@
         <v>728</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>1016</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>1017</v>
+        <v>1004</v>
       </c>
       <c r="B2" t="s">
         <v>729</v>
@@ -16239,39 +16120,39 @@
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="E2" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="F2" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="G2" t="s">
         <v>729</v>
       </c>
       <c r="H2" t="s">
-        <v>1019</v>
+        <v>1006</v>
       </c>
       <c r="I2" t="s">
-        <v>1020</v>
+        <v>1007</v>
       </c>
       <c r="J2" t="s">
-        <v>1021</v>
+        <v>1008</v>
       </c>
       <c r="K2" t="s">
         <v>730</v>
       </c>
       <c r="L2" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
       <c r="M2" t="s">
-        <v>1023</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>1024</v>
+        <v>1011</v>
       </c>
       <c r="B3" t="s">
         <v>731</v>
@@ -16280,33 +16161,33 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="E3" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="F3" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="G3" t="s">
         <v>731</v>
       </c>
       <c r="H3" t="s">
-        <v>1026</v>
+        <v>1013</v>
       </c>
       <c r="K3" t="s">
         <v>732</v>
       </c>
       <c r="L3" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
       <c r="M3" t="s">
-        <v>1027</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>1028</v>
+        <v>1014</v>
       </c>
       <c r="B4" t="s">
         <v>733</v>
@@ -16315,68 +16196,68 @@
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="E4" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="F4" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="G4" t="s">
         <v>734</v>
       </c>
       <c r="H4" t="s">
-        <v>1029</v>
+        <v>1015</v>
       </c>
       <c r="K4" t="s">
         <v>735</v>
       </c>
       <c r="L4" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
       <c r="M4" t="s">
-        <v>1030</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>1031</v>
+        <v>1017</v>
       </c>
       <c r="B5" t="s">
-        <v>1032</v>
+        <v>1018</v>
       </c>
       <c r="C5" t="s">
         <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="E5" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="F5" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="G5" t="s">
         <v>734</v>
       </c>
       <c r="H5" t="s">
-        <v>1033</v>
+        <v>1019</v>
       </c>
       <c r="K5" t="s">
         <v>735</v>
       </c>
       <c r="L5" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
       <c r="M5" t="s">
-        <v>1034</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>1035</v>
+        <v>1021</v>
       </c>
       <c r="B6" t="s">
         <v>736</v>
@@ -16385,13 +16266,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="E6" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="F6" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="G6" t="s">
         <v>737</v>
@@ -16400,24 +16281,24 @@
         <v>695</v>
       </c>
       <c r="I6" t="s">
-        <v>1036</v>
+        <v>1022</v>
       </c>
       <c r="J6" t="s">
-        <v>1037</v>
+        <v>1023</v>
       </c>
       <c r="K6" t="s">
         <v>738</v>
       </c>
       <c r="L6" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
       <c r="M6" t="s">
-        <v>1038</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="B7" t="s">
         <v>739</v>
@@ -16426,39 +16307,39 @@
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="E7" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="F7" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="G7" t="s">
         <v>740</v>
       </c>
       <c r="H7" t="s">
-        <v>1040</v>
+        <v>1025</v>
       </c>
       <c r="I7" t="s">
-        <v>1005</v>
+        <v>992</v>
       </c>
       <c r="J7" t="s">
-        <v>1041</v>
+        <v>1026</v>
       </c>
       <c r="K7" t="s">
         <v>741</v>
       </c>
       <c r="L7" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
       <c r="M7" t="s">
-        <v>1042</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>1043</v>
+        <v>1028</v>
       </c>
       <c r="B8" t="s">
         <v>742</v>
@@ -16467,33 +16348,33 @@
         <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="E8" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="F8" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="G8" t="s">
         <v>742</v>
       </c>
       <c r="H8" t="s">
-        <v>1044</v>
+        <v>1029</v>
       </c>
       <c r="K8" t="s">
         <v>743</v>
       </c>
       <c r="L8" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
       <c r="M8" t="s">
-        <v>1045</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>1046</v>
+        <v>1031</v>
       </c>
       <c r="B9" t="s">
         <v>744</v>
@@ -16502,33 +16383,33 @@
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="E9" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="F9" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="I9" t="s">
-        <v>1047</v>
+        <v>1032</v>
       </c>
       <c r="J9" t="s">
-        <v>1048</v>
+        <v>1033</v>
       </c>
       <c r="K9" t="s">
-        <v>1049</v>
+        <v>1034</v>
       </c>
       <c r="L9" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
       <c r="M9" t="s">
-        <v>1050</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>1051</v>
+        <v>1036</v>
       </c>
       <c r="B10" t="s">
         <v>745</v>
@@ -16537,33 +16418,33 @@
         <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="E10" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="F10" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="I10" t="s">
-        <v>1047</v>
+        <v>1032</v>
       </c>
       <c r="J10" t="s">
-        <v>1048</v>
+        <v>1033</v>
       </c>
       <c r="K10" t="s">
-        <v>1049</v>
+        <v>1034</v>
       </c>
       <c r="L10" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
       <c r="M10" t="s">
-        <v>1052</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>1053</v>
+        <v>1038</v>
       </c>
       <c r="B11" t="s">
         <v>746</v>
@@ -16572,33 +16453,33 @@
         <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="E11" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="F11" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="I11" t="s">
-        <v>1047</v>
+        <v>1032</v>
       </c>
       <c r="J11" t="s">
-        <v>1048</v>
+        <v>1033</v>
       </c>
       <c r="K11" t="s">
-        <v>1049</v>
+        <v>1034</v>
       </c>
       <c r="L11" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
       <c r="M11" t="s">
-        <v>1054</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>1055</v>
+        <v>1040</v>
       </c>
       <c r="B12" t="s">
         <v>747</v>
@@ -16607,33 +16488,33 @@
         <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="E12" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="F12" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="I12" t="s">
-        <v>1047</v>
+        <v>1032</v>
       </c>
       <c r="J12" t="s">
-        <v>1048</v>
+        <v>1033</v>
       </c>
       <c r="K12" t="s">
-        <v>1049</v>
+        <v>1034</v>
       </c>
       <c r="L12" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
       <c r="M12" t="s">
-        <v>1052</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>1056</v>
+        <v>1041</v>
       </c>
       <c r="B13" t="s">
         <v>748</v>
@@ -16642,293 +16523,98 @@
         <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="E13" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="F13" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="I13" t="s">
-        <v>1047</v>
+        <v>1032</v>
       </c>
       <c r="J13" t="s">
-        <v>1048</v>
+        <v>1033</v>
       </c>
       <c r="K13" t="s">
-        <v>1049</v>
+        <v>1034</v>
       </c>
       <c r="L13" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
       <c r="M13" t="s">
-        <v>1057</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>1058</v>
+        <v>1043</v>
       </c>
       <c r="B14" t="s">
         <v>750</v>
       </c>
       <c r="C14" t="s">
-        <v>749</v>
+        <v>1234</v>
       </c>
       <c r="D14" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="E14" t="s">
-        <v>1025</v>
+        <v>1005</v>
       </c>
       <c r="F14" t="s">
-        <v>1025</v>
-      </c>
-      <c r="H14" t="s">
-        <v>1059</v>
+        <v>1012</v>
+      </c>
+      <c r="I14" t="s">
+        <v>1022</v>
+      </c>
+      <c r="J14" t="s">
+        <v>1023</v>
       </c>
       <c r="K14" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="L14" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
       <c r="M14" t="s">
-        <v>1060</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>1061</v>
+        <v>1044</v>
       </c>
       <c r="B15" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="C15" t="s">
-        <v>749</v>
+        <v>1232</v>
       </c>
       <c r="D15" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="E15" t="s">
-        <v>1025</v>
+        <v>1005</v>
       </c>
       <c r="F15" t="s">
-        <v>1025</v>
-      </c>
-      <c r="H15" t="s">
-        <v>1062</v>
+        <v>1012</v>
+      </c>
+      <c r="I15" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J15" t="s">
+        <v>1033</v>
       </c>
       <c r="K15" t="s">
-        <v>753</v>
+        <v>1034</v>
       </c>
       <c r="L15" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
       <c r="M15" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B16" t="s">
-        <v>754</v>
-      </c>
-      <c r="C16" t="s">
-        <v>749</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1018</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F16" t="s">
-        <v>1025</v>
-      </c>
-      <c r="H16" t="s">
-        <v>1064</v>
-      </c>
-      <c r="K16" t="s">
-        <v>755</v>
-      </c>
-      <c r="L16" t="s">
-        <v>1022</v>
-      </c>
-      <c r="M16" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B17" t="s">
-        <v>756</v>
-      </c>
-      <c r="C17" t="s">
-        <v>749</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1018</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F17" t="s">
-        <v>1025</v>
-      </c>
-      <c r="H17" t="s">
-        <v>695</v>
-      </c>
-      <c r="K17" t="s">
-        <v>757</v>
-      </c>
-      <c r="L17" t="s">
-        <v>1022</v>
-      </c>
-      <c r="M17" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B18" t="s">
-        <v>758</v>
-      </c>
-      <c r="C18" t="s">
-        <v>749</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1018</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F18" t="s">
-        <v>1025</v>
-      </c>
-      <c r="H18" t="s">
-        <v>717</v>
-      </c>
-      <c r="K18" t="s">
-        <v>760</v>
-      </c>
-      <c r="L18" t="s">
-        <v>1022</v>
-      </c>
-      <c r="M18" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B19" t="s">
-        <v>762</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F19" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I19" t="s">
-        <v>1036</v>
-      </c>
-      <c r="J19" t="s">
-        <v>1037</v>
-      </c>
-      <c r="K19" t="s">
-        <v>738</v>
-      </c>
-      <c r="L19" t="s">
-        <v>1022</v>
-      </c>
-      <c r="M19" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" t="s">
-        <v>1072</v>
-      </c>
-      <c r="B20" t="s">
-        <v>763</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F20" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I20" t="s">
-        <v>1047</v>
-      </c>
-      <c r="J20" t="s">
-        <v>1048</v>
-      </c>
-      <c r="K20" t="s">
-        <v>1049</v>
-      </c>
-      <c r="L20" t="s">
-        <v>1022</v>
-      </c>
-      <c r="M20" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" t="s">
-        <v>1074</v>
-      </c>
-      <c r="B21" t="s">
-        <v>761</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E21" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F21" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I21" t="s">
-        <v>1047</v>
-      </c>
-      <c r="J21" t="s">
-        <v>1048</v>
-      </c>
-      <c r="K21" t="s">
-        <v>1049</v>
-      </c>
-      <c r="L21" t="s">
-        <v>1022</v>
-      </c>
-      <c r="M21" t="s">
-        <v>1075</v>
+        <v>1233</v>
       </c>
     </row>
   </sheetData>
@@ -16940,7 +16626,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84C9ADE8-E8E1-442A-91BD-AA392C318296}">
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="7.58203125" bestFit="1" customWidth="1"/>
@@ -16954,42 +16640,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="10" t="s">
-        <v>1008</v>
+        <v>995</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>726</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1076</v>
+        <v>1045</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1077</v>
+        <v>1046</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>1078</v>
+        <v>1047</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>1079</v>
+        <v>1048</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>1080</v>
+        <v>1049</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>1081</v>
+        <v>1050</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>1016</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>1017</v>
+        <v>1004</v>
       </c>
       <c r="B2" t="s">
-        <v>1082</v>
+        <v>1051</v>
       </c>
       <c r="C2" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="E2">
         <v>12</v>
@@ -16998,21 +16684,21 @@
         <v>2</v>
       </c>
       <c r="G2" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="I2" t="s">
-        <v>1084</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>1017</v>
+        <v>1004</v>
       </c>
       <c r="B3" t="s">
-        <v>1085</v>
+        <v>1054</v>
       </c>
       <c r="C3" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="E3">
         <v>12</v>
@@ -17021,18 +16707,18 @@
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>1017</v>
+        <v>1004</v>
       </c>
       <c r="B4" t="s">
-        <v>1086</v>
+        <v>1055</v>
       </c>
       <c r="C4" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="E4">
         <v>12</v>
@@ -17041,18 +16727,18 @@
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>1017</v>
+        <v>1004</v>
       </c>
       <c r="B5" t="s">
-        <v>1087</v>
+        <v>1056</v>
       </c>
       <c r="C5" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="E5">
         <v>12</v>
@@ -17061,21 +16747,21 @@
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="I5" t="s">
-        <v>1088</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>1024</v>
+        <v>1011</v>
       </c>
       <c r="B6" t="s">
-        <v>1089</v>
+        <v>1058</v>
       </c>
       <c r="C6" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -17084,18 +16770,18 @@
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>1024</v>
+        <v>1011</v>
       </c>
       <c r="B7" t="s">
-        <v>1090</v>
+        <v>1059</v>
       </c>
       <c r="C7" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="E7">
         <v>12</v>
@@ -17104,18 +16790,18 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>1024</v>
+        <v>1011</v>
       </c>
       <c r="B8" t="s">
-        <v>1091</v>
+        <v>1062</v>
       </c>
       <c r="C8" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="E8">
         <v>12</v>
@@ -17124,21 +16810,18 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>1018</v>
-      </c>
-      <c r="I8" t="s">
-        <v>1092</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>1024</v>
+        <v>1014</v>
       </c>
       <c r="B9" t="s">
-        <v>1093</v>
+        <v>1063</v>
       </c>
       <c r="C9" t="s">
-        <v>1083</v>
+        <v>1064</v>
       </c>
       <c r="E9">
         <v>12</v>
@@ -17147,21 +16830,18 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>1018</v>
-      </c>
-      <c r="I9" t="s">
-        <v>1092</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>1024</v>
+        <v>1014</v>
       </c>
       <c r="B10" t="s">
-        <v>1094</v>
+        <v>1065</v>
       </c>
       <c r="C10" t="s">
-        <v>1083</v>
+        <v>1064</v>
       </c>
       <c r="E10">
         <v>12</v>
@@ -17170,18 +16850,18 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>1028</v>
+        <v>1014</v>
       </c>
       <c r="B11" t="s">
-        <v>1095</v>
+        <v>1066</v>
       </c>
       <c r="C11" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="E11">
         <v>12</v>
@@ -17190,18 +16870,21 @@
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>1018</v>
+        <v>1005</v>
+      </c>
+      <c r="I11" t="s">
+        <v>1067</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>1028</v>
+        <v>1017</v>
       </c>
       <c r="B12" t="s">
-        <v>1097</v>
+        <v>1068</v>
       </c>
       <c r="C12" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="E12">
         <v>12</v>
@@ -17210,18 +16893,21 @@
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>1018</v>
+        <v>1005</v>
+      </c>
+      <c r="I12" t="s">
+        <v>1069</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>1028</v>
+        <v>1017</v>
       </c>
       <c r="B13" t="s">
-        <v>1098</v>
+        <v>1070</v>
       </c>
       <c r="C13" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -17230,67 +16916,64 @@
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="I13" t="s">
-        <v>1099</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>1031</v>
+        <v>1021</v>
       </c>
       <c r="B14" t="s">
-        <v>1100</v>
+        <v>1071</v>
       </c>
       <c r="C14" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="E14">
         <v>12</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="I14" t="s">
-        <v>1101</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>1031</v>
+        <v>1021</v>
       </c>
       <c r="B15" t="s">
-        <v>1102</v>
+        <v>1073</v>
       </c>
       <c r="C15" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="E15">
         <v>12</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>1018</v>
-      </c>
-      <c r="I15" t="s">
-        <v>1101</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>1035</v>
+        <v>1021</v>
       </c>
       <c r="B16" t="s">
-        <v>1103</v>
+        <v>1074</v>
       </c>
       <c r="C16" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="E16">
         <v>12</v>
@@ -17299,61 +16982,58 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>1018</v>
-      </c>
-      <c r="I16" t="s">
-        <v>1104</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>1035</v>
+        <v>1021</v>
       </c>
       <c r="B17" t="s">
-        <v>1105</v>
+        <v>1075</v>
       </c>
       <c r="C17" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="E17">
         <v>12</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>1035</v>
+        <v>1021</v>
       </c>
       <c r="B18" t="s">
-        <v>1106</v>
+        <v>1076</v>
       </c>
       <c r="C18" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="E18">
         <v>12</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>1035</v>
+        <v>1021</v>
       </c>
       <c r="B19" t="s">
-        <v>1107</v>
+        <v>1077</v>
       </c>
       <c r="C19" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="E19">
         <v>12</v>
@@ -17362,18 +17042,18 @@
         <v>2</v>
       </c>
       <c r="G19" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>1035</v>
+        <v>1021</v>
       </c>
       <c r="B20" t="s">
-        <v>1108</v>
+        <v>1078</v>
       </c>
       <c r="C20" t="s">
-        <v>1096</v>
+        <v>1052</v>
       </c>
       <c r="E20">
         <v>12</v>
@@ -17382,18 +17062,18 @@
         <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>1035</v>
+        <v>1021</v>
       </c>
       <c r="B21" t="s">
-        <v>1109</v>
+        <v>1079</v>
       </c>
       <c r="C21" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="E21">
         <v>12</v>
@@ -17402,18 +17082,21 @@
         <v>2</v>
       </c>
       <c r="G21" t="s">
-        <v>1018</v>
+        <v>1005</v>
+      </c>
+      <c r="I21" t="s">
+        <v>1080</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>1035</v>
+        <v>1021</v>
       </c>
       <c r="B22" t="s">
-        <v>1110</v>
+        <v>1081</v>
       </c>
       <c r="C22" t="s">
-        <v>1083</v>
+        <v>1064</v>
       </c>
       <c r="E22">
         <v>12</v>
@@ -17422,18 +17105,18 @@
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>1035</v>
+        <v>1021</v>
       </c>
       <c r="B23" t="s">
-        <v>1111</v>
+        <v>1060</v>
       </c>
       <c r="C23" t="s">
-        <v>1096</v>
+        <v>1052</v>
       </c>
       <c r="E23">
         <v>12</v>
@@ -17442,21 +17125,21 @@
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="I23" t="s">
-        <v>1112</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>1035</v>
+        <v>1021</v>
       </c>
       <c r="B24" t="s">
-        <v>1113</v>
+        <v>1061</v>
       </c>
       <c r="C24" t="s">
-        <v>1096</v>
+        <v>1052</v>
       </c>
       <c r="E24">
         <v>12</v>
@@ -17465,64 +17148,67 @@
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>1018</v>
+        <v>1005</v>
+      </c>
+      <c r="I24" t="s">
+        <v>1227</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
       <c r="B25" t="s">
-        <v>1091</v>
+        <v>1082</v>
       </c>
       <c r="C25" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="E25">
         <v>12</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="I25" t="s">
-        <v>1114</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
       <c r="B26" t="s">
-        <v>1093</v>
+        <v>1084</v>
       </c>
       <c r="C26" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="E26">
         <v>12</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="I26" t="s">
-        <v>1114</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="B27" t="s">
-        <v>1115</v>
+        <v>1086</v>
       </c>
       <c r="C27" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="E27">
         <v>12</v>
@@ -17531,21 +17217,21 @@
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="I27" t="s">
-        <v>1116</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="B28" t="s">
-        <v>1117</v>
+        <v>1088</v>
       </c>
       <c r="C28" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="E28">
         <v>12</v>
@@ -17554,21 +17240,21 @@
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="I28" t="s">
-        <v>1118</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="B29" t="s">
-        <v>1119</v>
+        <v>1090</v>
       </c>
       <c r="C29" t="s">
-        <v>1083</v>
+        <v>1064</v>
       </c>
       <c r="E29">
         <v>12</v>
@@ -17577,67 +17263,61 @@
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="I29" t="s">
-        <v>1120</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="B30" t="s">
-        <v>1121</v>
+        <v>1092</v>
       </c>
       <c r="C30" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="E30">
         <v>12</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" t="s">
-        <v>1018</v>
-      </c>
-      <c r="I30" t="s">
-        <v>1122</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="B31" t="s">
-        <v>1123</v>
+        <v>1093</v>
       </c>
       <c r="C31" t="s">
-        <v>1096</v>
+        <v>1052</v>
       </c>
       <c r="E31">
         <v>12</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" t="s">
-        <v>1018</v>
-      </c>
-      <c r="I31" t="s">
-        <v>1124</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="B32" t="s">
-        <v>1125</v>
+        <v>1094</v>
       </c>
       <c r="C32" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="E32">
         <v>12</v>
@@ -17646,18 +17326,18 @@
         <v>2</v>
       </c>
       <c r="G32" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="B33" t="s">
-        <v>1126</v>
+        <v>1095</v>
       </c>
       <c r="C33" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="E33">
         <v>12</v>
@@ -17666,18 +17346,18 @@
         <v>2</v>
       </c>
       <c r="G33" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="B34" t="s">
-        <v>1127</v>
+        <v>1096</v>
       </c>
       <c r="C34" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="E34">
         <v>12</v>
@@ -17686,18 +17366,21 @@
         <v>2</v>
       </c>
       <c r="G34" t="s">
-        <v>1018</v>
+        <v>1005</v>
+      </c>
+      <c r="I34" t="s">
+        <v>1097</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="B35" t="s">
-        <v>1128</v>
+        <v>1098</v>
       </c>
       <c r="C35" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="E35">
         <v>12</v>
@@ -17706,18 +17389,21 @@
         <v>2</v>
       </c>
       <c r="G35" t="s">
-        <v>1018</v>
+        <v>1005</v>
+      </c>
+      <c r="I35" t="s">
+        <v>1099</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
       <c r="B36" t="s">
-        <v>1129</v>
+        <v>1100</v>
       </c>
       <c r="C36" t="s">
-        <v>1083</v>
+        <v>1064</v>
       </c>
       <c r="E36">
         <v>12</v>
@@ -17726,21 +17412,21 @@
         <v>2</v>
       </c>
       <c r="G36" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="I36" t="s">
-        <v>1130</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
       <c r="B37" t="s">
-        <v>1131</v>
+        <v>1101</v>
       </c>
       <c r="C37" t="s">
-        <v>1083</v>
+        <v>1064</v>
       </c>
       <c r="E37">
         <v>12</v>
@@ -17749,21 +17435,18 @@
         <v>2</v>
       </c>
       <c r="G37" t="s">
-        <v>1018</v>
-      </c>
-      <c r="I37" t="s">
-        <v>1132</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>1043</v>
+        <v>1028</v>
       </c>
       <c r="B38" t="s">
-        <v>1133</v>
+        <v>1102</v>
       </c>
       <c r="C38" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="E38">
         <v>12</v>
@@ -17772,64 +17455,67 @@
         <v>2</v>
       </c>
       <c r="G38" t="s">
-        <v>1018</v>
-      </c>
-      <c r="I38" t="s">
-        <v>1045</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>1043</v>
+        <v>1031</v>
       </c>
       <c r="B39" t="s">
-        <v>1134</v>
+        <v>1103</v>
       </c>
       <c r="C39" t="s">
-        <v>1096</v>
+        <v>1104</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1105</v>
       </c>
       <c r="E39">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>1018</v>
+        <v>1012</v>
+      </c>
+      <c r="I39" t="s">
+        <v>1106</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>1043</v>
+        <v>1031</v>
       </c>
       <c r="B40" t="s">
-        <v>1135</v>
+        <v>1107</v>
       </c>
       <c r="C40" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="E40">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>1018</v>
+        <v>1012</v>
+      </c>
+      <c r="I40" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>1046</v>
+        <v>1031</v>
       </c>
       <c r="B41" t="s">
-        <v>1136</v>
+        <v>1109</v>
       </c>
       <c r="C41" t="s">
-        <v>1137</v>
-      </c>
-      <c r="D41" t="s">
-        <v>1138</v>
+        <v>1052</v>
       </c>
       <c r="E41">
         <v>10</v>
@@ -17838,21 +17524,21 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="I41" t="s">
-        <v>1139</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>1046</v>
+        <v>1031</v>
       </c>
       <c r="B42" t="s">
-        <v>1140</v>
+        <v>1110</v>
       </c>
       <c r="C42" t="s">
-        <v>1096</v>
+        <v>1052</v>
       </c>
       <c r="E42">
         <v>10</v>
@@ -17861,21 +17547,18 @@
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I42" t="s">
-        <v>1141</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>1046</v>
+        <v>1031</v>
       </c>
       <c r="B43" t="s">
-        <v>1142</v>
+        <v>1111</v>
       </c>
       <c r="C43" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="E43">
         <v>10</v>
@@ -17884,84 +17567,81 @@
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I43" t="s">
-        <v>1141</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>1046</v>
+        <v>1031</v>
       </c>
       <c r="B44" t="s">
-        <v>1143</v>
+        <v>1112</v>
       </c>
       <c r="C44" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="E44">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>1025</v>
+        <v>1012</v>
+      </c>
+      <c r="I44" t="s">
+        <v>1113</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>1046</v>
+        <v>1036</v>
       </c>
       <c r="B45" t="s">
-        <v>1144</v>
+        <v>1114</v>
       </c>
       <c r="C45" t="s">
-        <v>1083</v>
+        <v>1064</v>
       </c>
       <c r="E45">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>1046</v>
+        <v>1036</v>
       </c>
       <c r="B46" t="s">
-        <v>1145</v>
+        <v>1115</v>
       </c>
       <c r="C46" t="s">
-        <v>1083</v>
+        <v>1064</v>
       </c>
       <c r="E46">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I46" t="s">
-        <v>1146</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>1051</v>
+        <v>1036</v>
       </c>
       <c r="B47" t="s">
-        <v>1147</v>
+        <v>1116</v>
       </c>
       <c r="C47" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="E47">
         <v>24</v>
@@ -17970,18 +17650,18 @@
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>1051</v>
+        <v>1036</v>
       </c>
       <c r="B48" t="s">
-        <v>1148</v>
+        <v>1117</v>
       </c>
       <c r="C48" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="E48">
         <v>24</v>
@@ -17990,18 +17670,18 @@
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>1051</v>
+        <v>1036</v>
       </c>
       <c r="B49" t="s">
-        <v>1149</v>
+        <v>1118</v>
       </c>
       <c r="C49" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="E49">
         <v>24</v>
@@ -18010,18 +17690,18 @@
         <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>1051</v>
+        <v>1036</v>
       </c>
       <c r="B50" t="s">
-        <v>1150</v>
+        <v>1119</v>
       </c>
       <c r="C50" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="E50">
         <v>24</v>
@@ -18030,61 +17710,67 @@
         <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>1051</v>
+        <v>1038</v>
       </c>
       <c r="B51" t="s">
-        <v>1151</v>
+        <v>1120</v>
       </c>
       <c r="C51" t="s">
-        <v>1096</v>
+        <v>1104</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1121</v>
       </c>
       <c r="E51">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>1025</v>
+        <v>1012</v>
+      </c>
+      <c r="I51" t="s">
+        <v>1122</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>1051</v>
+        <v>1038</v>
       </c>
       <c r="B52" t="s">
-        <v>1152</v>
+        <v>1123</v>
       </c>
       <c r="C52" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="E52">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>1025</v>
+        <v>1012</v>
+      </c>
+      <c r="I52" t="s">
+        <v>1124</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>1053</v>
+        <v>1038</v>
       </c>
       <c r="B53" t="s">
-        <v>1153</v>
+        <v>1125</v>
       </c>
       <c r="C53" t="s">
-        <v>1137</v>
-      </c>
-      <c r="D53" t="s">
-        <v>1154</v>
+        <v>1052</v>
       </c>
       <c r="E53">
         <v>12</v>
@@ -18093,21 +17779,21 @@
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="I53" t="s">
-        <v>1155</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>1053</v>
+        <v>1038</v>
       </c>
       <c r="B54" t="s">
-        <v>1156</v>
+        <v>1127</v>
       </c>
       <c r="C54" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="E54">
         <v>12</v>
@@ -18116,492 +17802,204 @@
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="I54" t="s">
-        <v>1157</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>1053</v>
+        <v>1040</v>
       </c>
       <c r="B55" t="s">
-        <v>1158</v>
+        <v>1129</v>
       </c>
       <c r="C55" t="s">
-        <v>1083</v>
+        <v>1104</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1130</v>
       </c>
       <c r="E55">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>1025</v>
+        <v>1012</v>
+      </c>
+      <c r="H55" t="s">
+        <v>1131</v>
       </c>
       <c r="I55" t="s">
-        <v>1159</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>1053</v>
+        <v>1041</v>
       </c>
       <c r="B56" t="s">
-        <v>1160</v>
+        <v>1133</v>
       </c>
       <c r="C56" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E56">
-        <v>12</v>
+        <v>1064</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="I56" t="s">
-        <v>1161</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>1055</v>
+        <v>1041</v>
       </c>
       <c r="B57" t="s">
-        <v>1162</v>
+        <v>1135</v>
       </c>
       <c r="C57" t="s">
-        <v>1137</v>
-      </c>
-      <c r="D57" t="s">
-        <v>1163</v>
-      </c>
-      <c r="E57">
-        <v>6</v>
+        <v>1064</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>1025</v>
-      </c>
-      <c r="H57" t="s">
-        <v>1164</v>
+        <v>1012</v>
       </c>
       <c r="I57" t="s">
-        <v>1165</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>1056</v>
+        <v>1041</v>
       </c>
       <c r="B58" t="s">
-        <v>1166</v>
+        <v>1137</v>
       </c>
       <c r="C58" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="I58" t="s">
-        <v>1167</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>1056</v>
+        <v>1043</v>
       </c>
       <c r="B59" t="s">
-        <v>1168</v>
+        <v>1139</v>
       </c>
       <c r="C59" t="s">
-        <v>1096</v>
+        <v>1052</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="I59" t="s">
-        <v>1169</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>1056</v>
+        <v>1043</v>
       </c>
       <c r="B60" t="s">
-        <v>1170</v>
+        <v>1141</v>
       </c>
       <c r="C60" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="I60" t="s">
-        <v>1171</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>1058</v>
+        <v>1043</v>
       </c>
       <c r="B61" t="s">
-        <v>1172</v>
+        <v>1143</v>
       </c>
       <c r="C61" t="s">
-        <v>1096</v>
+        <v>1064</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61" t="s">
+        <v>1012</v>
       </c>
       <c r="I61" t="s">
-        <v>1173</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>1058</v>
+        <v>1044</v>
       </c>
       <c r="B62" t="s">
-        <v>1174</v>
+        <v>1145</v>
       </c>
       <c r="C62" t="s">
-        <v>1096</v>
+        <v>1104</v>
+      </c>
+      <c r="D62" t="s">
+        <v>1146</v>
       </c>
       <c r="I62" t="s">
-        <v>1173</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>1058</v>
+        <v>1044</v>
       </c>
       <c r="B63" t="s">
-        <v>1175</v>
+        <v>1147</v>
       </c>
       <c r="C63" t="s">
-        <v>1096</v>
+        <v>1052</v>
       </c>
       <c r="I63" t="s">
-        <v>1173</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>1058</v>
+        <v>1044</v>
       </c>
       <c r="B64" t="s">
-        <v>1176</v>
+        <v>1148</v>
       </c>
       <c r="C64" t="s">
-        <v>1096</v>
+        <v>1052</v>
       </c>
       <c r="I64" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9">
-      <c r="A65" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B65" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C65" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I65" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9">
-      <c r="A66" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B66" t="s">
-        <v>1178</v>
-      </c>
-      <c r="C66" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I66" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9">
-      <c r="A67" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B67" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C67" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E67">
-        <v>12</v>
-      </c>
-      <c r="F67">
-        <v>3</v>
-      </c>
-      <c r="G67" t="s">
-        <v>1018</v>
-      </c>
-      <c r="I67" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9">
-      <c r="A68" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B68" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C68" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E68">
-        <v>12</v>
-      </c>
-      <c r="F68">
-        <v>3</v>
-      </c>
-      <c r="G68" t="s">
-        <v>1018</v>
-      </c>
-      <c r="I68" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9">
-      <c r="A69" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B69" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C69" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I69" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9">
-      <c r="A70" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1183</v>
-      </c>
-      <c r="C70" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I70" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9">
-      <c r="A71" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B71" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C71" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I71" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9">
-      <c r="A72" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B72" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C72" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I72" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9">
-      <c r="A73" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B73" t="s">
-        <v>759</v>
-      </c>
-      <c r="C73" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I73" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9">
-      <c r="A74" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B74" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C74" t="s">
-        <v>1083</v>
-      </c>
-      <c r="F74">
-        <v>1</v>
-      </c>
-      <c r="G74" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I74" t="s">
-        <v>1187</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9">
-      <c r="A75" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B75" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C75" t="s">
-        <v>1096</v>
-      </c>
-      <c r="F75">
-        <v>1</v>
-      </c>
-      <c r="G75" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I75" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9">
-      <c r="A76" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1190</v>
-      </c>
-      <c r="C76" t="s">
-        <v>1096</v>
-      </c>
-      <c r="F76">
-        <v>1</v>
-      </c>
-      <c r="G76" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I76" t="s">
-        <v>1191</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9">
-      <c r="A77" t="s">
-        <v>1072</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1192</v>
-      </c>
-      <c r="C77" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I77" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9">
-      <c r="A78" t="s">
-        <v>1072</v>
-      </c>
-      <c r="B78" t="s">
-        <v>1194</v>
-      </c>
-      <c r="C78" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I78" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9">
-      <c r="A79" t="s">
-        <v>1072</v>
-      </c>
-      <c r="B79" t="s">
-        <v>1195</v>
-      </c>
-      <c r="C79" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I79" t="s">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9">
-      <c r="A80" t="s">
-        <v>1074</v>
-      </c>
-      <c r="B80" t="s">
-        <v>1197</v>
-      </c>
-      <c r="C80" t="s">
-        <v>1137</v>
-      </c>
-      <c r="D80" t="s">
-        <v>1198</v>
-      </c>
-      <c r="I80" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9">
-      <c r="A81" t="s">
-        <v>1074</v>
-      </c>
-      <c r="B81" t="s">
-        <v>1199</v>
-      </c>
-      <c r="C81" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I81" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9">
-      <c r="A82" t="s">
-        <v>1074</v>
-      </c>
-      <c r="B82" t="s">
-        <v>1200</v>
-      </c>
-      <c r="C82" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I82" t="s">
-        <v>1201</v>
+        <v>1229</v>
       </c>
     </row>
   </sheetData>
@@ -18632,16 +18030,16 @@
         <v>18</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1202</v>
+        <v>1149</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1203</v>
+        <v>1150</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>1205</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -18652,13 +18050,13 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>1206</v>
+        <v>1153</v>
       </c>
       <c r="E2" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F2" t="s">
-        <v>1207</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -18669,16 +18067,16 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="D3" t="s">
         <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F3" t="s">
-        <v>1209</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -18689,16 +18087,16 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>1210</v>
+        <v>1157</v>
       </c>
       <c r="D4" t="s">
         <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F4" t="s">
-        <v>1211</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -18709,16 +18107,16 @@
         <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>1210</v>
+        <v>1157</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F5" t="s">
-        <v>1212</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -18729,16 +18127,16 @@
         <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>1210</v>
+        <v>1157</v>
       </c>
       <c r="D6" t="s">
-        <v>1213</v>
+        <v>1160</v>
       </c>
       <c r="E6" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F6" t="s">
-        <v>1214</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -18749,16 +18147,16 @@
         <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>1210</v>
+        <v>1157</v>
       </c>
       <c r="D7" t="s">
-        <v>1215</v>
+        <v>1162</v>
       </c>
       <c r="E7" t="s">
-        <v>1216</v>
+        <v>1163</v>
       </c>
       <c r="F7" t="s">
-        <v>1217</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -18769,16 +18167,16 @@
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="D8" t="s">
-        <v>1218</v>
+        <v>1165</v>
       </c>
       <c r="E8" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F8" t="s">
-        <v>1219</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -18789,16 +18187,16 @@
         <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>1206</v>
+        <v>1153</v>
       </c>
       <c r="D9" t="s">
-        <v>1220</v>
+        <v>1167</v>
       </c>
       <c r="E9" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F9" t="s">
-        <v>1221</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -18809,13 +18207,13 @@
         <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="E10" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F10" t="s">
-        <v>1222</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -18826,16 +18224,16 @@
         <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="D11" t="s">
-        <v>1223</v>
+        <v>1170</v>
       </c>
       <c r="E11" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F11" t="s">
-        <v>1224</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -18846,16 +18244,16 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>1210</v>
+        <v>1157</v>
       </c>
       <c r="D12" t="s">
         <v>52</v>
       </c>
       <c r="E12" t="s">
-        <v>1216</v>
+        <v>1163</v>
       </c>
       <c r="F12" t="s">
-        <v>1225</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -18863,19 +18261,19 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>1003</v>
+        <v>990</v>
       </c>
       <c r="C13" t="s">
-        <v>1210</v>
+        <v>1157</v>
       </c>
       <c r="D13" t="s">
-        <v>1226</v>
+        <v>1173</v>
       </c>
       <c r="E13" t="s">
-        <v>1216</v>
+        <v>1163</v>
       </c>
       <c r="F13" t="s">
-        <v>1227</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -18886,13 +18284,13 @@
         <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="E14" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F14" t="s">
-        <v>1228</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -18903,13 +18301,13 @@
         <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="E15" t="s">
-        <v>1216</v>
+        <v>1163</v>
       </c>
       <c r="F15" t="s">
-        <v>1229</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -18920,13 +18318,13 @@
         <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="E16" t="s">
-        <v>1216</v>
+        <v>1163</v>
       </c>
       <c r="F16" t="s">
-        <v>1230</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -18937,13 +18335,13 @@
         <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="E17" t="s">
-        <v>1216</v>
+        <v>1163</v>
       </c>
       <c r="F17" t="s">
-        <v>1231</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -18954,16 +18352,16 @@
         <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="D18" t="s">
-        <v>1232</v>
+        <v>1179</v>
       </c>
       <c r="E18" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F18" t="s">
-        <v>1233</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -18974,16 +18372,16 @@
         <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="D19" t="s">
-        <v>1234</v>
+        <v>1181</v>
       </c>
       <c r="E19" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F19" t="s">
-        <v>1235</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -18994,429 +18392,429 @@
         <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="E20" t="s">
-        <v>1216</v>
+        <v>1163</v>
       </c>
       <c r="F20" t="s">
-        <v>1236</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>1237</v>
+        <v>1184</v>
       </c>
       <c r="B21" t="s">
-        <v>1008</v>
+        <v>995</v>
       </c>
       <c r="C21" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="D21" t="s">
-        <v>1238</v>
+        <v>1185</v>
       </c>
       <c r="E21" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F21" t="s">
-        <v>1239</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>1237</v>
+        <v>1184</v>
       </c>
       <c r="B22" t="s">
         <v>725</v>
       </c>
       <c r="C22" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="E22" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F22" t="s">
-        <v>1240</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>1237</v>
+        <v>1184</v>
       </c>
       <c r="B23" t="s">
-        <v>1009</v>
+        <v>996</v>
       </c>
       <c r="C23" t="s">
-        <v>1210</v>
+        <v>1157</v>
       </c>
       <c r="D23" t="s">
-        <v>1241</v>
+        <v>1188</v>
       </c>
       <c r="E23" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F23" t="s">
-        <v>1242</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>1237</v>
+        <v>1184</v>
       </c>
       <c r="B24" t="s">
-        <v>1010</v>
+        <v>997</v>
       </c>
       <c r="C24" t="s">
-        <v>1210</v>
+        <v>1157</v>
       </c>
       <c r="D24" t="s">
-        <v>1243</v>
+        <v>1190</v>
       </c>
       <c r="E24" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F24" t="s">
-        <v>1244</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>1237</v>
+        <v>1184</v>
       </c>
       <c r="B25" t="s">
-        <v>1011</v>
+        <v>998</v>
       </c>
       <c r="C25" t="s">
-        <v>1210</v>
+        <v>1157</v>
       </c>
       <c r="D25" t="s">
-        <v>1243</v>
+        <v>1190</v>
       </c>
       <c r="E25" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F25" t="s">
-        <v>1245</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>1237</v>
+        <v>1184</v>
       </c>
       <c r="B26" t="s">
-        <v>1012</v>
+        <v>999</v>
       </c>
       <c r="C26" t="s">
-        <v>1210</v>
+        <v>1157</v>
       </c>
       <c r="D26" t="s">
-        <v>1243</v>
+        <v>1190</v>
       </c>
       <c r="E26" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F26" t="s">
-        <v>1246</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>1237</v>
+        <v>1184</v>
       </c>
       <c r="B27" t="s">
         <v>727</v>
       </c>
       <c r="C27" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="E27" t="s">
-        <v>1216</v>
+        <v>1163</v>
       </c>
       <c r="F27" t="s">
-        <v>1247</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>1237</v>
+        <v>1184</v>
       </c>
       <c r="B28" t="s">
-        <v>1013</v>
+        <v>1000</v>
       </c>
       <c r="C28" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="D28" t="s">
-        <v>1248</v>
+        <v>1195</v>
       </c>
       <c r="E28" t="s">
-        <v>1216</v>
+        <v>1163</v>
       </c>
       <c r="F28" t="s">
-        <v>1249</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>1237</v>
+        <v>1184</v>
       </c>
       <c r="B29" t="s">
-        <v>1014</v>
+        <v>1001</v>
       </c>
       <c r="C29" t="s">
-        <v>1210</v>
+        <v>1157</v>
       </c>
       <c r="D29" t="s">
-        <v>1250</v>
+        <v>1197</v>
       </c>
       <c r="E29" t="s">
-        <v>1216</v>
+        <v>1163</v>
       </c>
       <c r="F29" t="s">
-        <v>1251</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>1237</v>
+        <v>1184</v>
       </c>
       <c r="B30" t="s">
-        <v>1015</v>
+        <v>1002</v>
       </c>
       <c r="C30" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="E30" t="s">
-        <v>1216</v>
+        <v>1163</v>
       </c>
       <c r="F30" t="s">
-        <v>1252</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>1237</v>
+        <v>1184</v>
       </c>
       <c r="B31" t="s">
         <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="E31" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F31" t="s">
-        <v>1253</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>1237</v>
+        <v>1184</v>
       </c>
       <c r="B32" t="s">
         <v>728</v>
       </c>
       <c r="C32" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="D32" t="s">
-        <v>1254</v>
+        <v>1201</v>
       </c>
       <c r="E32" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F32" t="s">
-        <v>1255</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>1237</v>
+        <v>1184</v>
       </c>
       <c r="B33" t="s">
-        <v>1016</v>
+        <v>1003</v>
       </c>
       <c r="C33" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="E33" t="s">
-        <v>1216</v>
+        <v>1163</v>
       </c>
       <c r="F33" t="s">
-        <v>1256</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>1257</v>
+        <v>1204</v>
       </c>
       <c r="B34" t="s">
-        <v>1008</v>
+        <v>995</v>
       </c>
       <c r="C34" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="D34" t="s">
-        <v>1238</v>
+        <v>1185</v>
       </c>
       <c r="E34" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F34" t="s">
-        <v>1258</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>1257</v>
+        <v>1204</v>
       </c>
       <c r="B35" t="s">
         <v>726</v>
       </c>
       <c r="C35" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="D35" t="s">
-        <v>1259</v>
+        <v>1206</v>
       </c>
       <c r="E35" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F35" t="s">
-        <v>1260</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>1257</v>
+        <v>1204</v>
       </c>
       <c r="B36" t="s">
-        <v>1076</v>
+        <v>1045</v>
       </c>
       <c r="C36" t="s">
-        <v>1210</v>
+        <v>1157</v>
       </c>
       <c r="D36" t="s">
-        <v>1261</v>
+        <v>1208</v>
       </c>
       <c r="E36" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F36" t="s">
-        <v>1262</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>1257</v>
+        <v>1204</v>
       </c>
       <c r="B37" t="s">
-        <v>1077</v>
+        <v>1046</v>
       </c>
       <c r="C37" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="D37" t="s">
-        <v>1259</v>
+        <v>1206</v>
       </c>
       <c r="E37" t="s">
-        <v>1216</v>
+        <v>1163</v>
       </c>
       <c r="F37" t="s">
-        <v>1263</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>1257</v>
+        <v>1204</v>
       </c>
       <c r="B38" t="s">
-        <v>1078</v>
+        <v>1047</v>
       </c>
       <c r="C38" t="s">
-        <v>1206</v>
+        <v>1153</v>
       </c>
       <c r="E38" t="s">
-        <v>1216</v>
+        <v>1163</v>
       </c>
       <c r="F38" t="s">
-        <v>1264</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>1257</v>
+        <v>1204</v>
       </c>
       <c r="B39" t="s">
-        <v>1079</v>
+        <v>1048</v>
       </c>
       <c r="C39" t="s">
-        <v>1206</v>
+        <v>1153</v>
       </c>
       <c r="E39" t="s">
-        <v>1216</v>
+        <v>1163</v>
       </c>
       <c r="F39" t="s">
-        <v>1265</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>1257</v>
+        <v>1204</v>
       </c>
       <c r="B40" t="s">
-        <v>1080</v>
+        <v>1049</v>
       </c>
       <c r="C40" t="s">
-        <v>1210</v>
+        <v>1157</v>
       </c>
       <c r="D40" t="s">
-        <v>1243</v>
+        <v>1190</v>
       </c>
       <c r="E40" t="s">
-        <v>1216</v>
+        <v>1163</v>
       </c>
       <c r="F40" t="s">
-        <v>1266</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>1257</v>
+        <v>1204</v>
       </c>
       <c r="B41" t="s">
-        <v>1081</v>
+        <v>1050</v>
       </c>
       <c r="C41" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="D41" t="s">
-        <v>1267</v>
+        <v>1214</v>
       </c>
       <c r="E41" t="s">
-        <v>1216</v>
+        <v>1163</v>
       </c>
       <c r="F41" t="s">
-        <v>1268</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>1257</v>
+        <v>1204</v>
       </c>
       <c r="B42" t="s">
-        <v>1016</v>
+        <v>1003</v>
       </c>
       <c r="C42" t="s">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="E42" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F42" t="s">
         <v>1216</v>
-      </c>
-      <c r="F42" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -19427,13 +18825,13 @@
         <v>78</v>
       </c>
       <c r="C43" t="s">
-        <v>1270</v>
+        <v>1217</v>
       </c>
       <c r="D43" t="s">
-        <v>1271</v>
+        <v>1218</v>
       </c>
       <c r="E43" t="s">
-        <v>1204</v>
+        <v>1151</v>
       </c>
       <c r="F43" t="s">
         <v>79</v>

--- a/outputs/mai-report-policy/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7863BAE1-3BB9-4636-89F1-3C36F6D4348C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E4BF72-E475-4F03-80C9-BEC7B6CE9607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38370" yWindow="-4030" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="열정의" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">상병코드조건!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">상병코드조건!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">열정의!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">질환규칙!$A$1:$M$1</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3886" uniqueCount="1236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3945" uniqueCount="1293">
   <si>
     <t>maiReport 식이 참조·설정 데이터 v1.0.0 | 2026-09-22</t>
   </si>
@@ -2257,9 +2257,6 @@
     <t>만성 신장질환</t>
   </si>
   <si>
-    <t>만성 콩팥병</t>
-  </si>
-  <si>
     <t>KDIGO-2024; NIDDK-CKD</t>
   </si>
   <si>
@@ -2291,9 +2288,6 @@
   </si>
   <si>
     <t>위 절제 · 비만수술 상태</t>
-  </si>
-  <si>
-    <t>인지 · 연하 장애</t>
   </si>
   <si>
     <t>투석 · 이식</t>
@@ -3498,15 +3492,6 @@
     <t>신장 이식 상태</t>
   </si>
   <si>
-    <t>F00</t>
-  </si>
-  <si>
-    <t>F03</t>
-  </si>
-  <si>
-    <t>G30</t>
-  </si>
-  <si>
     <t>R13</t>
   </si>
   <si>
@@ -3753,14 +3738,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>후보 조건을 출시 전에 확정해야 한다</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>연하장애. 후보 조건을 출시 전에 확정해야 한다</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>진료기록만으로 활성 질환·치료 필요·식품 금기를 확정하지 않는다. I12 · I13은 만성 신장질환(DX-05)에만 둔다</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -3773,16 +3750,213 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>상세기획이 연하장애를 보호 대상으로 적고 있어 1차에 둔다. 후보 조건이 아직 없어 지금은 걸리지 않는다 — 출시 전 확정 필요</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>1차</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>DX-05에서 코드를 분리했다. 상세기획이 투석을 보호 대상으로 적고 있고 후보 조건도 완성돼 있어 1차에 둔다</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>접두</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>뇌졸중·수술 뒤 부상병으로 붙는 일이 많아 주상병만 보면 놓친다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>만성 신장질환</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>연하장애</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼킴이 어려운 상태에서는 음식의 양·속도·질감을 개인 평가 없이 자동으로 권하지 않는다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>상세기획이 연하장애를 보호 대상으로 적고 있어 1차에 둔다. 인지장애(F00~F03 · G30)는 뺐다 — 치매 자체가 식이 목표의 금기가 아니고 후기의 삼킴 문제는 R13으로 잡힌다. 뇌졸중 경로는 DX-06이 일부 잡는다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>코드 이름</t>
+  </si>
+  <si>
+    <t>2형 당뇨병</t>
+  </si>
+  <si>
+    <t>기타 명시된 당뇨병</t>
+  </si>
+  <si>
+    <t>상세불명의 당뇨병</t>
+  </si>
+  <si>
+    <t>본태성(원발성) 고혈압</t>
+  </si>
+  <si>
+    <t>고혈압성 심장질환</t>
+  </si>
+  <si>
+    <t>이차성 고혈압</t>
+  </si>
+  <si>
+    <t>순수 고콜레스테롤혈증</t>
+  </si>
+  <si>
+    <t>기타 고지질혈증</t>
+  </si>
+  <si>
+    <t>상세불명의 고지질혈증</t>
+  </si>
+  <si>
+    <t>순수 고글리세리드혈증</t>
+  </si>
+  <si>
+    <t>혼합성 고지질혈증</t>
+  </si>
+  <si>
+    <t>만성 신장질환 3기</t>
+  </si>
+  <si>
+    <t>만성 신장질환 4기</t>
+  </si>
+  <si>
+    <t>만성 신장질환 5기</t>
+  </si>
+  <si>
+    <t>만성 신장질환 1기</t>
+  </si>
+  <si>
+    <t>만성 신장질환 2기</t>
+  </si>
+  <si>
+    <t>상세불명의 만성 신장질환</t>
+  </si>
+  <si>
+    <t>상세불명의 신장기능상실</t>
+  </si>
+  <si>
+    <t>2형 당뇨병 · 신장 합병증 동반</t>
+  </si>
+  <si>
+    <t>상세불명 당뇨병 · 신장 합병증 동반</t>
+  </si>
+  <si>
+    <t>고혈압성 신장질환</t>
+  </si>
+  <si>
+    <t>고혈압성 심장 및 신장질환</t>
+  </si>
+  <si>
+    <t>급성 심근경색증</t>
+  </si>
+  <si>
+    <t>뇌경색증</t>
+  </si>
+  <si>
+    <t>출혈 또는 경색으로 명시되지 않은 뇌졸중</t>
+  </si>
+  <si>
+    <t>뇌혈관질환의 후유증</t>
+  </si>
+  <si>
+    <t>진구성 심근경색증</t>
+  </si>
+  <si>
+    <t>협심증</t>
+  </si>
+  <si>
+    <t>후속 심근경색증</t>
+  </si>
+  <si>
+    <t>급성 심근경색증 후 특정 현존 합병증</t>
+  </si>
+  <si>
+    <t>기타 급성 허혈성 심장질환</t>
+  </si>
+  <si>
+    <t>만성 허혈성 심장질환</t>
+  </si>
+  <si>
+    <t>달리 분류되지 않은 지방간</t>
+  </si>
+  <si>
+    <t>기타 명시된 염증성 간질환 — 비알코올성 지방간염 포함</t>
+  </si>
+  <si>
+    <t>알코올성 지방간</t>
+  </si>
+  <si>
+    <t>임신 · 출산 및 산후기 (O00~O99)</t>
+  </si>
+  <si>
+    <t>임신 확인됨</t>
+  </si>
+  <si>
+    <t>우연히 발견된 임신 상태</t>
+  </si>
+  <si>
+    <t>정상 임신의 관리</t>
+  </si>
+  <si>
+    <t>고위험 임신의 관리</t>
+  </si>
+  <si>
+    <t>산후 관리 및 검사</t>
+  </si>
+  <si>
+    <t>신경성 식욕부진</t>
+  </si>
+  <si>
+    <t>비정형 신경성 식욕부진</t>
+  </si>
+  <si>
+    <t>신경성 폭식증</t>
+  </si>
+  <si>
+    <t>비정형 신경성 폭식증</t>
+  </si>
+  <si>
+    <t>기타 섭식장애</t>
+  </si>
+  <si>
+    <t>상세불명의 섭식장애</t>
+  </si>
+  <si>
+    <t>영양실조 (E40~E46)</t>
+  </si>
+  <si>
+    <t>비정상적 체중감소</t>
+  </si>
+  <si>
+    <t>악성 신생물 (C00~C97)</t>
+  </si>
+  <si>
+    <t>위 부분의 후천성 결손</t>
+  </si>
+  <si>
+    <t>장관우회 및 문합 상태</t>
+  </si>
+  <si>
+    <t>위수술후증후군</t>
+  </si>
+  <si>
+    <t>투석간호</t>
+  </si>
+  <si>
+    <t>신장투석에 의존</t>
+  </si>
+  <si>
+    <t>신장이식 상태</t>
+  </si>
+  <si>
+    <t>연하곤란</t>
+  </si>
+  <si>
+    <t>그 코드가 무엇인지 사람이 읽기 위한 것. 판정에 쓰지 않는다. ICD-10 기준 표기이며 실제 KCD 마스터의 공식 명칭·5단위 세분류와 대조해야 한다</t>
   </si>
 </sst>
 </file>
@@ -4245,7 +4419,7 @@
     </row>
     <row r="2" spans="1:3" ht="25.4" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -4271,7 +4445,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1219</v>
+        <v>1214</v>
       </c>
       <c r="C5" s="1">
         <v>171</v>
@@ -4282,7 +4456,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="C6" s="1">
         <v>8</v>
@@ -4290,10 +4464,10 @@
     </row>
     <row r="7" spans="1:3" ht="25.4" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>1221</v>
+        <v>1216</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="C7" s="1">
         <v>14</v>
@@ -4301,13 +4475,13 @@
     </row>
     <row r="8" spans="1:3" ht="25.4" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="C8" s="1">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="25.4" customHeight="1">
@@ -4324,10 +4498,10 @@
     </row>
     <row r="10" spans="1:3" ht="25.4" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>1224</v>
+        <v>1219</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1225</v>
+        <v>1220</v>
       </c>
       <c r="C10" s="11">
         <v>42</v>
@@ -4340,7 +4514,7 @@
     </row>
     <row r="12" spans="1:3" ht="25.4" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -4350,7 +4524,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C13" s="1">
         <v>171</v>
@@ -4409,7 +4583,7 @@
     </row>
     <row r="21" spans="1:3" ht="25.4" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -4738,7 +4912,7 @@
         <v>86</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C53" s="4"/>
     </row>
@@ -4802,7 +4976,7 @@
         <v>50</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="M1" s="6" t="s">
         <v>53</v>
@@ -4860,7 +5034,7 @@
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>98</v>
@@ -4918,7 +5092,7 @@
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>98</v>
@@ -4974,7 +5148,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>98</v>
@@ -5084,7 +5258,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>118</v>
@@ -5140,7 +5314,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>118</v>
@@ -5306,7 +5480,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>133</v>
@@ -5362,7 +5536,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>138</v>
@@ -5420,7 +5594,7 @@
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>143</v>
@@ -5476,7 +5650,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>138</v>
@@ -5532,7 +5706,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>138</v>
@@ -5858,7 +6032,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>166</v>
@@ -5914,7 +6088,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>118</v>
@@ -5970,7 +6144,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>118</v>
@@ -6026,7 +6200,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>118</v>
@@ -6082,7 +6256,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>98</v>
@@ -6248,7 +6422,7 @@
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>98</v>
@@ -6304,7 +6478,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>98</v>
@@ -6362,7 +6536,7 @@
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>98</v>
@@ -6586,7 +6760,7 @@
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>221</v>
@@ -6700,7 +6874,7 @@
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>98</v>
@@ -6758,7 +6932,7 @@
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>98</v>
@@ -6872,7 +7046,7 @@
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>118</v>
@@ -6930,7 +7104,7 @@
       </c>
       <c r="K39" s="1"/>
       <c r="L39" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>118</v>
@@ -6988,7 +7162,7 @@
       </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>118</v>
@@ -7158,7 +7332,7 @@
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>138</v>
@@ -7272,7 +7446,7 @@
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>143</v>
@@ -7330,7 +7504,7 @@
       </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>138</v>
@@ -7444,7 +7618,7 @@
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>143</v>
@@ -7502,7 +7676,7 @@
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>143</v>
@@ -7616,7 +7790,7 @@
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>138</v>
@@ -7730,7 +7904,7 @@
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>118</v>
@@ -7788,7 +7962,7 @@
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>221</v>
@@ -7902,7 +8076,7 @@
       </c>
       <c r="K56" s="1"/>
       <c r="L56" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>118</v>
@@ -8128,7 +8302,7 @@
       </c>
       <c r="K60" s="1"/>
       <c r="L60" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M60" s="1" t="s">
         <v>143</v>
@@ -8242,7 +8416,7 @@
       </c>
       <c r="K62" s="1"/>
       <c r="L62" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="M62" s="1" t="s">
         <v>98</v>
@@ -8300,7 +8474,7 @@
       </c>
       <c r="K63" s="1"/>
       <c r="L63" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M63" s="1" t="s">
         <v>221</v>
@@ -8358,7 +8532,7 @@
       </c>
       <c r="K64" s="1"/>
       <c r="L64" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M64" s="1" t="s">
         <v>138</v>
@@ -8416,7 +8590,7 @@
       </c>
       <c r="K65" s="1"/>
       <c r="L65" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M65" s="1" t="s">
         <v>98</v>
@@ -8474,7 +8648,7 @@
       </c>
       <c r="K66" s="1"/>
       <c r="L66" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M66" s="1" t="s">
         <v>98</v>
@@ -8532,7 +8706,7 @@
       </c>
       <c r="K67" s="1"/>
       <c r="L67" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M67" s="1" t="s">
         <v>98</v>
@@ -8646,7 +8820,7 @@
       </c>
       <c r="K69" s="1"/>
       <c r="L69" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M69" s="1" t="s">
         <v>98</v>
@@ -8704,7 +8878,7 @@
       </c>
       <c r="K70" s="1"/>
       <c r="L70" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M70" s="1" t="s">
         <v>118</v>
@@ -8818,7 +8992,7 @@
       </c>
       <c r="K72" s="1"/>
       <c r="L72" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M72" s="1" t="s">
         <v>118</v>
@@ -8876,7 +9050,7 @@
       </c>
       <c r="K73" s="1"/>
       <c r="L73" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M73" s="1" t="s">
         <v>194</v>
@@ -8990,7 +9164,7 @@
       </c>
       <c r="K75" s="1"/>
       <c r="L75" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>133</v>
@@ -9048,7 +9222,7 @@
       </c>
       <c r="K76" s="1"/>
       <c r="L76" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>133</v>
@@ -9106,7 +9280,7 @@
       </c>
       <c r="K77" s="1"/>
       <c r="L77" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M77" s="1" t="s">
         <v>98</v>
@@ -9164,7 +9338,7 @@
       </c>
       <c r="K78" s="1"/>
       <c r="L78" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M78" s="1" t="s">
         <v>143</v>
@@ -9222,7 +9396,7 @@
       </c>
       <c r="K79" s="1"/>
       <c r="L79" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M79" s="1" t="s">
         <v>98</v>
@@ -9280,7 +9454,7 @@
       </c>
       <c r="K80" s="1"/>
       <c r="L80" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M80" s="1" t="s">
         <v>98</v>
@@ -9338,7 +9512,7 @@
       </c>
       <c r="K81" s="1"/>
       <c r="L81" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M81" s="1" t="s">
         <v>98</v>
@@ -9452,7 +9626,7 @@
       </c>
       <c r="K83" s="1"/>
       <c r="L83" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M83" s="1" t="s">
         <v>143</v>
@@ -9510,7 +9684,7 @@
       </c>
       <c r="K84" s="1"/>
       <c r="L84" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M84" s="1" t="s">
         <v>143</v>
@@ -9624,7 +9798,7 @@
       </c>
       <c r="K86" s="1"/>
       <c r="L86" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="M86" s="1" t="s">
         <v>391</v>
@@ -9682,7 +9856,7 @@
       </c>
       <c r="K87" s="1"/>
       <c r="L87" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M87" s="1" t="s">
         <v>396</v>
@@ -9740,7 +9914,7 @@
       </c>
       <c r="K88" s="1"/>
       <c r="L88" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M88" s="1" t="s">
         <v>396</v>
@@ -9798,7 +9972,7 @@
       </c>
       <c r="K89" s="1"/>
       <c r="L89" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M89" s="1" t="s">
         <v>166</v>
@@ -9856,7 +10030,7 @@
       </c>
       <c r="K90" s="1"/>
       <c r="L90" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M90" s="1" t="s">
         <v>166</v>
@@ -9914,7 +10088,7 @@
       </c>
       <c r="K91" s="1"/>
       <c r="L91" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M91" s="1" t="s">
         <v>118</v>
@@ -9972,7 +10146,7 @@
       </c>
       <c r="K92" s="1"/>
       <c r="L92" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M92" s="1" t="s">
         <v>118</v>
@@ -10086,7 +10260,7 @@
       </c>
       <c r="K94" s="1"/>
       <c r="L94" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M94" s="1" t="s">
         <v>118</v>
@@ -10424,7 +10598,7 @@
       </c>
       <c r="K100" s="1"/>
       <c r="L100" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M100" s="1" t="s">
         <v>98</v>
@@ -10482,7 +10656,7 @@
       </c>
       <c r="K101" s="1"/>
       <c r="L101" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M101" s="1" t="s">
         <v>98</v>
@@ -10652,7 +10826,7 @@
       </c>
       <c r="K104" s="1"/>
       <c r="L104" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M104" s="1" t="s">
         <v>118</v>
@@ -10766,7 +10940,7 @@
       </c>
       <c r="K106" s="1"/>
       <c r="L106" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M106" s="1" t="s">
         <v>118</v>
@@ -10824,7 +10998,7 @@
       </c>
       <c r="K107" s="1"/>
       <c r="L107" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M107" s="1" t="s">
         <v>118</v>
@@ -10938,7 +11112,7 @@
       </c>
       <c r="K109" s="1"/>
       <c r="L109" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M109" s="1" t="s">
         <v>133</v>
@@ -10996,7 +11170,7 @@
       </c>
       <c r="K110" s="1"/>
       <c r="L110" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="M110" s="1" t="s">
         <v>98</v>
@@ -11110,7 +11284,7 @@
       </c>
       <c r="K112" s="1"/>
       <c r="L112" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M112" s="1" t="s">
         <v>133</v>
@@ -11168,7 +11342,7 @@
       </c>
       <c r="K113" s="1"/>
       <c r="L113" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>138</v>
@@ -11226,7 +11400,7 @@
       </c>
       <c r="K114" s="1"/>
       <c r="L114" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="M114" s="1" t="s">
         <v>143</v>
@@ -11396,7 +11570,7 @@
       </c>
       <c r="K117" s="1"/>
       <c r="L117" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>98</v>
@@ -11510,7 +11684,7 @@
       </c>
       <c r="K119" s="1"/>
       <c r="L119" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="M119" s="1" t="s">
         <v>143</v>
@@ -11568,7 +11742,7 @@
       </c>
       <c r="K120" s="1"/>
       <c r="L120" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="M120" s="1" t="s">
         <v>138</v>
@@ -11626,7 +11800,7 @@
       </c>
       <c r="K121" s="1"/>
       <c r="L121" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="M121" s="1" t="s">
         <v>396</v>
@@ -11852,7 +12026,7 @@
       </c>
       <c r="K125" s="1"/>
       <c r="L125" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M125" s="1" t="s">
         <v>396</v>
@@ -11910,7 +12084,7 @@
       </c>
       <c r="K126" s="1"/>
       <c r="L126" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M126" s="1" t="s">
         <v>166</v>
@@ -11968,7 +12142,7 @@
       </c>
       <c r="K127" s="1"/>
       <c r="L127" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M127" s="1" t="s">
         <v>118</v>
@@ -12026,7 +12200,7 @@
       </c>
       <c r="K128" s="1"/>
       <c r="L128" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M128" s="1" t="s">
         <v>118</v>
@@ -12140,7 +12314,7 @@
       </c>
       <c r="K130" s="1"/>
       <c r="L130" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M130" s="1" t="s">
         <v>118</v>
@@ -12198,7 +12372,7 @@
       </c>
       <c r="K131" s="1"/>
       <c r="L131" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M131" s="1" t="s">
         <v>118</v>
@@ -12312,7 +12486,7 @@
       </c>
       <c r="K133" s="1"/>
       <c r="L133" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M133" s="1" t="s">
         <v>98</v>
@@ -12426,7 +12600,7 @@
       </c>
       <c r="K135" s="1"/>
       <c r="L135" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M135" s="1" t="s">
         <v>98</v>
@@ -12540,7 +12714,7 @@
       </c>
       <c r="K137" s="1"/>
       <c r="L137" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M137" s="1" t="s">
         <v>98</v>
@@ -12598,7 +12772,7 @@
       </c>
       <c r="K138" s="1"/>
       <c r="L138" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M138" s="1" t="s">
         <v>98</v>
@@ -12656,7 +12830,7 @@
       </c>
       <c r="K139" s="1"/>
       <c r="L139" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M139" s="1" t="s">
         <v>118</v>
@@ -12714,7 +12888,7 @@
       </c>
       <c r="K140" s="1"/>
       <c r="L140" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M140" s="1" t="s">
         <v>138</v>
@@ -12772,7 +12946,7 @@
       </c>
       <c r="K141" s="1"/>
       <c r="L141" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="M141" s="1" t="s">
         <v>166</v>
@@ -12886,7 +13060,7 @@
       </c>
       <c r="K143" s="1"/>
       <c r="L143" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M143" s="1" t="s">
         <v>118</v>
@@ -12944,7 +13118,7 @@
       </c>
       <c r="K144" s="1"/>
       <c r="L144" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="M144" s="1" t="s">
         <v>118</v>
@@ -13114,7 +13288,7 @@
       </c>
       <c r="K147" s="1"/>
       <c r="L147" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M147" s="1" t="s">
         <v>396</v>
@@ -13172,7 +13346,7 @@
       </c>
       <c r="K148" s="1"/>
       <c r="L148" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M148" s="1" t="s">
         <v>118</v>
@@ -13230,7 +13404,7 @@
       </c>
       <c r="K149" s="1"/>
       <c r="L149" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M149" s="1" t="s">
         <v>118</v>
@@ -13288,7 +13462,7 @@
       </c>
       <c r="K150" s="1"/>
       <c r="L150" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M150" s="1" t="s">
         <v>118</v>
@@ -13346,7 +13520,7 @@
       </c>
       <c r="K151" s="1"/>
       <c r="L151" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M151" s="1" t="s">
         <v>118</v>
@@ -13404,7 +13578,7 @@
       </c>
       <c r="K152" s="1"/>
       <c r="L152" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="M152" s="1" t="s">
         <v>138</v>
@@ -13518,7 +13692,7 @@
       </c>
       <c r="K154" s="1"/>
       <c r="L154" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M154" s="1" t="s">
         <v>118</v>
@@ -13576,7 +13750,7 @@
       </c>
       <c r="K155" s="1"/>
       <c r="L155" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M155" s="1" t="s">
         <v>143</v>
@@ -13690,7 +13864,7 @@
       </c>
       <c r="K157" s="1"/>
       <c r="L157" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="M157" s="1" t="s">
         <v>138</v>
@@ -13804,7 +13978,7 @@
       </c>
       <c r="K159" s="1"/>
       <c r="L159" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M159" s="1" t="s">
         <v>133</v>
@@ -13918,7 +14092,7 @@
       </c>
       <c r="K161" s="1"/>
       <c r="L161" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M161" s="1" t="s">
         <v>133</v>
@@ -13976,7 +14150,7 @@
       </c>
       <c r="K162" s="1"/>
       <c r="L162" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M162" s="1" t="s">
         <v>143</v>
@@ -14132,13 +14306,13 @@
         <v>94</v>
       </c>
       <c r="G165" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="H165">
         <v>17</v>
       </c>
       <c r="I165" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="J165" t="s">
         <v>125</v>
@@ -14150,13 +14324,13 @@
         <v>99</v>
       </c>
       <c r="O165" t="s">
+        <v>942</v>
+      </c>
+      <c r="P165" t="s">
+        <v>943</v>
+      </c>
+      <c r="Q165" t="s">
         <v>944</v>
-      </c>
-      <c r="P165" t="s">
-        <v>945</v>
-      </c>
-      <c r="Q165" t="s">
-        <v>946</v>
       </c>
       <c r="R165" t="s">
         <v>103</v>
@@ -14185,13 +14359,13 @@
         <v>104</v>
       </c>
       <c r="G166" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="H166">
         <v>14</v>
       </c>
       <c r="I166" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="J166" t="s">
         <v>125</v>
@@ -14203,13 +14377,13 @@
         <v>99</v>
       </c>
       <c r="O166" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="P166" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="Q166" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="R166" t="s">
         <v>103</v>
@@ -14238,13 +14412,13 @@
         <v>94</v>
       </c>
       <c r="G167" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="H167">
         <v>14</v>
       </c>
       <c r="I167" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="J167" t="s">
         <v>125</v>
@@ -14256,13 +14430,13 @@
         <v>99</v>
       </c>
       <c r="O167" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="P167" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="Q167" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="R167" t="s">
         <v>103</v>
@@ -14291,13 +14465,13 @@
         <v>104</v>
       </c>
       <c r="G168" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H168">
         <v>14</v>
       </c>
       <c r="I168" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="J168" t="s">
         <v>125</v>
@@ -14309,13 +14483,13 @@
         <v>99</v>
       </c>
       <c r="O168" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="P168" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="Q168" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="R168" t="s">
         <v>103</v>
@@ -14344,13 +14518,13 @@
         <v>94</v>
       </c>
       <c r="G169" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="H169">
         <v>14</v>
       </c>
       <c r="I169" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="J169" t="s">
         <v>125</v>
@@ -14362,13 +14536,13 @@
         <v>99</v>
       </c>
       <c r="O169" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="P169" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="Q169" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="R169" t="s">
         <v>103</v>
@@ -14397,13 +14571,13 @@
         <v>104</v>
       </c>
       <c r="G170" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="H170">
         <v>15</v>
       </c>
       <c r="I170" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="J170" t="s">
         <v>125</v>
@@ -14415,13 +14589,13 @@
         <v>99</v>
       </c>
       <c r="O170" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="P170" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="Q170" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="R170" t="s">
         <v>103</v>
@@ -14450,13 +14624,13 @@
         <v>94</v>
       </c>
       <c r="G171" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="H171">
         <v>18</v>
       </c>
       <c r="I171" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="J171" t="s">
         <v>125</v>
@@ -14468,13 +14642,13 @@
         <v>99</v>
       </c>
       <c r="O171" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="P171" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="Q171" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="R171" t="s">
         <v>103</v>
@@ -14494,22 +14668,22 @@
         <v>9</v>
       </c>
       <c r="D172" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="E172" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="F172" t="s">
         <v>199</v>
       </c>
       <c r="G172" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="H172">
         <v>20</v>
       </c>
       <c r="I172" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="J172" t="s">
         <v>125</v>
@@ -14521,13 +14695,13 @@
         <v>99</v>
       </c>
       <c r="O172" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="P172" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="Q172" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="R172" t="s">
         <v>103</v>
@@ -15102,152 +15276,152 @@
         <v>30</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>78</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>756</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="32">
       <c r="A4" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="32">
       <c r="A5" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>970</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>971</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="32">
       <c r="A6" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="C6" s="1">
         <v>28</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="32">
       <c r="A7" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="48">
       <c r="A8" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="32">
       <c r="A9" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C9" s="1">
         <v>84</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -15255,16 +15429,16 @@
         <v>36</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>763</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>764</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="66" customHeight="1">
@@ -15272,452 +15446,452 @@
         <v>36</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>767</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="66" customHeight="1">
       <c r="A12" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>772</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="66" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>775</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>777</v>
       </c>
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:5" ht="66" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="1" t="s">
         <v>779</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="66" customHeight="1">
       <c r="A15" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>785</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="66" customHeight="1">
       <c r="A16" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>788</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>790</v>
       </c>
       <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:5" ht="66" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>791</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>793</v>
       </c>
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:5" ht="66" customHeight="1">
       <c r="A18" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>796</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="66" customHeight="1">
       <c r="A19" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>801</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>802</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="66" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>804</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>805</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>802</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="66" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>808</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>809</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="66" customHeight="1">
       <c r="A22" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>813</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="66" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>816</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>817</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="66" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>820</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="66" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>824</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>825</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="66" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>827</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>828</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>825</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="66" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>830</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>831</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>825</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="66" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>833</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>834</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>825</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="66" customHeight="1">
       <c r="A29" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>838</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>839</v>
-      </c>
       <c r="E29" s="1" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="66" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>841</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>842</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="66" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>845</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>846</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="66" customHeight="1">
       <c r="A32" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>850</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>851</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="66" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>854</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>855</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="66" customHeight="1">
       <c r="A34" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>857</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>859</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>860</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="66" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>863</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>864</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="66" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>867</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>868</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="66" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>870</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>871</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>872</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="66" customHeight="1">
@@ -15725,16 +15899,16 @@
         <v>641</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>874</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="E38" s="4" t="s">
         <v>875</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>876</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="66" customHeight="1">
@@ -15742,16 +15916,16 @@
         <v>641</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C39" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="66" customHeight="1">
@@ -15759,16 +15933,16 @@
         <v>641</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C40" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="66" customHeight="1">
@@ -15776,67 +15950,67 @@
         <v>641</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>877</v>
+      </c>
+      <c r="E41" s="4" t="s">
         <v>883</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>884</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>879</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="66" customHeight="1">
       <c r="A42" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>886</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="D42" s="4" t="s">
         <v>887</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="E42" s="4" t="s">
         <v>888</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>889</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="66" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>891</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="E43" s="4" t="s">
         <v>892</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>893</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="66" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>895</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="E44" s="4" t="s">
         <v>896</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>897</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="66" customHeight="1">
@@ -15844,191 +16018,191 @@
         <v>36</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C45" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="66" customHeight="1">
       <c r="A46" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>902</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="D46" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>903</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>904</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>893</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="66" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>906</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="E47" s="4" t="s">
         <v>907</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>908</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="66" customHeight="1">
       <c r="A48" s="4" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C48" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="66" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>103</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="66" customHeight="1">
       <c r="A50" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>916</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="D50" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="E50" s="4" t="s">
         <v>917</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>918</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>799</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="66" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B51" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>920</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>921</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>754</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="66" customHeight="1">
       <c r="A52" s="4" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B52" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>923</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="E52" s="4" t="s">
         <v>924</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>925</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="66" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>927</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="E53" s="4" t="s">
         <v>928</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>929</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="66" customHeight="1">
       <c r="A54" s="4" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>931</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="E54" s="4" t="s">
         <v>932</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>933</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="66" customHeight="1">
       <c r="A55" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>935</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="D55" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>936</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>937</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>893</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="66" customHeight="1">
       <c r="A56" s="4" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>82</v>
@@ -16037,10 +16211,10 @@
         <v>1</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
   </sheetData>
@@ -16070,34 +16244,34 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="10" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>725</v>
       </c>
       <c r="C1" s="10" t="s">
+        <v>994</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>995</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>996</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>997</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>998</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>999</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>727</v>
       </c>
       <c r="H1" s="10" t="s">
+        <v>998</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>999</v>
+      </c>
+      <c r="J1" s="10" t="s">
         <v>1000</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>1001</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>1002</v>
       </c>
       <c r="K1" s="10" t="s">
         <v>53</v>
@@ -16106,12 +16280,12 @@
         <v>728</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B2" t="s">
         <v>729</v>
@@ -16120,39 +16294,39 @@
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="E2" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="F2" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="G2" t="s">
         <v>729</v>
       </c>
       <c r="H2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="J2" t="s">
         <v>1006</v>
-      </c>
-      <c r="I2" t="s">
-        <v>1007</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1008</v>
       </c>
       <c r="K2" t="s">
         <v>730</v>
       </c>
       <c r="L2" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="M2" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B3" t="s">
         <v>731</v>
@@ -16161,33 +16335,33 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="E3" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="F3" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="G3" t="s">
         <v>731</v>
       </c>
       <c r="H3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="K3" t="s">
         <v>732</v>
       </c>
       <c r="L3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="M3" t="s">
-        <v>1230</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="B4" t="s">
         <v>733</v>
@@ -16196,68 +16370,68 @@
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="E4" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="F4" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="G4" t="s">
         <v>734</v>
       </c>
       <c r="H4" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="K4" t="s">
         <v>735</v>
       </c>
       <c r="L4" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="M4" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="B5" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C5" t="s">
         <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="E5" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="F5" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="G5" t="s">
         <v>734</v>
       </c>
       <c r="H5" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="K5" t="s">
         <v>735</v>
       </c>
       <c r="L5" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="M5" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B6" t="s">
         <v>736</v>
@@ -16266,352 +16440,352 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="E6" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="F6" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="G6" t="s">
-        <v>737</v>
+        <v>1230</v>
       </c>
       <c r="H6" t="s">
         <v>695</v>
       </c>
       <c r="I6" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="J6" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="K6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="L6" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="M6" t="s">
-        <v>1231</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B7" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="E7" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="F7" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="G7" t="s">
+        <v>739</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I7" t="s">
+        <v>990</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1024</v>
+      </c>
+      <c r="K7" t="s">
         <v>740</v>
       </c>
-      <c r="H7" t="s">
+      <c r="L7" t="s">
+        <v>1007</v>
+      </c>
+      <c r="M7" t="s">
         <v>1025</v>
-      </c>
-      <c r="I7" t="s">
-        <v>992</v>
-      </c>
-      <c r="J7" t="s">
-        <v>1026</v>
-      </c>
-      <c r="K7" t="s">
-        <v>741</v>
-      </c>
-      <c r="L7" t="s">
-        <v>1009</v>
-      </c>
-      <c r="M7" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B8" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="E8" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="F8" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="G8" t="s">
+        <v>741</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1027</v>
+      </c>
+      <c r="K8" t="s">
         <v>742</v>
       </c>
-      <c r="H8" t="s">
-        <v>1029</v>
-      </c>
-      <c r="K8" t="s">
-        <v>743</v>
-      </c>
       <c r="L8" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="M8" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="B9" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="E9" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="F9" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="I9" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1031</v>
+      </c>
+      <c r="K9" t="s">
         <v>1032</v>
       </c>
-      <c r="J9" t="s">
+      <c r="L9" t="s">
+        <v>1007</v>
+      </c>
+      <c r="M9" t="s">
         <v>1033</v>
-      </c>
-      <c r="K9" t="s">
-        <v>1034</v>
-      </c>
-      <c r="L9" t="s">
-        <v>1009</v>
-      </c>
-      <c r="M9" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="E10" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="F10" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="I10" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1031</v>
+      </c>
+      <c r="K10" t="s">
         <v>1032</v>
       </c>
-      <c r="J10" t="s">
-        <v>1033</v>
-      </c>
-      <c r="K10" t="s">
-        <v>1034</v>
-      </c>
       <c r="L10" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="M10" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B11" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C11" t="s">
         <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="E11" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="F11" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="I11" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J11" t="s">
+        <v>1031</v>
+      </c>
+      <c r="K11" t="s">
         <v>1032</v>
       </c>
-      <c r="J11" t="s">
-        <v>1033</v>
-      </c>
-      <c r="K11" t="s">
-        <v>1034</v>
-      </c>
       <c r="L11" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="M11" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B12" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="E12" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="F12" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="I12" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J12" t="s">
+        <v>1031</v>
+      </c>
+      <c r="K12" t="s">
         <v>1032</v>
       </c>
-      <c r="J12" t="s">
-        <v>1033</v>
-      </c>
-      <c r="K12" t="s">
-        <v>1034</v>
-      </c>
       <c r="L12" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="M12" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B13" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="E13" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="F13" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="I13" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J13" t="s">
+        <v>1031</v>
+      </c>
+      <c r="K13" t="s">
         <v>1032</v>
       </c>
-      <c r="J13" t="s">
-        <v>1033</v>
-      </c>
-      <c r="K13" t="s">
-        <v>1034</v>
-      </c>
       <c r="L13" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="M13" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B14" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C14" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
       <c r="D14" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="E14" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="F14" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="I14" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="J14" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="K14" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="L14" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="M14" t="s">
-        <v>1235</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B15" t="s">
-        <v>749</v>
+        <v>1231</v>
       </c>
       <c r="C15" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1010</v>
+      </c>
+      <c r="I15" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J15" t="s">
         <v>1232</v>
       </c>
-      <c r="D15" t="s">
-        <v>1012</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1005</v>
-      </c>
-      <c r="F15" t="s">
-        <v>1012</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="K15" t="s">
         <v>1032</v>
       </c>
-      <c r="J15" t="s">
-        <v>1033</v>
-      </c>
-      <c r="K15" t="s">
-        <v>1034</v>
-      </c>
       <c r="L15" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="M15" t="s">
         <v>1233</v>
@@ -16626,1384 +16800,1549 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84C9ADE8-E8E1-442A-91BD-AA392C318296}">
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="7.58203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.4140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="52.58203125" customWidth="1"/>
+    <col min="3" max="3" width="46.58203125" customWidth="1"/>
+    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.4140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="52.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="10" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>726</v>
       </c>
       <c r="C1" s="10" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>1045</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>1046</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>1047</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>1048</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="J1" s="10" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B2" t="s">
         <v>1049</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="C2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D2" t="s">
         <v>1050</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="F2">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2" t="s">
         <v>1003</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="J2" t="s">
         <v>1051</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B3" t="s">
         <v>1052</v>
       </c>
-      <c r="E2">
+      <c r="C3" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F3">
         <v>12</v>
       </c>
-      <c r="F2">
+      <c r="G3">
         <v>2</v>
       </c>
-      <c r="G2" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="H3" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B4" t="s">
         <v>1053</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C4" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F4">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B5" t="s">
         <v>1054</v>
       </c>
-      <c r="C3" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E3">
+      <c r="C5" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F5">
         <v>12</v>
       </c>
-      <c r="F3">
+      <c r="G5">
         <v>2</v>
       </c>
-      <c r="G3" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="H5" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J5" t="s">
         <v>1055</v>
       </c>
-      <c r="C4" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E4">
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F6">
         <v>12</v>
       </c>
-      <c r="F4">
+      <c r="G6">
         <v>2</v>
       </c>
-      <c r="G4" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E5">
+      <c r="H6" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F7">
         <v>12</v>
       </c>
-      <c r="F5">
+      <c r="G7">
         <v>2</v>
       </c>
-      <c r="G5" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I5" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="H7" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F8">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F9">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F10">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F11">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J11" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F12">
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J12" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F13">
+        <v>12</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J13" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F14">
+        <v>12</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J14" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F15">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F16">
+        <v>12</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F17">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F18">
+        <v>12</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F19">
+        <v>12</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F20">
+        <v>12</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F21">
+        <v>12</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J21" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F22">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B23" t="s">
         <v>1058</v>
       </c>
-      <c r="C6" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E6">
+      <c r="C23" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F23">
         <v>12</v>
       </c>
-      <c r="F6">
+      <c r="G23">
         <v>2</v>
       </c>
-      <c r="G6" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="H23" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J23" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B24" t="s">
         <v>1059</v>
       </c>
-      <c r="C7" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E7">
+      <c r="C24" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F24">
         <v>12</v>
       </c>
-      <c r="F7">
+      <c r="G24">
         <v>2</v>
       </c>
-      <c r="G7" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="H24" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J24" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F25">
+        <v>12</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J25" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F26">
+        <v>12</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J26" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F27">
+        <v>12</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J27" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F28">
+        <v>12</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J28" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D29" t="s">
         <v>1062</v>
       </c>
-      <c r="C8" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E8">
+      <c r="F29">
         <v>12</v>
       </c>
-      <c r="F8">
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J29" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F30">
+        <v>12</v>
+      </c>
+      <c r="G30">
         <v>2</v>
       </c>
-      <c r="G8" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1063</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E9">
+      <c r="H30" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F31">
         <v>12</v>
       </c>
-      <c r="F9">
+      <c r="G31">
         <v>2</v>
       </c>
-      <c r="G9" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E10">
+      <c r="H31" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F32">
         <v>12</v>
       </c>
-      <c r="F10">
+      <c r="G32">
         <v>2</v>
       </c>
-      <c r="G10" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E11">
+      <c r="H32" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F33">
         <v>12</v>
       </c>
-      <c r="F11">
+      <c r="G33">
         <v>2</v>
       </c>
-      <c r="G11" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I11" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E12">
+      <c r="H33" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F34">
         <v>12</v>
       </c>
-      <c r="F12">
+      <c r="G34">
         <v>2</v>
       </c>
-      <c r="G12" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I12" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1070</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E13">
+      <c r="H34" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J34" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F35">
         <v>12</v>
       </c>
-      <c r="F13">
+      <c r="G35">
         <v>2</v>
       </c>
-      <c r="G13" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I13" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1071</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E14">
+      <c r="H35" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J35" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F36">
         <v>12</v>
       </c>
-      <c r="F14">
+      <c r="G36">
+        <v>2</v>
+      </c>
+      <c r="H36" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J36" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F37">
+        <v>12</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+      <c r="H37" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F38">
+        <v>12</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+      <c r="H38" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F39">
+        <v>10</v>
+      </c>
+      <c r="G39">
         <v>1</v>
       </c>
-      <c r="G14" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I14" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1073</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E15">
+      <c r="H39" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J39" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F40">
+        <v>10</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J40" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D41" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F41">
+        <v>10</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J41" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F42">
+        <v>10</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F43">
+        <v>10</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F44">
         <v>12</v>
       </c>
-      <c r="F15">
+      <c r="G44">
         <v>1</v>
       </c>
-      <c r="G15" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E16">
+      <c r="H44" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J44" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F45">
+        <v>24</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D46" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F46">
+        <v>24</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D47" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F47">
+        <v>24</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F48">
+        <v>24</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D49" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F49">
+        <v>24</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F50">
+        <v>24</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E51" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F51">
         <v>12</v>
       </c>
-      <c r="F16">
+      <c r="G51">
         <v>1</v>
       </c>
-      <c r="G16" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E17">
+      <c r="H51" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J51" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F52">
         <v>12</v>
       </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
-      <c r="G17" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E18">
+      <c r="G52">
+        <v>1</v>
+      </c>
+      <c r="H52" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J52" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F53">
         <v>12</v>
       </c>
-      <c r="F18">
-        <v>2</v>
-      </c>
-      <c r="G18" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E19">
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J53" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F54">
         <v>12</v>
       </c>
-      <c r="F19">
-        <v>2</v>
-      </c>
-      <c r="G19" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E20">
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J54" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E55" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F55">
+        <v>6</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55" t="s">
+        <v>1010</v>
+      </c>
+      <c r="I55" t="s">
+        <v>1129</v>
+      </c>
+      <c r="J55" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D56" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J56" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D57" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J57" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D58" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J58" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D59" t="s">
+        <v>1050</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J59" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J60" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J61" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D62" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F62">
         <v>12</v>
       </c>
-      <c r="F20">
-        <v>2</v>
-      </c>
-      <c r="G20" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1079</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E21">
-        <v>12</v>
-      </c>
-      <c r="F21">
-        <v>2</v>
-      </c>
-      <c r="G21" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I21" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E22">
-        <v>12</v>
-      </c>
-      <c r="F22">
-        <v>2</v>
-      </c>
-      <c r="G22" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E23">
-        <v>12</v>
-      </c>
-      <c r="F23">
-        <v>2</v>
-      </c>
-      <c r="G23" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I23" t="s">
-        <v>1226</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E24">
-        <v>12</v>
-      </c>
-      <c r="F24">
-        <v>2</v>
-      </c>
-      <c r="G24" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I24" t="s">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E25">
-        <v>12</v>
-      </c>
-      <c r="F25">
+      <c r="G62">
         <v>1</v>
       </c>
-      <c r="G25" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I25" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C26" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E26">
-        <v>12</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I26" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E27">
-        <v>12</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I27" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C28" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E28">
-        <v>12</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I28" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B29" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C29" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E29">
-        <v>12</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I29" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E30">
-        <v>12</v>
-      </c>
-      <c r="F30">
-        <v>2</v>
-      </c>
-      <c r="G30" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B31" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C31" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E31">
-        <v>12</v>
-      </c>
-      <c r="F31">
-        <v>2</v>
-      </c>
-      <c r="G31" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C32" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E32">
-        <v>12</v>
-      </c>
-      <c r="F32">
-        <v>2</v>
-      </c>
-      <c r="G32" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B33" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C33" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E33">
-        <v>12</v>
-      </c>
-      <c r="F33">
-        <v>2</v>
-      </c>
-      <c r="G33" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E34">
-        <v>12</v>
-      </c>
-      <c r="F34">
-        <v>2</v>
-      </c>
-      <c r="G34" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I34" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E35">
-        <v>12</v>
-      </c>
-      <c r="F35">
-        <v>2</v>
-      </c>
-      <c r="G35" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I35" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1100</v>
-      </c>
-      <c r="C36" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E36">
-        <v>12</v>
-      </c>
-      <c r="F36">
-        <v>2</v>
-      </c>
-      <c r="G36" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I36" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1101</v>
-      </c>
-      <c r="C37" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E37">
-        <v>12</v>
-      </c>
-      <c r="F37">
-        <v>2</v>
-      </c>
-      <c r="G37" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B38" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C38" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E38">
-        <v>12</v>
-      </c>
-      <c r="F38">
-        <v>2</v>
-      </c>
-      <c r="G38" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1103</v>
-      </c>
-      <c r="C39" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D39" t="s">
-        <v>1105</v>
-      </c>
-      <c r="E39">
-        <v>10</v>
-      </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-      <c r="G39" t="s">
-        <v>1012</v>
-      </c>
-      <c r="I39" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B40" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C40" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E40">
-        <v>10</v>
-      </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
-      <c r="G40" t="s">
-        <v>1012</v>
-      </c>
-      <c r="I40" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B41" t="s">
-        <v>1109</v>
-      </c>
-      <c r="C41" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E41">
-        <v>10</v>
-      </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-      <c r="G41" t="s">
-        <v>1012</v>
-      </c>
-      <c r="I41" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C42" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E42">
-        <v>10</v>
-      </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-      <c r="G42" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C43" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E43">
-        <v>10</v>
-      </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="G43" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="A44" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B44" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C44" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E44">
-        <v>12</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-      <c r="G44" t="s">
-        <v>1012</v>
-      </c>
-      <c r="I44" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B45" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C45" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E45">
-        <v>24</v>
-      </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
-      <c r="G45" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B46" t="s">
-        <v>1115</v>
-      </c>
-      <c r="C46" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E46">
-        <v>24</v>
-      </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-      <c r="G46" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B47" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C47" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E47">
-        <v>24</v>
-      </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-      <c r="G47" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B48" t="s">
-        <v>1117</v>
-      </c>
-      <c r="C48" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E48">
-        <v>24</v>
-      </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
-      <c r="G48" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B49" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C49" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E49">
-        <v>24</v>
-      </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-      <c r="G49" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B50" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C50" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E50">
-        <v>24</v>
-      </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-      <c r="G50" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B51" t="s">
-        <v>1120</v>
-      </c>
-      <c r="C51" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D51" t="s">
-        <v>1121</v>
-      </c>
-      <c r="E51">
-        <v>12</v>
-      </c>
-      <c r="F51">
-        <v>1</v>
-      </c>
-      <c r="G51" t="s">
-        <v>1012</v>
-      </c>
-      <c r="I51" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B52" t="s">
-        <v>1123</v>
-      </c>
-      <c r="C52" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E52">
-        <v>12</v>
-      </c>
-      <c r="F52">
-        <v>1</v>
-      </c>
-      <c r="G52" t="s">
-        <v>1012</v>
-      </c>
-      <c r="I52" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B53" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C53" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E53">
-        <v>12</v>
-      </c>
-      <c r="F53">
-        <v>1</v>
-      </c>
-      <c r="G53" t="s">
-        <v>1012</v>
-      </c>
-      <c r="I53" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B54" t="s">
-        <v>1127</v>
-      </c>
-      <c r="C54" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E54">
-        <v>12</v>
-      </c>
-      <c r="F54">
-        <v>1</v>
-      </c>
-      <c r="G54" t="s">
-        <v>1012</v>
-      </c>
-      <c r="I54" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B55" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C55" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D55" t="s">
-        <v>1130</v>
-      </c>
-      <c r="E55">
-        <v>6</v>
-      </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
-      <c r="G55" t="s">
-        <v>1012</v>
-      </c>
-      <c r="H55" t="s">
-        <v>1131</v>
-      </c>
-      <c r="I55" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
-      <c r="A56" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B56" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C56" t="s">
-        <v>1064</v>
-      </c>
-      <c r="F56">
-        <v>1</v>
-      </c>
-      <c r="G56" t="s">
-        <v>1012</v>
-      </c>
-      <c r="I56" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
-      <c r="A57" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B57" t="s">
-        <v>1135</v>
-      </c>
-      <c r="C57" t="s">
-        <v>1064</v>
-      </c>
-      <c r="F57">
-        <v>1</v>
-      </c>
-      <c r="G57" t="s">
-        <v>1012</v>
-      </c>
-      <c r="I57" t="s">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
-      <c r="A58" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B58" t="s">
-        <v>1137</v>
-      </c>
-      <c r="C58" t="s">
-        <v>1064</v>
-      </c>
-      <c r="F58">
-        <v>1</v>
-      </c>
-      <c r="G58" t="s">
-        <v>1012</v>
-      </c>
-      <c r="I58" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
-      <c r="A59" t="s">
-        <v>1043</v>
-      </c>
-      <c r="B59" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C59" t="s">
-        <v>1052</v>
-      </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
-      <c r="G59" t="s">
-        <v>1012</v>
-      </c>
-      <c r="I59" t="s">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60" t="s">
-        <v>1043</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1141</v>
-      </c>
-      <c r="C60" t="s">
-        <v>1064</v>
-      </c>
-      <c r="F60">
-        <v>1</v>
-      </c>
-      <c r="G60" t="s">
-        <v>1012</v>
-      </c>
-      <c r="I60" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
-      <c r="A61" t="s">
-        <v>1043</v>
-      </c>
-      <c r="B61" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C61" t="s">
-        <v>1064</v>
-      </c>
-      <c r="F61">
-        <v>1</v>
-      </c>
-      <c r="G61" t="s">
-        <v>1012</v>
-      </c>
-      <c r="I61" t="s">
-        <v>1144</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
-      <c r="A62" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B62" t="s">
-        <v>1145</v>
-      </c>
-      <c r="C62" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D62" t="s">
-        <v>1146</v>
-      </c>
-      <c r="I62" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
-      <c r="A63" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B63" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C63" t="s">
-        <v>1052</v>
-      </c>
-      <c r="I63" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9">
-      <c r="A64" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B64" t="s">
-        <v>1148</v>
-      </c>
-      <c r="C64" t="s">
-        <v>1052</v>
-      </c>
-      <c r="I64" t="s">
+      <c r="H62" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J62" t="s">
         <v>1229</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1" xr:uid="{84C9ADE8-E8E1-442A-91BD-AA392C318296}"/>
+  <autoFilter ref="A1:J1" xr:uid="{84C9ADE8-E8E1-442A-91BD-AA392C318296}"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18011,7 +18350,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4846F037-20B4-4728-8141-7B4C51F45A0D}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -18030,16 +18369,16 @@
         <v>18</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1150</v>
+        <v>1145</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>1152</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -18050,13 +18389,13 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="E2" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F2" t="s">
-        <v>1154</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -18067,16 +18406,16 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="D3" t="s">
         <v>26</v>
       </c>
       <c r="E3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F3" t="s">
         <v>1151</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -18087,16 +18426,16 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="D4" t="s">
         <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F4" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -18107,16 +18446,16 @@
         <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F5" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -18127,16 +18466,16 @@
         <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="D6" t="s">
-        <v>1160</v>
+        <v>1155</v>
       </c>
       <c r="E6" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F6" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -18147,16 +18486,16 @@
         <v>36</v>
       </c>
       <c r="C7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D7" t="s">
         <v>1157</v>
       </c>
-      <c r="D7" t="s">
-        <v>1162</v>
-      </c>
       <c r="E7" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F7" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -18167,16 +18506,16 @@
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="D8" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="E8" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F8" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -18187,16 +18526,16 @@
         <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="D9" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
       <c r="E9" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F9" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -18207,13 +18546,13 @@
         <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="E10" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F10" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -18224,16 +18563,16 @@
         <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="D11" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="E11" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F11" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -18244,16 +18583,16 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="D12" t="s">
         <v>52</v>
       </c>
       <c r="E12" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F12" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -18261,19 +18600,19 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C13" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="D13" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="E13" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F13" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -18284,13 +18623,13 @@
         <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="E14" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F14" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -18301,13 +18640,13 @@
         <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="E15" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F15" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -18318,13 +18657,13 @@
         <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="E16" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F16" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -18335,13 +18674,13 @@
         <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="E17" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F17" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -18352,16 +18691,16 @@
         <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="D18" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="E18" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F18" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -18372,16 +18711,16 @@
         <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="D19" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="E19" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F19" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -18392,448 +18731,465 @@
         <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="E20" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F20" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="B21" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="C21" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="D21" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="E21" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F21" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="B22" t="s">
         <v>725</v>
       </c>
       <c r="C22" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="E22" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F22" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B23" t="s">
+        <v>994</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F23" t="s">
         <v>1184</v>
-      </c>
-      <c r="B23" t="s">
-        <v>996</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1188</v>
-      </c>
-      <c r="E23" t="s">
-        <v>1151</v>
-      </c>
-      <c r="F23" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="B24" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C24" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="D24" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="E24" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F24" t="s">
-        <v>1191</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="B25" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="C25" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="D25" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="E25" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F25" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="B26" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="C26" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="D26" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="E26" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F26" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="B27" t="s">
         <v>727</v>
       </c>
       <c r="C27" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="E27" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F27" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="B28" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C28" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="D28" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="E28" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F28" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="B29" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C29" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="D29" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="E29" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F29" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="B30" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C30" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="E30" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F30" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="B31" t="s">
         <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="E31" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F31" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="B32" t="s">
         <v>728</v>
       </c>
       <c r="C32" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="D32" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="E32" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F32" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="B33" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="C33" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="E33" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F33" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="B34" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="C34" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="D34" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="E34" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F34" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="B35" t="s">
         <v>726</v>
       </c>
       <c r="C35" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="D35" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="E35" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F35" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="B36" t="s">
-        <v>1045</v>
+        <v>1234</v>
       </c>
       <c r="C36" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D36" t="s">
-        <v>1208</v>
+        <v>1150</v>
       </c>
       <c r="E36" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="F36" t="s">
-        <v>1209</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F37" t="s">
         <v>1204</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C37" t="s">
-        <v>1155</v>
-      </c>
-      <c r="D37" t="s">
-        <v>1206</v>
-      </c>
-      <c r="E37" t="s">
-        <v>1163</v>
-      </c>
-      <c r="F37" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="B38" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="C38" t="s">
-        <v>1153</v>
+        <v>1150</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1201</v>
       </c>
       <c r="E38" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F38" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="B39" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="C39" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="E39" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F39" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="B40" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="C40" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D40" t="s">
-        <v>1190</v>
+        <v>1148</v>
       </c>
       <c r="E40" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F40" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="B41" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="C41" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="D41" t="s">
-        <v>1214</v>
+        <v>1185</v>
       </c>
       <c r="E41" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F41" t="s">
-        <v>1215</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="B42" t="s">
-        <v>1003</v>
+        <v>1048</v>
       </c>
       <c r="C42" t="s">
-        <v>1155</v>
+        <v>1150</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1209</v>
       </c>
       <c r="E42" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="F42" t="s">
-        <v>1216</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E43" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F43" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
         <v>7</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B44" t="s">
         <v>78</v>
       </c>
-      <c r="C43" t="s">
-        <v>1217</v>
-      </c>
-      <c r="D43" t="s">
-        <v>1218</v>
-      </c>
-      <c r="E43" t="s">
-        <v>1151</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="C44" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E44" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F44" t="s">
         <v>79</v>
       </c>
     </row>

--- a/outputs/mai-report-policy/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E4BF72-E475-4F03-80C9-BEC7B6CE9607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2D107C-A7F1-409E-A448-E9A6AE57CD57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38370" yWindow="-4030" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3945" uniqueCount="1293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3966" uniqueCount="1301">
   <si>
     <t>maiReport 식이 참조·설정 데이터 v1.0.0 | 2026-09-22</t>
   </si>
@@ -2258,12 +2258,6 @@
   </si>
   <si>
     <t>KDIGO-2024; NIDDK-CKD</t>
-  </si>
-  <si>
-    <t>심혈관질환</t>
-  </si>
-  <si>
-    <t>심장 · 뇌혈관 질환(협심증 · 심근경색 · 뇌졸중 등)</t>
   </si>
   <si>
     <t>AHA-HF</t>
@@ -3135,12 +3129,6 @@
     <t>DIET-Q-03;DIET-Q-07</t>
   </si>
   <si>
-    <t>심부전은 처방된 수분 계획이 우선이다</t>
-  </si>
-  <si>
-    <t>뇌졸중의 음식 질감·도구 목표 보류는 성격 값이 없어 아직 못 건다. 질감 성격을 만들지 결정 필요</t>
-  </si>
-  <si>
     <t>DX-07</t>
   </si>
   <si>
@@ -3567,9 +3555,6 @@
     <t>검진 경계 신호가 있을 때만 쓰는 문구</t>
   </si>
   <si>
-    <t>감량 · 공복 · 증량 · 수분 또는 빈칸</t>
-  </si>
-  <si>
     <t>질환별 금지가 이 값을 보고 문구를 뺀다. 빈칸은 어느 금지에도 걸리지 않는다</t>
   </si>
   <si>
@@ -3637,9 +3622,6 @@
   </si>
   <si>
     <t>축정의 시트의 질문 ID를 참조한다. 이름 문자열로 쓰지 않는다</t>
-  </si>
-  <si>
-    <t>감량 · 공복 · 증량 · 수분 세미콜론 구분</t>
   </si>
   <si>
     <t>문구세트의 성격 열과 대조해 뺀다</t>
@@ -3957,6 +3939,56 @@
   </si>
   <si>
     <t>그 코드가 무엇인지 사람이 읽기 위한 것. 판정에 쓰지 않는다. ICD-10 기준 표기이며 실제 KCD 마스터의 공식 명칭·5단위 세분류와 대조해야 한다</t>
+  </si>
+  <si>
+    <t>질감</t>
+  </si>
+  <si>
+    <t>심장질환</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>심장질환(협심증 · 심근경색 · 심부전 등)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>심부전은 처방된 수분 계획이 우선이다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>뇌혈관질환은 금지 성격이 달라 DX-21로 분리했다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DX-21</t>
+  </si>
+  <si>
+    <t>뇌혈관질환</t>
+  </si>
+  <si>
+    <t>뇌혈관질환(뇌졸중 등)</t>
+  </si>
+  <si>
+    <t>연하·기능 상태를 확인하기 전에는 음식의 질감과 도구를 요구하는 목표를 내지 않는다</t>
+  </si>
+  <si>
+    <t>심장질환(DX-06)에서 분리했다. 연하곤란이 함께 코딩되면 DX-20도 같이 걸린다</t>
+  </si>
+  <si>
+    <t>DX-21</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>감량;공복;증량;질감</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>감량 · 공복 · 증량 · 수분 · 질감 또는 빈칸</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>감량 · 공복 · 증량 · 수분 · 질감 세미콜론 구분</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4419,7 +4451,7 @@
     </row>
     <row r="2" spans="1:3" ht="25.4" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -4445,7 +4477,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="C5" s="1">
         <v>171</v>
@@ -4456,7 +4488,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="C6" s="1">
         <v>8</v>
@@ -4464,21 +4496,21 @@
     </row>
     <row r="7" spans="1:3" ht="25.4" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>1216</v>
+        <v>1210</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="C7" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="25.4" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="C8" s="1">
         <v>61</v>
@@ -4498,10 +4530,10 @@
     </row>
     <row r="10" spans="1:3" ht="25.4" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1220</v>
+        <v>1214</v>
       </c>
       <c r="C10" s="11">
         <v>42</v>
@@ -4514,7 +4546,7 @@
     </row>
     <row r="12" spans="1:3" ht="25.4" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -4524,7 +4556,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C13" s="1">
         <v>171</v>
@@ -4583,7 +4615,7 @@
     </row>
     <row r="21" spans="1:3" ht="25.4" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -4912,7 +4944,7 @@
         <v>86</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C53" s="4"/>
     </row>
@@ -4976,7 +5008,7 @@
         <v>50</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="M1" s="6" t="s">
         <v>53</v>
@@ -5034,7 +5066,7 @@
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>98</v>
@@ -5092,7 +5124,7 @@
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>98</v>
@@ -5148,7 +5180,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>98</v>
@@ -5258,7 +5290,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>118</v>
@@ -5314,7 +5346,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>118</v>
@@ -5480,7 +5512,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>133</v>
@@ -5536,7 +5568,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>138</v>
@@ -5594,7 +5626,7 @@
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>143</v>
@@ -5650,7 +5682,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>138</v>
@@ -5706,7 +5738,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>138</v>
@@ -6032,7 +6064,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>166</v>
@@ -6088,7 +6120,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>118</v>
@@ -6144,7 +6176,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>118</v>
@@ -6200,7 +6232,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>118</v>
@@ -6256,7 +6288,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>98</v>
@@ -6311,7 +6343,9 @@
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>1287</v>
+      </c>
       <c r="M25" s="1" t="s">
         <v>118</v>
       </c>
@@ -6422,7 +6456,7 @@
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>98</v>
@@ -6478,7 +6512,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>98</v>
@@ -6536,7 +6570,7 @@
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>98</v>
@@ -6760,7 +6794,7 @@
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>221</v>
@@ -6874,7 +6908,7 @@
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>98</v>
@@ -6932,7 +6966,7 @@
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>98</v>
@@ -7046,7 +7080,7 @@
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>118</v>
@@ -7104,7 +7138,7 @@
       </c>
       <c r="K39" s="1"/>
       <c r="L39" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>118</v>
@@ -7162,7 +7196,7 @@
       </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>118</v>
@@ -7332,7 +7366,7 @@
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>138</v>
@@ -7446,7 +7480,7 @@
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>143</v>
@@ -7504,7 +7538,7 @@
       </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>138</v>
@@ -7618,7 +7652,7 @@
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>143</v>
@@ -7676,7 +7710,7 @@
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>143</v>
@@ -7790,7 +7824,7 @@
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>138</v>
@@ -7904,7 +7938,7 @@
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>118</v>
@@ -7962,7 +7996,7 @@
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>221</v>
@@ -8076,7 +8110,7 @@
       </c>
       <c r="K56" s="1"/>
       <c r="L56" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>118</v>
@@ -8189,7 +8223,9 @@
         <v>198</v>
       </c>
       <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
+      <c r="L58" s="1" t="s">
+        <v>1287</v>
+      </c>
       <c r="M58" s="1" t="s">
         <v>143</v>
       </c>
@@ -8245,7 +8281,9 @@
         <v>198</v>
       </c>
       <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
+      <c r="L59" s="1" t="s">
+        <v>1287</v>
+      </c>
       <c r="M59" s="1" t="s">
         <v>143</v>
       </c>
@@ -8302,7 +8340,7 @@
       </c>
       <c r="K60" s="1"/>
       <c r="L60" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M60" s="1" t="s">
         <v>143</v>
@@ -8416,7 +8454,7 @@
       </c>
       <c r="K62" s="1"/>
       <c r="L62" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M62" s="1" t="s">
         <v>98</v>
@@ -8474,7 +8512,7 @@
       </c>
       <c r="K63" s="1"/>
       <c r="L63" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M63" s="1" t="s">
         <v>221</v>
@@ -8532,7 +8570,7 @@
       </c>
       <c r="K64" s="1"/>
       <c r="L64" s="1" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="M64" s="1" t="s">
         <v>138</v>
@@ -8590,7 +8628,7 @@
       </c>
       <c r="K65" s="1"/>
       <c r="L65" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M65" s="1" t="s">
         <v>98</v>
@@ -8648,7 +8686,7 @@
       </c>
       <c r="K66" s="1"/>
       <c r="L66" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M66" s="1" t="s">
         <v>98</v>
@@ -8706,7 +8744,7 @@
       </c>
       <c r="K67" s="1"/>
       <c r="L67" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M67" s="1" t="s">
         <v>98</v>
@@ -8820,7 +8858,7 @@
       </c>
       <c r="K69" s="1"/>
       <c r="L69" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M69" s="1" t="s">
         <v>98</v>
@@ -8878,7 +8916,7 @@
       </c>
       <c r="K70" s="1"/>
       <c r="L70" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M70" s="1" t="s">
         <v>118</v>
@@ -8992,7 +9030,7 @@
       </c>
       <c r="K72" s="1"/>
       <c r="L72" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M72" s="1" t="s">
         <v>118</v>
@@ -9050,7 +9088,7 @@
       </c>
       <c r="K73" s="1"/>
       <c r="L73" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M73" s="1" t="s">
         <v>194</v>
@@ -9164,7 +9202,7 @@
       </c>
       <c r="K75" s="1"/>
       <c r="L75" s="1" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>133</v>
@@ -9222,7 +9260,7 @@
       </c>
       <c r="K76" s="1"/>
       <c r="L76" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>133</v>
@@ -9280,7 +9318,7 @@
       </c>
       <c r="K77" s="1"/>
       <c r="L77" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M77" s="1" t="s">
         <v>98</v>
@@ -9338,7 +9376,7 @@
       </c>
       <c r="K78" s="1"/>
       <c r="L78" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M78" s="1" t="s">
         <v>143</v>
@@ -9396,7 +9434,7 @@
       </c>
       <c r="K79" s="1"/>
       <c r="L79" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M79" s="1" t="s">
         <v>98</v>
@@ -9454,7 +9492,7 @@
       </c>
       <c r="K80" s="1"/>
       <c r="L80" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M80" s="1" t="s">
         <v>98</v>
@@ -9512,7 +9550,7 @@
       </c>
       <c r="K81" s="1"/>
       <c r="L81" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M81" s="1" t="s">
         <v>98</v>
@@ -9626,7 +9664,7 @@
       </c>
       <c r="K83" s="1"/>
       <c r="L83" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M83" s="1" t="s">
         <v>143</v>
@@ -9684,7 +9722,7 @@
       </c>
       <c r="K84" s="1"/>
       <c r="L84" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M84" s="1" t="s">
         <v>143</v>
@@ -9798,7 +9836,7 @@
       </c>
       <c r="K86" s="1"/>
       <c r="L86" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M86" s="1" t="s">
         <v>391</v>
@@ -9856,7 +9894,7 @@
       </c>
       <c r="K87" s="1"/>
       <c r="L87" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M87" s="1" t="s">
         <v>396</v>
@@ -9914,7 +9952,7 @@
       </c>
       <c r="K88" s="1"/>
       <c r="L88" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M88" s="1" t="s">
         <v>396</v>
@@ -9972,7 +10010,7 @@
       </c>
       <c r="K89" s="1"/>
       <c r="L89" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M89" s="1" t="s">
         <v>166</v>
@@ -10030,7 +10068,7 @@
       </c>
       <c r="K90" s="1"/>
       <c r="L90" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M90" s="1" t="s">
         <v>166</v>
@@ -10088,7 +10126,7 @@
       </c>
       <c r="K91" s="1"/>
       <c r="L91" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M91" s="1" t="s">
         <v>118</v>
@@ -10146,7 +10184,7 @@
       </c>
       <c r="K92" s="1"/>
       <c r="L92" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M92" s="1" t="s">
         <v>118</v>
@@ -10203,7 +10241,9 @@
         <v>198</v>
       </c>
       <c r="K93" s="1"/>
-      <c r="L93" s="1"/>
+      <c r="L93" s="1" t="s">
+        <v>1287</v>
+      </c>
       <c r="M93" s="1" t="s">
         <v>118</v>
       </c>
@@ -10260,7 +10300,7 @@
       </c>
       <c r="K94" s="1"/>
       <c r="L94" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M94" s="1" t="s">
         <v>118</v>
@@ -10598,7 +10638,7 @@
       </c>
       <c r="K100" s="1"/>
       <c r="L100" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M100" s="1" t="s">
         <v>98</v>
@@ -10656,7 +10696,7 @@
       </c>
       <c r="K101" s="1"/>
       <c r="L101" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M101" s="1" t="s">
         <v>98</v>
@@ -10826,7 +10866,7 @@
       </c>
       <c r="K104" s="1"/>
       <c r="L104" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M104" s="1" t="s">
         <v>118</v>
@@ -10940,7 +10980,7 @@
       </c>
       <c r="K106" s="1"/>
       <c r="L106" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M106" s="1" t="s">
         <v>118</v>
@@ -10998,7 +11038,7 @@
       </c>
       <c r="K107" s="1"/>
       <c r="L107" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M107" s="1" t="s">
         <v>118</v>
@@ -11112,7 +11152,7 @@
       </c>
       <c r="K109" s="1"/>
       <c r="L109" s="1" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="M109" s="1" t="s">
         <v>133</v>
@@ -11170,7 +11210,7 @@
       </c>
       <c r="K110" s="1"/>
       <c r="L110" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M110" s="1" t="s">
         <v>98</v>
@@ -11284,7 +11324,7 @@
       </c>
       <c r="K112" s="1"/>
       <c r="L112" s="1" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="M112" s="1" t="s">
         <v>133</v>
@@ -11342,7 +11382,7 @@
       </c>
       <c r="K113" s="1"/>
       <c r="L113" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>138</v>
@@ -11400,7 +11440,7 @@
       </c>
       <c r="K114" s="1"/>
       <c r="L114" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M114" s="1" t="s">
         <v>143</v>
@@ -11570,7 +11610,7 @@
       </c>
       <c r="K117" s="1"/>
       <c r="L117" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>98</v>
@@ -11684,7 +11724,7 @@
       </c>
       <c r="K119" s="1"/>
       <c r="L119" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M119" s="1" t="s">
         <v>143</v>
@@ -11742,7 +11782,7 @@
       </c>
       <c r="K120" s="1"/>
       <c r="L120" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M120" s="1" t="s">
         <v>138</v>
@@ -11800,7 +11840,7 @@
       </c>
       <c r="K121" s="1"/>
       <c r="L121" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M121" s="1" t="s">
         <v>396</v>
@@ -12026,7 +12066,7 @@
       </c>
       <c r="K125" s="1"/>
       <c r="L125" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M125" s="1" t="s">
         <v>396</v>
@@ -12084,7 +12124,7 @@
       </c>
       <c r="K126" s="1"/>
       <c r="L126" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M126" s="1" t="s">
         <v>166</v>
@@ -12142,7 +12182,7 @@
       </c>
       <c r="K127" s="1"/>
       <c r="L127" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M127" s="1" t="s">
         <v>118</v>
@@ -12200,7 +12240,7 @@
       </c>
       <c r="K128" s="1"/>
       <c r="L128" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M128" s="1" t="s">
         <v>118</v>
@@ -12314,7 +12354,7 @@
       </c>
       <c r="K130" s="1"/>
       <c r="L130" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M130" s="1" t="s">
         <v>118</v>
@@ -12372,7 +12412,7 @@
       </c>
       <c r="K131" s="1"/>
       <c r="L131" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M131" s="1" t="s">
         <v>118</v>
@@ -12429,7 +12469,9 @@
         <v>453</v>
       </c>
       <c r="K132" s="1"/>
-      <c r="L132" s="1"/>
+      <c r="L132" s="1" t="s">
+        <v>1287</v>
+      </c>
       <c r="M132" s="1" t="s">
         <v>194</v>
       </c>
@@ -12486,7 +12528,7 @@
       </c>
       <c r="K133" s="1"/>
       <c r="L133" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M133" s="1" t="s">
         <v>98</v>
@@ -12600,7 +12642,7 @@
       </c>
       <c r="K135" s="1"/>
       <c r="L135" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M135" s="1" t="s">
         <v>98</v>
@@ -12657,7 +12699,9 @@
         <v>343</v>
       </c>
       <c r="K136" s="1"/>
-      <c r="L136" s="1"/>
+      <c r="L136" s="1" t="s">
+        <v>1287</v>
+      </c>
       <c r="M136" s="1" t="s">
         <v>98</v>
       </c>
@@ -12714,7 +12758,7 @@
       </c>
       <c r="K137" s="1"/>
       <c r="L137" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M137" s="1" t="s">
         <v>98</v>
@@ -12772,7 +12816,7 @@
       </c>
       <c r="K138" s="1"/>
       <c r="L138" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M138" s="1" t="s">
         <v>98</v>
@@ -12830,7 +12874,7 @@
       </c>
       <c r="K139" s="1"/>
       <c r="L139" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M139" s="1" t="s">
         <v>118</v>
@@ -12888,7 +12932,7 @@
       </c>
       <c r="K140" s="1"/>
       <c r="L140" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M140" s="1" t="s">
         <v>138</v>
@@ -12946,7 +12990,7 @@
       </c>
       <c r="K141" s="1"/>
       <c r="L141" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M141" s="1" t="s">
         <v>166</v>
@@ -13060,7 +13104,7 @@
       </c>
       <c r="K143" s="1"/>
       <c r="L143" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M143" s="1" t="s">
         <v>118</v>
@@ -13118,7 +13162,7 @@
       </c>
       <c r="K144" s="1"/>
       <c r="L144" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M144" s="1" t="s">
         <v>118</v>
@@ -13175,7 +13219,9 @@
         <v>198</v>
       </c>
       <c r="K145" s="1"/>
-      <c r="L145" s="1"/>
+      <c r="L145" s="1" t="s">
+        <v>1287</v>
+      </c>
       <c r="M145" s="1" t="s">
         <v>98</v>
       </c>
@@ -13288,7 +13334,7 @@
       </c>
       <c r="K147" s="1"/>
       <c r="L147" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M147" s="1" t="s">
         <v>396</v>
@@ -13346,7 +13392,7 @@
       </c>
       <c r="K148" s="1"/>
       <c r="L148" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M148" s="1" t="s">
         <v>118</v>
@@ -13404,7 +13450,7 @@
       </c>
       <c r="K149" s="1"/>
       <c r="L149" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M149" s="1" t="s">
         <v>118</v>
@@ -13462,7 +13508,7 @@
       </c>
       <c r="K150" s="1"/>
       <c r="L150" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M150" s="1" t="s">
         <v>118</v>
@@ -13520,7 +13566,7 @@
       </c>
       <c r="K151" s="1"/>
       <c r="L151" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M151" s="1" t="s">
         <v>118</v>
@@ -13578,7 +13624,7 @@
       </c>
       <c r="K152" s="1"/>
       <c r="L152" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M152" s="1" t="s">
         <v>138</v>
@@ -13635,7 +13681,9 @@
         <v>198</v>
       </c>
       <c r="K153" s="1"/>
-      <c r="L153" s="1"/>
+      <c r="L153" s="1" t="s">
+        <v>1287</v>
+      </c>
       <c r="M153" s="1" t="s">
         <v>98</v>
       </c>
@@ -13692,7 +13740,7 @@
       </c>
       <c r="K154" s="1"/>
       <c r="L154" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M154" s="1" t="s">
         <v>118</v>
@@ -13750,7 +13798,7 @@
       </c>
       <c r="K155" s="1"/>
       <c r="L155" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M155" s="1" t="s">
         <v>143</v>
@@ -13864,7 +13912,7 @@
       </c>
       <c r="K157" s="1"/>
       <c r="L157" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="M157" s="1" t="s">
         <v>138</v>
@@ -13978,7 +14026,7 @@
       </c>
       <c r="K159" s="1"/>
       <c r="L159" s="1" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="M159" s="1" t="s">
         <v>133</v>
@@ -14092,7 +14140,7 @@
       </c>
       <c r="K161" s="1"/>
       <c r="L161" s="1" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="M161" s="1" t="s">
         <v>133</v>
@@ -14150,7 +14198,7 @@
       </c>
       <c r="K162" s="1"/>
       <c r="L162" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="M162" s="1" t="s">
         <v>143</v>
@@ -14306,13 +14354,13 @@
         <v>94</v>
       </c>
       <c r="G165" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="H165">
         <v>17</v>
       </c>
       <c r="I165" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="J165" t="s">
         <v>125</v>
@@ -14324,13 +14372,13 @@
         <v>99</v>
       </c>
       <c r="O165" t="s">
+        <v>940</v>
+      </c>
+      <c r="P165" t="s">
+        <v>941</v>
+      </c>
+      <c r="Q165" t="s">
         <v>942</v>
-      </c>
-      <c r="P165" t="s">
-        <v>943</v>
-      </c>
-      <c r="Q165" t="s">
-        <v>944</v>
       </c>
       <c r="R165" t="s">
         <v>103</v>
@@ -14359,13 +14407,13 @@
         <v>104</v>
       </c>
       <c r="G166" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="H166">
         <v>14</v>
       </c>
       <c r="I166" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="J166" t="s">
         <v>125</v>
@@ -14377,13 +14425,13 @@
         <v>99</v>
       </c>
       <c r="O166" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="P166" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="Q166" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="R166" t="s">
         <v>103</v>
@@ -14412,13 +14460,13 @@
         <v>94</v>
       </c>
       <c r="G167" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="H167">
         <v>14</v>
       </c>
       <c r="I167" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="J167" t="s">
         <v>125</v>
@@ -14430,13 +14478,13 @@
         <v>99</v>
       </c>
       <c r="O167" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="P167" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="Q167" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="R167" t="s">
         <v>103</v>
@@ -14465,13 +14513,13 @@
         <v>104</v>
       </c>
       <c r="G168" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="H168">
         <v>14</v>
       </c>
       <c r="I168" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="J168" t="s">
         <v>125</v>
@@ -14483,13 +14531,13 @@
         <v>99</v>
       </c>
       <c r="O168" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="P168" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="Q168" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="R168" t="s">
         <v>103</v>
@@ -14518,13 +14566,13 @@
         <v>94</v>
       </c>
       <c r="G169" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="H169">
         <v>14</v>
       </c>
       <c r="I169" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="J169" t="s">
         <v>125</v>
@@ -14536,13 +14584,13 @@
         <v>99</v>
       </c>
       <c r="O169" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="P169" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="Q169" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="R169" t="s">
         <v>103</v>
@@ -14571,13 +14619,13 @@
         <v>104</v>
       </c>
       <c r="G170" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="H170">
         <v>15</v>
       </c>
       <c r="I170" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="J170" t="s">
         <v>125</v>
@@ -14589,13 +14637,13 @@
         <v>99</v>
       </c>
       <c r="O170" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="P170" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="Q170" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="R170" t="s">
         <v>103</v>
@@ -14624,13 +14672,13 @@
         <v>94</v>
       </c>
       <c r="G171" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="H171">
         <v>18</v>
       </c>
       <c r="I171" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="J171" t="s">
         <v>125</v>
@@ -14642,13 +14690,13 @@
         <v>99</v>
       </c>
       <c r="O171" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="P171" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="Q171" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="R171" t="s">
         <v>103</v>
@@ -14668,22 +14716,22 @@
         <v>9</v>
       </c>
       <c r="D172" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="E172" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="F172" t="s">
         <v>199</v>
       </c>
       <c r="G172" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="H172">
         <v>20</v>
       </c>
       <c r="I172" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="J172" t="s">
         <v>125</v>
@@ -14695,13 +14743,13 @@
         <v>99</v>
       </c>
       <c r="O172" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="P172" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="Q172" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="R172" t="s">
         <v>103</v>
@@ -15276,152 +15324,152 @@
         <v>30</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>78</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>754</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="32">
       <c r="A4" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="32">
       <c r="A5" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>968</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>969</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="32">
       <c r="A6" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="C6" s="1">
         <v>28</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="32">
       <c r="A7" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="48">
       <c r="A8" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="32">
       <c r="A9" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C9" s="1">
         <v>84</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -15429,16 +15477,16 @@
         <v>36</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>761</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="66" customHeight="1">
@@ -15446,452 +15494,452 @@
         <v>36</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>765</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="66" customHeight="1">
       <c r="A12" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>770</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="66" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>773</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>774</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>775</v>
       </c>
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:5" ht="66" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="1" t="s">
         <v>777</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="66" customHeight="1">
       <c r="A15" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>782</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="66" customHeight="1">
       <c r="A16" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>786</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>788</v>
       </c>
       <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:5" ht="66" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>789</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>791</v>
       </c>
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:5" ht="66" customHeight="1">
       <c r="A18" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>794</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>795</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="66" customHeight="1">
       <c r="A19" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>799</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>800</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="66" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>802</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>800</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="66" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>806</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="66" customHeight="1">
       <c r="A22" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>809</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>811</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>812</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="66" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>814</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>815</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>812</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="66" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>818</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>819</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="66" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>822</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="66" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>825</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>826</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="66" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>828</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="66" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>831</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="66" customHeight="1">
       <c r="A29" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>837</v>
-      </c>
       <c r="E29" s="1" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="66" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>839</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>840</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="66" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>843</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>844</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="66" customHeight="1">
       <c r="A32" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>847</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>848</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>849</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="66" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>851</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>852</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="66" customHeight="1">
       <c r="A34" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>855</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>857</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>858</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="66" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>861</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>862</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="66" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>865</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="66" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>869</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="66" customHeight="1">
@@ -15899,16 +15947,16 @@
         <v>641</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="E38" s="4" t="s">
         <v>873</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>874</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="66" customHeight="1">
@@ -15916,16 +15964,16 @@
         <v>641</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C39" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="66" customHeight="1">
@@ -15933,16 +15981,16 @@
         <v>641</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C40" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="66" customHeight="1">
@@ -15950,67 +15998,67 @@
         <v>641</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="E41" s="4" t="s">
         <v>881</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>882</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>877</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="66" customHeight="1">
       <c r="A42" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>884</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="D42" s="4" t="s">
         <v>885</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="E42" s="4" t="s">
         <v>886</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>887</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="66" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>889</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="E43" s="4" t="s">
         <v>890</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>891</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="66" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>893</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="E44" s="4" t="s">
         <v>894</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>895</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="66" customHeight="1">
@@ -16018,191 +16066,191 @@
         <v>36</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C45" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="66" customHeight="1">
       <c r="A46" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>900</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="D46" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>901</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>902</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>891</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="66" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>904</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="E47" s="4" t="s">
         <v>905</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>906</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="66" customHeight="1">
       <c r="A48" s="4" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C48" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="66" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>103</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="66" customHeight="1">
       <c r="A50" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>914</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="D50" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="E50" s="4" t="s">
         <v>915</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>797</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="66" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B51" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>918</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>919</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>752</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="66" customHeight="1">
       <c r="A52" s="4" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B52" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>921</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="E52" s="4" t="s">
         <v>922</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>923</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="66" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>925</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="E53" s="4" t="s">
         <v>926</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>927</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="66" customHeight="1">
       <c r="A54" s="4" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>929</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="E54" s="4" t="s">
         <v>930</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>931</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="66" customHeight="1">
       <c r="A55" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>933</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="D55" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>934</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>935</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>891</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="66" customHeight="1">
       <c r="A56" s="4" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>82</v>
@@ -16211,10 +16259,10 @@
         <v>1</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
   </sheetData>
@@ -16225,7 +16273,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{216EACFD-C9FD-4000-8498-48312F82252B}">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="7.58203125" bestFit="1" customWidth="1"/>
@@ -16244,34 +16292,34 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="10" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>725</v>
       </c>
       <c r="C1" s="10" t="s">
+        <v>992</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>993</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>994</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>995</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>996</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>997</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>727</v>
       </c>
       <c r="H1" s="10" t="s">
+        <v>996</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>997</v>
+      </c>
+      <c r="J1" s="10" t="s">
         <v>998</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>999</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>1000</v>
       </c>
       <c r="K1" s="10" t="s">
         <v>53</v>
@@ -16280,12 +16328,12 @@
         <v>728</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="B2" t="s">
         <v>729</v>
@@ -16294,39 +16342,39 @@
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="E2" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="F2" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="G2" t="s">
         <v>729</v>
       </c>
       <c r="H2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J2" t="s">
         <v>1004</v>
-      </c>
-      <c r="I2" t="s">
-        <v>1005</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1006</v>
       </c>
       <c r="K2" t="s">
         <v>730</v>
       </c>
       <c r="L2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="M2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B3" t="s">
         <v>731</v>
@@ -16335,33 +16383,33 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="E3" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="F3" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="G3" t="s">
         <v>731</v>
       </c>
       <c r="H3" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="K3" t="s">
         <v>732</v>
       </c>
       <c r="L3" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="M3" t="s">
-        <v>1223</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B4" t="s">
         <v>733</v>
@@ -16370,68 +16418,68 @@
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="E4" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="F4" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="G4" t="s">
         <v>734</v>
       </c>
       <c r="H4" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="K4" t="s">
         <v>735</v>
       </c>
       <c r="L4" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="M4" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B5" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C5" t="s">
         <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="E5" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="F5" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="G5" t="s">
         <v>734</v>
       </c>
       <c r="H5" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="K5" t="s">
         <v>735</v>
       </c>
       <c r="L5" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="M5" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B6" t="s">
         <v>736</v>
@@ -16440,355 +16488,396 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="E6" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="F6" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="G6" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="H6" t="s">
         <v>695</v>
       </c>
       <c r="I6" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="J6" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K6" t="s">
         <v>737</v>
       </c>
       <c r="L6" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="M6" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B7" t="s">
-        <v>738</v>
+        <v>1288</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="E7" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="F7" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="G7" t="s">
-        <v>739</v>
+        <v>1289</v>
       </c>
       <c r="H7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="I7" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="J7" t="s">
-        <v>1024</v>
+        <v>1290</v>
       </c>
       <c r="K7" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="L7" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="M7" t="s">
-        <v>1025</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>1026</v>
+        <v>1292</v>
       </c>
       <c r="B8" t="s">
-        <v>741</v>
+        <v>1293</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="E8" t="s">
-        <v>1010</v>
+        <v>1001</v>
       </c>
       <c r="F8" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="G8" t="s">
-        <v>741</v>
+        <v>1294</v>
       </c>
       <c r="H8" t="s">
-        <v>1027</v>
+        <v>1021</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1287</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1295</v>
       </c>
       <c r="K8" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="L8" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="M8" t="s">
-        <v>1028</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="B9" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>1010</v>
+        <v>1001</v>
       </c>
       <c r="E9" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="F9" t="s">
-        <v>1010</v>
-      </c>
-      <c r="I9" t="s">
-        <v>1030</v>
-      </c>
-      <c r="J9" t="s">
-        <v>1031</v>
+        <v>1001</v>
+      </c>
+      <c r="G9" t="s">
+        <v>739</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1023</v>
       </c>
       <c r="K9" t="s">
-        <v>1032</v>
+        <v>740</v>
       </c>
       <c r="L9" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="M9" t="s">
-        <v>1033</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>1034</v>
+        <v>1025</v>
       </c>
       <c r="B10" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="E10" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="F10" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="I10" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="J10" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="K10" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="L10" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="M10" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="B11" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C11" t="s">
         <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="E11" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="F11" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="I11" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="J11" t="s">
+        <v>1027</v>
+      </c>
+      <c r="K11" t="s">
+        <v>1028</v>
+      </c>
+      <c r="L11" t="s">
+        <v>1005</v>
+      </c>
+      <c r="M11" t="s">
         <v>1031</v>
-      </c>
-      <c r="K11" t="s">
-        <v>1032</v>
-      </c>
-      <c r="L11" t="s">
-        <v>1007</v>
-      </c>
-      <c r="M11" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="B12" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="E12" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="F12" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="I12" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="J12" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="K12" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="L12" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="M12" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="B13" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="E13" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="F13" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="I13" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="J13" t="s">
+        <v>1027</v>
+      </c>
+      <c r="K13" t="s">
+        <v>1028</v>
+      </c>
+      <c r="L13" t="s">
+        <v>1005</v>
+      </c>
+      <c r="M13" t="s">
         <v>1031</v>
-      </c>
-      <c r="K13" t="s">
-        <v>1032</v>
-      </c>
-      <c r="L13" t="s">
-        <v>1007</v>
-      </c>
-      <c r="M13" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="B14" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="C14" t="s">
-        <v>1226</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="E14" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="F14" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="I14" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="J14" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="K14" t="s">
-        <v>737</v>
+        <v>1028</v>
       </c>
       <c r="L14" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="M14" t="s">
-        <v>1227</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="B15" t="s">
-        <v>1231</v>
+        <v>746</v>
       </c>
       <c r="C15" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I15" t="s">
+        <v>1018</v>
+      </c>
+      <c r="J15" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K15" t="s">
+        <v>737</v>
+      </c>
+      <c r="L15" t="s">
+        <v>1005</v>
+      </c>
+      <c r="M15" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B16" t="s">
         <v>1225</v>
       </c>
-      <c r="D15" t="s">
-        <v>1010</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1003</v>
-      </c>
-      <c r="F15" t="s">
-        <v>1010</v>
-      </c>
-      <c r="I15" t="s">
-        <v>1030</v>
-      </c>
-      <c r="J15" t="s">
-        <v>1232</v>
-      </c>
-      <c r="K15" t="s">
-        <v>1032</v>
-      </c>
-      <c r="L15" t="s">
-        <v>1007</v>
-      </c>
-      <c r="M15" t="s">
-        <v>1233</v>
+      <c r="C16" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I16" t="s">
+        <v>1298</v>
+      </c>
+      <c r="J16" t="s">
+        <v>1226</v>
+      </c>
+      <c r="K16" t="s">
+        <v>1028</v>
+      </c>
+      <c r="L16" t="s">
+        <v>1005</v>
+      </c>
+      <c r="M16" t="s">
+        <v>1227</v>
       </c>
     </row>
   </sheetData>
@@ -16815,48 +16904,48 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="10" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>726</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="D1" s="10" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H1" s="10" t="s">
         <v>1043</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>1044</v>
       </c>
-      <c r="F1" s="10" t="s">
-        <v>1045</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>1046</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>1047</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>1048</v>
-      </c>
       <c r="J1" s="10" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="B2" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="C2" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="D2" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="F2">
         <v>12</v>
@@ -16865,24 +16954,24 @@
         <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="J2" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="B3" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="C3" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
       <c r="D3" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="F3">
         <v>12</v>
@@ -16891,21 +16980,21 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="B4" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="C4" t="s">
-        <v>1237</v>
+        <v>1231</v>
       </c>
       <c r="D4" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="F4">
         <v>12</v>
@@ -16914,21 +17003,21 @@
         <v>2</v>
       </c>
       <c r="H4" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="B5" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C5" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="D5" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="F5">
         <v>12</v>
@@ -16937,24 +17026,24 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="J5" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B6" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="C6" t="s">
-        <v>1238</v>
+        <v>1232</v>
       </c>
       <c r="D6" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="F6">
         <v>12</v>
@@ -16963,21 +17052,21 @@
         <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B7" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="C7" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="D7" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -16986,21 +17075,21 @@
         <v>2</v>
       </c>
       <c r="H7" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B8" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="C8" t="s">
-        <v>1240</v>
+        <v>1234</v>
       </c>
       <c r="D8" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="F8">
         <v>12</v>
@@ -17009,21 +17098,21 @@
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B9" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="C9" t="s">
-        <v>1241</v>
+        <v>1235</v>
       </c>
       <c r="D9" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F9">
         <v>12</v>
@@ -17032,21 +17121,21 @@
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B10" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="C10" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="D10" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F10">
         <v>12</v>
@@ -17055,21 +17144,21 @@
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B11" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="C11" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="D11" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F11">
         <v>12</v>
@@ -17078,24 +17167,24 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="J11" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B12" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="C12" t="s">
-        <v>1244</v>
+        <v>1238</v>
       </c>
       <c r="D12" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F12">
         <v>12</v>
@@ -17104,24 +17193,24 @@
         <v>2</v>
       </c>
       <c r="H12" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="J12" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B13" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="C13" t="s">
-        <v>1245</v>
+        <v>1239</v>
       </c>
       <c r="D13" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -17130,24 +17219,24 @@
         <v>2</v>
       </c>
       <c r="H13" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="J13" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B14" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="C14" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
       <c r="D14" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F14">
         <v>12</v>
@@ -17156,24 +17245,24 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="J14" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B15" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="C15" t="s">
-        <v>1247</v>
+        <v>1241</v>
       </c>
       <c r="D15" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F15">
         <v>12</v>
@@ -17182,21 +17271,21 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B16" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="C16" t="s">
-        <v>1248</v>
+        <v>1242</v>
       </c>
       <c r="D16" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F16">
         <v>12</v>
@@ -17205,21 +17294,21 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B17" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="C17" t="s">
-        <v>1249</v>
+        <v>1243</v>
       </c>
       <c r="D17" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F17">
         <v>12</v>
@@ -17228,21 +17317,21 @@
         <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B18" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="C18" t="s">
-        <v>1250</v>
+        <v>1244</v>
       </c>
       <c r="D18" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F18">
         <v>12</v>
@@ -17251,21 +17340,21 @@
         <v>2</v>
       </c>
       <c r="H18" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B19" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="C19" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="D19" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F19">
         <v>12</v>
@@ -17274,21 +17363,21 @@
         <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B20" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="C20" t="s">
-        <v>1252</v>
+        <v>1246</v>
       </c>
       <c r="D20" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="F20">
         <v>12</v>
@@ -17297,21 +17386,21 @@
         <v>2</v>
       </c>
       <c r="H20" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B21" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="C21" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="D21" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F21">
         <v>12</v>
@@ -17320,24 +17409,24 @@
         <v>2</v>
       </c>
       <c r="H21" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="J21" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B22" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="C22" t="s">
-        <v>1254</v>
+        <v>1248</v>
       </c>
       <c r="D22" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F22">
         <v>12</v>
@@ -17346,21 +17435,21 @@
         <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B23" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="C23" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
       <c r="D23" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="F23">
         <v>12</v>
@@ -17369,24 +17458,24 @@
         <v>2</v>
       </c>
       <c r="H23" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="J23" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B24" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="C24" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="D24" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="F24">
         <v>12</v>
@@ -17395,24 +17484,24 @@
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="J24" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B25" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="C25" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
       <c r="D25" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="F25">
         <v>12</v>
@@ -17421,24 +17510,24 @@
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="J25" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B26" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="C26" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="D26" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="F26">
         <v>12</v>
@@ -17447,102 +17536,93 @@
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="J26" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B27" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C27" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="D27" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="F27">
         <v>12</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" t="s">
-        <v>1003</v>
-      </c>
-      <c r="J27" t="s">
-        <v>1085</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B28" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C28" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="D28" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="F28">
         <v>12</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" t="s">
-        <v>1003</v>
-      </c>
-      <c r="J28" t="s">
-        <v>1087</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B29" t="s">
         <v>1088</v>
       </c>
       <c r="C29" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="D29" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="F29">
         <v>12</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" t="s">
-        <v>1003</v>
-      </c>
-      <c r="J29" t="s">
-        <v>1089</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B30" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C30" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="D30" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="F30">
         <v>12</v>
@@ -17551,21 +17631,21 @@
         <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B31" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C31" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="D31" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="F31">
         <v>12</v>
@@ -17574,21 +17654,24 @@
         <v>2</v>
       </c>
       <c r="H31" t="s">
-        <v>1003</v>
+        <v>1001</v>
+      </c>
+      <c r="J31" t="s">
+        <v>1091</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B32" t="s">
         <v>1092</v>
       </c>
       <c r="C32" t="s">
-        <v>1264</v>
+        <v>1093</v>
       </c>
       <c r="D32" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="F32">
         <v>12</v>
@@ -17597,7 +17680,10 @@
         <v>2</v>
       </c>
       <c r="H32" t="s">
-        <v>1003</v>
+        <v>1001</v>
+      </c>
+      <c r="J32" t="s">
+        <v>1093</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -17605,13 +17691,13 @@
         <v>1022</v>
       </c>
       <c r="B33" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C33" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="D33" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="F33">
         <v>12</v>
@@ -17620,7 +17706,10 @@
         <v>2</v>
       </c>
       <c r="H33" t="s">
-        <v>1003</v>
+        <v>1001</v>
+      </c>
+      <c r="J33" t="s">
+        <v>1024</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -17628,13 +17717,13 @@
         <v>1022</v>
       </c>
       <c r="B34" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C34" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="D34" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="F34">
         <v>12</v>
@@ -17643,10 +17732,7 @@
         <v>2</v>
       </c>
       <c r="H34" t="s">
-        <v>1003</v>
-      </c>
-      <c r="J34" t="s">
-        <v>1095</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -17657,10 +17743,10 @@
         <v>1096</v>
       </c>
       <c r="C35" t="s">
-        <v>1097</v>
+        <v>1263</v>
       </c>
       <c r="D35" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="F35">
         <v>12</v>
@@ -17669,99 +17755,102 @@
         <v>2</v>
       </c>
       <c r="H35" t="s">
-        <v>1003</v>
-      </c>
-      <c r="J35" t="s">
-        <v>1097</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B36" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D36" t="s">
         <v>1098</v>
       </c>
-      <c r="C36" t="s">
-        <v>1267</v>
-      </c>
-      <c r="D36" t="s">
-        <v>1062</v>
+      <c r="E36" t="s">
+        <v>1099</v>
       </c>
       <c r="F36">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="J36" t="s">
-        <v>1028</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B37" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="C37" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="D37" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F37">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" t="s">
-        <v>1003</v>
+        <v>1008</v>
+      </c>
+      <c r="J37" t="s">
+        <v>1102</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B38" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="C38" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="D38" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="F38">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>1003</v>
+        <v>1008</v>
+      </c>
+      <c r="J38" t="s">
+        <v>1102</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="B39" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="C39" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="D39" t="s">
-        <v>1102</v>
-      </c>
-      <c r="E39" t="s">
-        <v>1103</v>
+        <v>1046</v>
       </c>
       <c r="F39">
         <v>10</v>
@@ -17770,24 +17859,21 @@
         <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>1010</v>
-      </c>
-      <c r="J39" t="s">
-        <v>1104</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="B40" t="s">
         <v>1105</v>
       </c>
       <c r="C40" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="D40" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="F40">
         <v>10</v>
@@ -17796,122 +17882,116 @@
         <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>1010</v>
-      </c>
-      <c r="J40" t="s">
-        <v>1106</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="B41" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="C41" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="D41" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="F41">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G41">
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="J41" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B42" t="s">
         <v>1108</v>
       </c>
       <c r="C42" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="D42" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="F42">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G42">
         <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B43" t="s">
         <v>1109</v>
       </c>
       <c r="C43" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="D43" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="F43">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G43">
         <v>1</v>
       </c>
       <c r="H43" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B44" t="s">
         <v>1110</v>
       </c>
       <c r="C44" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="D44" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="F44">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
       <c r="H44" t="s">
-        <v>1010</v>
-      </c>
-      <c r="J44" t="s">
-        <v>1111</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="B45" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C45" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="D45" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F45">
         <v>24</v>
@@ -17920,21 +18000,21 @@
         <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="B46" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="C46" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="D46" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F46">
         <v>24</v>
@@ -17943,21 +18023,21 @@
         <v>1</v>
       </c>
       <c r="H46" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="B47" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C47" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="D47" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F47">
         <v>24</v>
@@ -17966,93 +18046,102 @@
         <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B48" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E48" t="s">
         <v>1115</v>
       </c>
-      <c r="C48" t="s">
-        <v>1279</v>
-      </c>
-      <c r="D48" t="s">
-        <v>1062</v>
-      </c>
       <c r="F48">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G48">
         <v>1</v>
       </c>
       <c r="H48" t="s">
-        <v>1010</v>
+        <v>1008</v>
+      </c>
+      <c r="J48" t="s">
+        <v>1116</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B49" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C49" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="D49" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F49">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G49">
         <v>1</v>
       </c>
       <c r="H49" t="s">
-        <v>1010</v>
+        <v>1008</v>
+      </c>
+      <c r="J49" t="s">
+        <v>1118</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B50" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="C50" t="s">
-        <v>1281</v>
+        <v>1120</v>
       </c>
       <c r="D50" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="F50">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G50">
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>1010</v>
+        <v>1008</v>
+      </c>
+      <c r="J50" t="s">
+        <v>1120</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="B51" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="C51" t="s">
-        <v>1282</v>
+        <v>1122</v>
       </c>
       <c r="D51" t="s">
-        <v>1102</v>
-      </c>
-      <c r="E51" t="s">
-        <v>1119</v>
+        <v>1058</v>
       </c>
       <c r="F51">
         <v>12</v>
@@ -18061,272 +18150,272 @@
         <v>1</v>
       </c>
       <c r="H51" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="J51" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B52" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="C52" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="D52" t="s">
-        <v>1062</v>
+        <v>1098</v>
+      </c>
+      <c r="E52" t="s">
+        <v>1124</v>
       </c>
       <c r="F52">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G52">
         <v>1</v>
       </c>
       <c r="H52" t="s">
-        <v>1010</v>
+        <v>1008</v>
+      </c>
+      <c r="I52" t="s">
+        <v>1125</v>
       </c>
       <c r="J52" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B53" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="C53" t="s">
-        <v>1124</v>
+        <v>1279</v>
       </c>
       <c r="D53" t="s">
-        <v>1050</v>
-      </c>
-      <c r="F53">
-        <v>12</v>
+        <v>1058</v>
       </c>
       <c r="G53">
         <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="J53" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B54" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="C54" t="s">
-        <v>1126</v>
+        <v>1280</v>
       </c>
       <c r="D54" t="s">
-        <v>1062</v>
-      </c>
-      <c r="F54">
-        <v>12</v>
+        <v>1058</v>
       </c>
       <c r="G54">
         <v>1</v>
       </c>
       <c r="H54" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="J54" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="B55" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="C55" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="D55" t="s">
-        <v>1102</v>
-      </c>
-      <c r="E55" t="s">
-        <v>1128</v>
-      </c>
-      <c r="F55">
-        <v>6</v>
+        <v>1058</v>
       </c>
       <c r="G55">
         <v>1</v>
       </c>
       <c r="H55" t="s">
-        <v>1010</v>
-      </c>
-      <c r="I55" t="s">
-        <v>1129</v>
+        <v>1008</v>
       </c>
       <c r="J55" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="B56" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="C56" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="D56" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="G56">
         <v>1</v>
       </c>
       <c r="H56" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="J56" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="B57" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="C57" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="D57" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="G57">
         <v>1</v>
       </c>
       <c r="H57" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="J57" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="B58" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="C58" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="D58" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="G58">
         <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="J58" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="B59" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="C59" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="D59" t="s">
-        <v>1050</v>
+        <v>1222</v>
+      </c>
+      <c r="F59">
+        <v>12</v>
       </c>
       <c r="G59">
         <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="J59" t="s">
-        <v>1138</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>1041</v>
+        <v>1297</v>
       </c>
       <c r="B60" t="s">
-        <v>1139</v>
+        <v>1078</v>
       </c>
       <c r="C60" t="s">
-        <v>1289</v>
+        <v>1252</v>
       </c>
       <c r="D60" t="s">
-        <v>1062</v>
+        <v>1046</v>
+      </c>
+      <c r="F60">
+        <v>12</v>
       </c>
       <c r="G60">
         <v>1</v>
       </c>
       <c r="H60" t="s">
-        <v>1010</v>
+        <v>1001</v>
       </c>
       <c r="J60" t="s">
-        <v>1140</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>1041</v>
+        <v>1297</v>
       </c>
       <c r="B61" t="s">
-        <v>1141</v>
+        <v>1080</v>
       </c>
       <c r="C61" t="s">
-        <v>1290</v>
+        <v>1253</v>
       </c>
       <c r="D61" t="s">
-        <v>1062</v>
+        <v>1046</v>
+      </c>
+      <c r="F61">
+        <v>12</v>
       </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="H61" t="s">
-        <v>1010</v>
+        <v>1001</v>
       </c>
       <c r="J61" t="s">
-        <v>1142</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>1042</v>
+        <v>1297</v>
       </c>
       <c r="B62" t="s">
-        <v>1143</v>
+        <v>1082</v>
       </c>
       <c r="C62" t="s">
-        <v>1291</v>
+        <v>1254</v>
       </c>
       <c r="D62" t="s">
-        <v>1228</v>
+        <v>1046</v>
       </c>
       <c r="F62">
         <v>12</v>
@@ -18335,14 +18424,17 @@
         <v>1</v>
       </c>
       <c r="H62" t="s">
-        <v>1010</v>
+        <v>1001</v>
       </c>
       <c r="J62" t="s">
-        <v>1229</v>
+        <v>1083</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1" xr:uid="{84C9ADE8-E8E1-442A-91BD-AA392C318296}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J62">
+    <sortCondition ref="A2"/>
+  </sortState>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18369,16 +18461,16 @@
         <v>18</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -18389,13 +18481,13 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="E2" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F2" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -18406,16 +18498,16 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="D3" t="s">
         <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F3" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -18426,16 +18518,16 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="D4" t="s">
         <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F4" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -18446,16 +18538,16 @@
         <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F5" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -18466,16 +18558,16 @@
         <v>33</v>
       </c>
       <c r="C6" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F6" t="s">
         <v>1152</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1155</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1146</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -18486,16 +18578,16 @@
         <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="D7" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="E7" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="F7" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -18506,16 +18598,16 @@
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="D8" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="E8" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F8" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -18526,16 +18618,16 @@
         <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="D9" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="E9" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F9" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -18546,13 +18638,13 @@
         <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="E10" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F10" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -18563,16 +18655,16 @@
         <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="D11" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="E11" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F11" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -18583,16 +18675,16 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="D12" t="s">
         <v>52</v>
       </c>
       <c r="E12" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="F12" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -18600,19 +18692,19 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C13" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="D13" t="s">
-        <v>1168</v>
+        <v>1299</v>
       </c>
       <c r="E13" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="F13" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -18623,13 +18715,13 @@
         <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="E14" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F14" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -18640,13 +18732,13 @@
         <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="E15" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="F15" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -18657,13 +18749,13 @@
         <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="E16" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="F16" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -18674,13 +18766,13 @@
         <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="E17" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="F17" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -18691,16 +18783,16 @@
         <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="D18" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="E18" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F18" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -18711,16 +18803,16 @@
         <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="D19" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
       <c r="E19" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F19" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -18731,446 +18823,446 @@
         <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="E20" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="F20" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="B21" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C21" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="D21" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
       <c r="E21" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F21" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="B22" t="s">
         <v>725</v>
       </c>
       <c r="C22" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="E22" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F22" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B23" t="s">
+        <v>992</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F23" t="s">
         <v>1179</v>
-      </c>
-      <c r="B23" t="s">
-        <v>994</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1152</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1183</v>
-      </c>
-      <c r="E23" t="s">
-        <v>1146</v>
-      </c>
-      <c r="F23" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="B24" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="C24" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="D24" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="E24" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F24" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="B25" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C25" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="D25" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="E25" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F25" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="B26" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C26" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="D26" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="E26" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F26" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="B27" t="s">
         <v>727</v>
       </c>
       <c r="C27" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="E27" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="F27" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="B28" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="C28" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="D28" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="E28" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="F28" t="s">
-        <v>1191</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="B29" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="C29" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="D29" t="s">
-        <v>1192</v>
+        <v>1300</v>
       </c>
       <c r="E29" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="F29" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="B30" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C30" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="E30" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="F30" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="B31" t="s">
         <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="E31" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F31" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="B32" t="s">
         <v>728</v>
       </c>
       <c r="C32" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="D32" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
       <c r="E32" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F32" t="s">
-        <v>1197</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="B33" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C33" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="E33" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="F33" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="B34" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C34" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="D34" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
       <c r="E34" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F34" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="B35" t="s">
         <v>726</v>
       </c>
       <c r="C35" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="D35" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="E35" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F35" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="B36" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="C36" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="E36" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F36" t="s">
-        <v>1292</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="B37" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="C37" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="D37" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="E37" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F37" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E38" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F38" t="s">
         <v>1199</v>
-      </c>
-      <c r="B38" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C38" t="s">
-        <v>1150</v>
-      </c>
-      <c r="D38" t="s">
-        <v>1201</v>
-      </c>
-      <c r="E38" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F38" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="B39" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="C39" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="E39" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="F39" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="B40" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="C40" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="E40" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="F40" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="B41" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="C41" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="D41" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="E41" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="F41" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="B42" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="C42" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="D42" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="E42" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="F42" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="B43" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C43" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="E43" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="F43" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -19181,13 +19273,13 @@
         <v>78</v>
       </c>
       <c r="C44" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="D44" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
       <c r="E44" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="F44" t="s">
         <v>79</v>

--- a/outputs/mai-report-policy/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2D107C-A7F1-409E-A448-E9A6AE57CD57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A641A7-7C45-43FF-88AE-91A4343086CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38370" yWindow="-4030" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3966" uniqueCount="1301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3966" uniqueCount="1302">
   <si>
     <t>maiReport 식이 참조·설정 데이터 v1.0.0 | 2026-09-22</t>
   </si>
@@ -3756,10 +3756,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>삼킴이 어려운 상태에서는 음식의 양·속도·질감을 개인 평가 없이 자동으로 권하지 않는다</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>상세기획이 연하장애를 보호 대상으로 적고 있어 1차에 둔다. 인지장애(F00~F03 · G30)는 뺐다 — 치매 자체가 식이 목표의 금기가 아니고 후기의 삼킴 문제는 R13으로 잡힌다. 뇌졸중 경로는 DX-06이 일부 잡는다</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -3969,9 +3965,6 @@
     <t>뇌혈관질환(뇌졸중 등)</t>
   </si>
   <si>
-    <t>연하·기능 상태를 확인하기 전에는 음식의 질감과 도구를 요구하는 목표를 내지 않는다</t>
-  </si>
-  <si>
     <t>심장질환(DX-06)에서 분리했다. 연하곤란이 함께 코딩되면 DX-20도 같이 걸린다</t>
   </si>
   <si>
@@ -3979,15 +3972,27 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>감량;공복;증량;질감</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>감량 · 공복 · 증량 · 수분 · 질감 또는 빈칸</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>감량 · 공복 · 증량 · 수분 · 질감 세미콜론 구분</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>질감;수분</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>연하·기능 상태를 확인하기 전에는 음식의 질감과 도구를 요구하는 목표를 내지 않는다. 뇌졸중 뒤 삼킴 장애에서는 묽은 액체가 기도로 넘어가기 쉬워 물·차 권유도 막는다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>감량;공복;증량;질감;수분</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼킴이 어려운 상태에서는 음식의 양·속도·질감을 개인 평가 없이 자동으로 권하지 않는다. 묽은 액체는 후두가 닫히기 전에 기도로 넘어가기 쉬워 물·차 권유도 막는다</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -6344,7 +6349,7 @@
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>118</v>
@@ -8224,7 +8229,7 @@
       </c>
       <c r="K58" s="1"/>
       <c r="L58" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="M58" s="1" t="s">
         <v>143</v>
@@ -8282,7 +8287,7 @@
       </c>
       <c r="K59" s="1"/>
       <c r="L59" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="M59" s="1" t="s">
         <v>143</v>
@@ -10242,7 +10247,7 @@
       </c>
       <c r="K93" s="1"/>
       <c r="L93" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="M93" s="1" t="s">
         <v>118</v>
@@ -12470,7 +12475,7 @@
       </c>
       <c r="K132" s="1"/>
       <c r="L132" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="M132" s="1" t="s">
         <v>194</v>
@@ -12700,7 +12705,7 @@
       </c>
       <c r="K136" s="1"/>
       <c r="L136" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="M136" s="1" t="s">
         <v>98</v>
@@ -13220,7 +13225,7 @@
       </c>
       <c r="K145" s="1"/>
       <c r="L145" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="M145" s="1" t="s">
         <v>98</v>
@@ -13682,7 +13687,7 @@
       </c>
       <c r="K153" s="1"/>
       <c r="L153" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="M153" s="1" t="s">
         <v>98</v>
@@ -16523,7 +16528,7 @@
         <v>1020</v>
       </c>
       <c r="B7" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
@@ -16538,7 +16543,7 @@
         <v>1001</v>
       </c>
       <c r="G7" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="H7" t="s">
         <v>1021</v>
@@ -16547,7 +16552,7 @@
         <v>988</v>
       </c>
       <c r="J7" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="K7" t="s">
         <v>738</v>
@@ -16556,15 +16561,15 @@
         <v>1005</v>
       </c>
       <c r="M7" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B8" t="s">
         <v>1292</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1293</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
@@ -16579,16 +16584,16 @@
         <v>1001</v>
       </c>
       <c r="G8" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H8" t="s">
         <v>1021</v>
       </c>
       <c r="I8" t="s">
-        <v>1287</v>
+        <v>1298</v>
       </c>
       <c r="J8" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="K8" t="s">
         <v>738</v>
@@ -16597,7 +16602,7 @@
         <v>1005</v>
       </c>
       <c r="M8" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -16865,10 +16870,10 @@
         <v>1008</v>
       </c>
       <c r="I16" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="J16" t="s">
-        <v>1226</v>
+        <v>1301</v>
       </c>
       <c r="K16" t="s">
         <v>1028</v>
@@ -16877,7 +16882,7 @@
         <v>1005</v>
       </c>
       <c r="M16" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
   </sheetData>
@@ -16910,7 +16915,7 @@
         <v>726</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>1039</v>
@@ -16942,7 +16947,7 @@
         <v>1045</v>
       </c>
       <c r="C2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="D2" t="s">
         <v>1046</v>
@@ -16968,7 +16973,7 @@
         <v>1048</v>
       </c>
       <c r="C3" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="D3" t="s">
         <v>1046</v>
@@ -16991,7 +16996,7 @@
         <v>1049</v>
       </c>
       <c r="C4" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="D4" t="s">
         <v>1046</v>
@@ -17040,7 +17045,7 @@
         <v>1052</v>
       </c>
       <c r="C6" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="D6" t="s">
         <v>1046</v>
@@ -17063,7 +17068,7 @@
         <v>1053</v>
       </c>
       <c r="C7" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="D7" t="s">
         <v>1046</v>
@@ -17086,7 +17091,7 @@
         <v>1056</v>
       </c>
       <c r="C8" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="D8" t="s">
         <v>1046</v>
@@ -17109,7 +17114,7 @@
         <v>1057</v>
       </c>
       <c r="C9" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="D9" t="s">
         <v>1058</v>
@@ -17132,7 +17137,7 @@
         <v>1059</v>
       </c>
       <c r="C10" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="D10" t="s">
         <v>1058</v>
@@ -17155,7 +17160,7 @@
         <v>1060</v>
       </c>
       <c r="C11" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="D11" t="s">
         <v>1058</v>
@@ -17181,7 +17186,7 @@
         <v>1062</v>
       </c>
       <c r="C12" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="D12" t="s">
         <v>1058</v>
@@ -17207,7 +17212,7 @@
         <v>1064</v>
       </c>
       <c r="C13" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="D13" t="s">
         <v>1058</v>
@@ -17233,7 +17238,7 @@
         <v>1065</v>
       </c>
       <c r="C14" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="D14" t="s">
         <v>1058</v>
@@ -17259,7 +17264,7 @@
         <v>1067</v>
       </c>
       <c r="C15" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="D15" t="s">
         <v>1058</v>
@@ -17282,7 +17287,7 @@
         <v>1068</v>
       </c>
       <c r="C16" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="D16" t="s">
         <v>1058</v>
@@ -17305,7 +17310,7 @@
         <v>1069</v>
       </c>
       <c r="C17" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="D17" t="s">
         <v>1058</v>
@@ -17328,7 +17333,7 @@
         <v>1070</v>
       </c>
       <c r="C18" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="D18" t="s">
         <v>1058</v>
@@ -17351,7 +17356,7 @@
         <v>1071</v>
       </c>
       <c r="C19" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="D19" t="s">
         <v>1058</v>
@@ -17374,7 +17379,7 @@
         <v>1072</v>
       </c>
       <c r="C20" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="D20" t="s">
         <v>1046</v>
@@ -17397,7 +17402,7 @@
         <v>1073</v>
       </c>
       <c r="C21" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="D21" t="s">
         <v>1058</v>
@@ -17423,7 +17428,7 @@
         <v>1075</v>
       </c>
       <c r="C22" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="D22" t="s">
         <v>1058</v>
@@ -17446,7 +17451,7 @@
         <v>1054</v>
       </c>
       <c r="C23" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="D23" t="s">
         <v>1046</v>
@@ -17472,7 +17477,7 @@
         <v>1055</v>
       </c>
       <c r="C24" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="D24" t="s">
         <v>1046</v>
@@ -17498,7 +17503,7 @@
         <v>1076</v>
       </c>
       <c r="C25" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="D25" t="s">
         <v>1046</v>
@@ -17524,7 +17529,7 @@
         <v>1084</v>
       </c>
       <c r="C26" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="D26" t="s">
         <v>1058</v>
@@ -17550,7 +17555,7 @@
         <v>1086</v>
       </c>
       <c r="C27" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="D27" t="s">
         <v>1046</v>
@@ -17573,7 +17578,7 @@
         <v>1087</v>
       </c>
       <c r="C28" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="D28" t="s">
         <v>1046</v>
@@ -17596,7 +17601,7 @@
         <v>1088</v>
       </c>
       <c r="C29" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="D29" t="s">
         <v>1046</v>
@@ -17619,7 +17624,7 @@
         <v>1089</v>
       </c>
       <c r="C30" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="D30" t="s">
         <v>1046</v>
@@ -17642,7 +17647,7 @@
         <v>1090</v>
       </c>
       <c r="C31" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="D31" t="s">
         <v>1046</v>
@@ -17694,7 +17699,7 @@
         <v>1094</v>
       </c>
       <c r="C33" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="D33" t="s">
         <v>1058</v>
@@ -17720,7 +17725,7 @@
         <v>1095</v>
       </c>
       <c r="C34" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="D34" t="s">
         <v>1058</v>
@@ -17743,7 +17748,7 @@
         <v>1096</v>
       </c>
       <c r="C35" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D35" t="s">
         <v>1058</v>
@@ -17766,7 +17771,7 @@
         <v>1097</v>
       </c>
       <c r="C36" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D36" t="s">
         <v>1098</v>
@@ -17795,7 +17800,7 @@
         <v>1101</v>
       </c>
       <c r="C37" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="D37" t="s">
         <v>1058</v>
@@ -17821,7 +17826,7 @@
         <v>1103</v>
       </c>
       <c r="C38" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="D38" t="s">
         <v>1046</v>
@@ -17847,7 +17852,7 @@
         <v>1104</v>
       </c>
       <c r="C39" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="D39" t="s">
         <v>1046</v>
@@ -17870,7 +17875,7 @@
         <v>1105</v>
       </c>
       <c r="C40" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="D40" t="s">
         <v>1046</v>
@@ -17893,7 +17898,7 @@
         <v>1106</v>
       </c>
       <c r="C41" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="D41" t="s">
         <v>1046</v>
@@ -17919,7 +17924,7 @@
         <v>1108</v>
       </c>
       <c r="C42" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="D42" t="s">
         <v>1058</v>
@@ -17942,7 +17947,7 @@
         <v>1109</v>
       </c>
       <c r="C43" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="D43" t="s">
         <v>1058</v>
@@ -17965,7 +17970,7 @@
         <v>1110</v>
       </c>
       <c r="C44" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="D44" t="s">
         <v>1058</v>
@@ -17988,7 +17993,7 @@
         <v>1111</v>
       </c>
       <c r="C45" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="D45" t="s">
         <v>1058</v>
@@ -18011,7 +18016,7 @@
         <v>1112</v>
       </c>
       <c r="C46" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="D46" t="s">
         <v>1058</v>
@@ -18034,7 +18039,7 @@
         <v>1113</v>
       </c>
       <c r="C47" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="D47" t="s">
         <v>1058</v>
@@ -18057,7 +18062,7 @@
         <v>1114</v>
       </c>
       <c r="C48" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="D48" t="s">
         <v>1098</v>
@@ -18086,7 +18091,7 @@
         <v>1117</v>
       </c>
       <c r="C49" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="D49" t="s">
         <v>1058</v>
@@ -18164,7 +18169,7 @@
         <v>1123</v>
       </c>
       <c r="C52" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D52" t="s">
         <v>1098</v>
@@ -18196,7 +18201,7 @@
         <v>1127</v>
       </c>
       <c r="C53" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="D53" t="s">
         <v>1058</v>
@@ -18219,7 +18224,7 @@
         <v>1129</v>
       </c>
       <c r="C54" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="D54" t="s">
         <v>1058</v>
@@ -18242,7 +18247,7 @@
         <v>1131</v>
       </c>
       <c r="C55" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="D55" t="s">
         <v>1058</v>
@@ -18265,7 +18270,7 @@
         <v>1133</v>
       </c>
       <c r="C56" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="D56" t="s">
         <v>1046</v>
@@ -18288,7 +18293,7 @@
         <v>1135</v>
       </c>
       <c r="C57" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="D57" t="s">
         <v>1058</v>
@@ -18311,7 +18316,7 @@
         <v>1137</v>
       </c>
       <c r="C58" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D58" t="s">
         <v>1058</v>
@@ -18334,7 +18339,7 @@
         <v>1139</v>
       </c>
       <c r="C59" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D59" t="s">
         <v>1222</v>
@@ -18354,13 +18359,13 @@
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="B60" t="s">
         <v>1078</v>
       </c>
       <c r="C60" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="D60" t="s">
         <v>1046</v>
@@ -18380,13 +18385,13 @@
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="B61" t="s">
         <v>1080</v>
       </c>
       <c r="C61" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="D61" t="s">
         <v>1046</v>
@@ -18406,13 +18411,13 @@
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="B62" t="s">
         <v>1082</v>
       </c>
       <c r="C62" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="D62" t="s">
         <v>1046</v>
@@ -18698,7 +18703,7 @@
         <v>1148</v>
       </c>
       <c r="D13" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="E13" t="s">
         <v>1154</v>
@@ -18997,7 +19002,7 @@
         <v>1148</v>
       </c>
       <c r="D29" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="E29" t="s">
         <v>1154</v>
@@ -19122,7 +19127,7 @@
         <v>1193</v>
       </c>
       <c r="B36" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C36" t="s">
         <v>1146</v>
@@ -19131,7 +19136,7 @@
         <v>1142</v>
       </c>
       <c r="F36" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="37" spans="1:6">

--- a/outputs/mai-report-policy/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A641A7-7C45-43FF-88AE-91A4343086CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456F2916-CAF1-4D22-B466-C8D2708E71A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38370" yWindow="-4030" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3966" uniqueCount="1302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3959" uniqueCount="1301">
   <si>
     <t>maiReport 식이 참조·설정 데이터 v1.0.0 | 2026-09-22</t>
   </si>
@@ -2350,15 +2350,9 @@
     <t>끼니 경계 1</t>
   </si>
   <si>
-    <t>12:00:00</t>
-  </si>
-  <si>
     <t>지난 끼니 = 어제 저녁 / 오늘 아침</t>
   </si>
   <si>
-    <t>오전 11시 알림 진입이 어제 저녁 구간에 들어와야 함</t>
-  </si>
-  <si>
     <t>끼니 경계 2</t>
   </si>
   <si>
@@ -2375,9 +2369,6 @@
   </si>
   <si>
     <t>지난 끼니 = 오늘 점심 / 오늘 저녁</t>
-  </si>
-  <si>
-    <t>심야 예외 판정 기준과 같은 값</t>
   </si>
   <si>
     <t>날짜</t>
@@ -3940,38 +3931,10 @@
     <t>질감</t>
   </si>
   <si>
-    <t>심장질환</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>심장질환(협심증 · 심근경색 · 심부전 등)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>심부전은 처방된 수분 계획이 우선이다</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>뇌혈관질환은 금지 성격이 달라 DX-21로 분리했다</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>DX-21</t>
-  </si>
-  <si>
-    <t>뇌혈관질환</t>
-  </si>
-  <si>
-    <t>뇌혈관질환(뇌졸중 등)</t>
-  </si>
-  <si>
-    <t>심장질환(DX-06)에서 분리했다. 연하곤란이 함께 코딩되면 DX-20도 같이 걸린다</t>
-  </si>
-  <si>
-    <t>DX-21</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>감량 · 공복 · 증량 · 수분 · 질감 또는 빈칸</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -3980,20 +3943,55 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>질감;수분</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>연하·기능 상태를 확인하기 전에는 음식의 질감과 도구를 요구하는 목표를 내지 않는다. 뇌졸중 뒤 삼킴 장애에서는 묽은 액체가 기도로 넘어가기 쉬워 물·차 권유도 막는다</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>감량;공복;증량;질감;수분</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>삼킴이 어려운 상태에서는 음식의 양·속도·질감을 개인 평가 없이 자동으로 권하지 않는다. 묽은 액체는 후두가 닫히기 전에 기도로 넘어가기 쉬워 물·차 권유도 막는다</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>심야 예외 판정 기준과 같은 값. 저녁을 먹었는지는 18시부터 고정 답으로 가른다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>시간대 표시 「저녁」 우선. 저녁을 먹었는지 묻는 분기도 이 시각부터 쓴다</t>
+  </si>
+  <si>
+    <t>저녁 여부 확인 시각</t>
+  </si>
+  <si>
+    <t>지난 끼니 판정 · 대상 끼니 판정</t>
+  </si>
+  <si>
+    <t>이 시각 이후 첫 진입은 고정 답으로 갈린다. 아직 저녁 전이면 오늘 저녁을 대상으로, 이미 먹었으면 오늘 밤을 대상으로 준비·정리 행동만 낸다</t>
+  </si>
+  <si>
+    <t>DX-06</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>심혈관질환</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>심장 · 뇌혈관 질환(협심증 · 심근경색 · 뇌졸중 등)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>수분</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>뇌졸중 자체는 삼킴 장애가 아니라 질감·수분을 걸지 않는다. 삼킴 문제가 있으면 연하곤란(R13)이 따로 코딩되어 DX-20이 잡는다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>오전 11시 알림 진입이 어제 저녁 구간에 들어와야 함. 사용자별 경계는 2차</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>12:00:00</t>
   </si>
 </sst>
 </file>
@@ -4104,7 +4102,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4145,6 +4143,17 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4456,7 +4465,7 @@
     </row>
     <row r="2" spans="1:3" ht="25.4" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -4482,7 +4491,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="C5" s="1">
         <v>171</v>
@@ -4493,7 +4502,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="C6" s="1">
         <v>8</v>
@@ -4501,21 +4510,21 @@
     </row>
     <row r="7" spans="1:3" ht="25.4" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="C7" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="25.4" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="C8" s="1">
         <v>61</v>
@@ -4529,16 +4538,15 @@
         <v>8</v>
       </c>
       <c r="C9" s="1">
-        <f>COUNTA(설정값!B2:B103)</f>
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="25.4" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="C10" s="11">
         <v>42</v>
@@ -4551,7 +4559,7 @@
     </row>
     <row r="12" spans="1:3" ht="25.4" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -4561,7 +4569,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="C13" s="1">
         <v>171</v>
@@ -4620,7 +4628,7 @@
     </row>
     <row r="21" spans="1:3" ht="25.4" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -4949,7 +4957,7 @@
         <v>86</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="C53" s="4"/>
     </row>
@@ -5013,7 +5021,7 @@
         <v>50</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="M1" s="6" t="s">
         <v>53</v>
@@ -5071,7 +5079,7 @@
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>98</v>
@@ -5129,7 +5137,7 @@
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>98</v>
@@ -5185,7 +5193,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>98</v>
@@ -5295,7 +5303,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>118</v>
@@ -5351,7 +5359,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>118</v>
@@ -5517,7 +5525,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>133</v>
@@ -5573,7 +5581,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>138</v>
@@ -5631,7 +5639,7 @@
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>143</v>
@@ -5687,7 +5695,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>138</v>
@@ -5743,7 +5751,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>138</v>
@@ -6069,7 +6077,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>166</v>
@@ -6125,7 +6133,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>118</v>
@@ -6181,7 +6189,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>118</v>
@@ -6237,7 +6245,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>118</v>
@@ -6293,7 +6301,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>98</v>
@@ -6349,7 +6357,7 @@
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>118</v>
@@ -6461,7 +6469,7 @@
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>98</v>
@@ -6517,7 +6525,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>98</v>
@@ -6575,7 +6583,7 @@
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>98</v>
@@ -6799,7 +6807,7 @@
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>221</v>
@@ -6913,7 +6921,7 @@
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>98</v>
@@ -6971,7 +6979,7 @@
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>98</v>
@@ -7085,7 +7093,7 @@
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>118</v>
@@ -7143,7 +7151,7 @@
       </c>
       <c r="K39" s="1"/>
       <c r="L39" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>118</v>
@@ -7201,7 +7209,7 @@
       </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>118</v>
@@ -7371,7 +7379,7 @@
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>138</v>
@@ -7485,7 +7493,7 @@
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>143</v>
@@ -7543,7 +7551,7 @@
       </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>138</v>
@@ -7657,7 +7665,7 @@
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>143</v>
@@ -7715,7 +7723,7 @@
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>143</v>
@@ -7829,7 +7837,7 @@
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>138</v>
@@ -7943,7 +7951,7 @@
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>118</v>
@@ -8001,7 +8009,7 @@
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>221</v>
@@ -8115,7 +8123,7 @@
       </c>
       <c r="K56" s="1"/>
       <c r="L56" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>118</v>
@@ -8229,7 +8237,7 @@
       </c>
       <c r="K58" s="1"/>
       <c r="L58" s="1" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="M58" s="1" t="s">
         <v>143</v>
@@ -8287,7 +8295,7 @@
       </c>
       <c r="K59" s="1"/>
       <c r="L59" s="1" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="M59" s="1" t="s">
         <v>143</v>
@@ -8345,7 +8353,7 @@
       </c>
       <c r="K60" s="1"/>
       <c r="L60" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M60" s="1" t="s">
         <v>143</v>
@@ -8459,7 +8467,7 @@
       </c>
       <c r="K62" s="1"/>
       <c r="L62" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="M62" s="1" t="s">
         <v>98</v>
@@ -8517,7 +8525,7 @@
       </c>
       <c r="K63" s="1"/>
       <c r="L63" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M63" s="1" t="s">
         <v>221</v>
@@ -8575,7 +8583,7 @@
       </c>
       <c r="K64" s="1"/>
       <c r="L64" s="1" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="M64" s="1" t="s">
         <v>138</v>
@@ -8633,7 +8641,7 @@
       </c>
       <c r="K65" s="1"/>
       <c r="L65" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M65" s="1" t="s">
         <v>98</v>
@@ -8691,7 +8699,7 @@
       </c>
       <c r="K66" s="1"/>
       <c r="L66" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M66" s="1" t="s">
         <v>98</v>
@@ -8749,7 +8757,7 @@
       </c>
       <c r="K67" s="1"/>
       <c r="L67" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M67" s="1" t="s">
         <v>98</v>
@@ -8863,7 +8871,7 @@
       </c>
       <c r="K69" s="1"/>
       <c r="L69" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M69" s="1" t="s">
         <v>98</v>
@@ -8921,7 +8929,7 @@
       </c>
       <c r="K70" s="1"/>
       <c r="L70" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M70" s="1" t="s">
         <v>118</v>
@@ -9035,7 +9043,7 @@
       </c>
       <c r="K72" s="1"/>
       <c r="L72" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M72" s="1" t="s">
         <v>118</v>
@@ -9093,7 +9101,7 @@
       </c>
       <c r="K73" s="1"/>
       <c r="L73" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M73" s="1" t="s">
         <v>194</v>
@@ -9207,7 +9215,7 @@
       </c>
       <c r="K75" s="1"/>
       <c r="L75" s="1" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>133</v>
@@ -9265,7 +9273,7 @@
       </c>
       <c r="K76" s="1"/>
       <c r="L76" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>133</v>
@@ -9323,7 +9331,7 @@
       </c>
       <c r="K77" s="1"/>
       <c r="L77" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M77" s="1" t="s">
         <v>98</v>
@@ -9381,7 +9389,7 @@
       </c>
       <c r="K78" s="1"/>
       <c r="L78" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M78" s="1" t="s">
         <v>143</v>
@@ -9439,7 +9447,7 @@
       </c>
       <c r="K79" s="1"/>
       <c r="L79" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M79" s="1" t="s">
         <v>98</v>
@@ -9497,7 +9505,7 @@
       </c>
       <c r="K80" s="1"/>
       <c r="L80" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M80" s="1" t="s">
         <v>98</v>
@@ -9555,7 +9563,7 @@
       </c>
       <c r="K81" s="1"/>
       <c r="L81" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M81" s="1" t="s">
         <v>98</v>
@@ -9669,7 +9677,7 @@
       </c>
       <c r="K83" s="1"/>
       <c r="L83" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M83" s="1" t="s">
         <v>143</v>
@@ -9727,7 +9735,7 @@
       </c>
       <c r="K84" s="1"/>
       <c r="L84" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M84" s="1" t="s">
         <v>143</v>
@@ -9841,7 +9849,7 @@
       </c>
       <c r="K86" s="1"/>
       <c r="L86" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="M86" s="1" t="s">
         <v>391</v>
@@ -9899,7 +9907,7 @@
       </c>
       <c r="K87" s="1"/>
       <c r="L87" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M87" s="1" t="s">
         <v>396</v>
@@ -9957,7 +9965,7 @@
       </c>
       <c r="K88" s="1"/>
       <c r="L88" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M88" s="1" t="s">
         <v>396</v>
@@ -10015,7 +10023,7 @@
       </c>
       <c r="K89" s="1"/>
       <c r="L89" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M89" s="1" t="s">
         <v>166</v>
@@ -10073,7 +10081,7 @@
       </c>
       <c r="K90" s="1"/>
       <c r="L90" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M90" s="1" t="s">
         <v>166</v>
@@ -10131,7 +10139,7 @@
       </c>
       <c r="K91" s="1"/>
       <c r="L91" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M91" s="1" t="s">
         <v>118</v>
@@ -10189,7 +10197,7 @@
       </c>
       <c r="K92" s="1"/>
       <c r="L92" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M92" s="1" t="s">
         <v>118</v>
@@ -10247,7 +10255,7 @@
       </c>
       <c r="K93" s="1"/>
       <c r="L93" s="1" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="M93" s="1" t="s">
         <v>118</v>
@@ -10305,7 +10313,7 @@
       </c>
       <c r="K94" s="1"/>
       <c r="L94" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M94" s="1" t="s">
         <v>118</v>
@@ -10643,7 +10651,7 @@
       </c>
       <c r="K100" s="1"/>
       <c r="L100" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M100" s="1" t="s">
         <v>98</v>
@@ -10701,7 +10709,7 @@
       </c>
       <c r="K101" s="1"/>
       <c r="L101" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M101" s="1" t="s">
         <v>98</v>
@@ -10871,7 +10879,7 @@
       </c>
       <c r="K104" s="1"/>
       <c r="L104" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M104" s="1" t="s">
         <v>118</v>
@@ -10985,7 +10993,7 @@
       </c>
       <c r="K106" s="1"/>
       <c r="L106" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M106" s="1" t="s">
         <v>118</v>
@@ -11043,7 +11051,7 @@
       </c>
       <c r="K107" s="1"/>
       <c r="L107" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M107" s="1" t="s">
         <v>118</v>
@@ -11157,7 +11165,7 @@
       </c>
       <c r="K109" s="1"/>
       <c r="L109" s="1" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="M109" s="1" t="s">
         <v>133</v>
@@ -11215,7 +11223,7 @@
       </c>
       <c r="K110" s="1"/>
       <c r="L110" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="M110" s="1" t="s">
         <v>98</v>
@@ -11329,7 +11337,7 @@
       </c>
       <c r="K112" s="1"/>
       <c r="L112" s="1" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="M112" s="1" t="s">
         <v>133</v>
@@ -11387,7 +11395,7 @@
       </c>
       <c r="K113" s="1"/>
       <c r="L113" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>138</v>
@@ -11445,7 +11453,7 @@
       </c>
       <c r="K114" s="1"/>
       <c r="L114" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="M114" s="1" t="s">
         <v>143</v>
@@ -11615,7 +11623,7 @@
       </c>
       <c r="K117" s="1"/>
       <c r="L117" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>98</v>
@@ -11729,7 +11737,7 @@
       </c>
       <c r="K119" s="1"/>
       <c r="L119" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="M119" s="1" t="s">
         <v>143</v>
@@ -11787,7 +11795,7 @@
       </c>
       <c r="K120" s="1"/>
       <c r="L120" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="M120" s="1" t="s">
         <v>138</v>
@@ -11845,7 +11853,7 @@
       </c>
       <c r="K121" s="1"/>
       <c r="L121" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="M121" s="1" t="s">
         <v>396</v>
@@ -12071,7 +12079,7 @@
       </c>
       <c r="K125" s="1"/>
       <c r="L125" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M125" s="1" t="s">
         <v>396</v>
@@ -12129,7 +12137,7 @@
       </c>
       <c r="K126" s="1"/>
       <c r="L126" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M126" s="1" t="s">
         <v>166</v>
@@ -12187,7 +12195,7 @@
       </c>
       <c r="K127" s="1"/>
       <c r="L127" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M127" s="1" t="s">
         <v>118</v>
@@ -12245,7 +12253,7 @@
       </c>
       <c r="K128" s="1"/>
       <c r="L128" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M128" s="1" t="s">
         <v>118</v>
@@ -12359,7 +12367,7 @@
       </c>
       <c r="K130" s="1"/>
       <c r="L130" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M130" s="1" t="s">
         <v>118</v>
@@ -12417,7 +12425,7 @@
       </c>
       <c r="K131" s="1"/>
       <c r="L131" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M131" s="1" t="s">
         <v>118</v>
@@ -12475,7 +12483,7 @@
       </c>
       <c r="K132" s="1"/>
       <c r="L132" s="1" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="M132" s="1" t="s">
         <v>194</v>
@@ -12533,7 +12541,7 @@
       </c>
       <c r="K133" s="1"/>
       <c r="L133" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M133" s="1" t="s">
         <v>98</v>
@@ -12647,7 +12655,7 @@
       </c>
       <c r="K135" s="1"/>
       <c r="L135" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M135" s="1" t="s">
         <v>98</v>
@@ -12705,7 +12713,7 @@
       </c>
       <c r="K136" s="1"/>
       <c r="L136" s="1" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="M136" s="1" t="s">
         <v>98</v>
@@ -12763,7 +12771,7 @@
       </c>
       <c r="K137" s="1"/>
       <c r="L137" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M137" s="1" t="s">
         <v>98</v>
@@ -12821,7 +12829,7 @@
       </c>
       <c r="K138" s="1"/>
       <c r="L138" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M138" s="1" t="s">
         <v>98</v>
@@ -12879,7 +12887,7 @@
       </c>
       <c r="K139" s="1"/>
       <c r="L139" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M139" s="1" t="s">
         <v>118</v>
@@ -12937,7 +12945,7 @@
       </c>
       <c r="K140" s="1"/>
       <c r="L140" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M140" s="1" t="s">
         <v>138</v>
@@ -12995,7 +13003,7 @@
       </c>
       <c r="K141" s="1"/>
       <c r="L141" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="M141" s="1" t="s">
         <v>166</v>
@@ -13109,7 +13117,7 @@
       </c>
       <c r="K143" s="1"/>
       <c r="L143" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M143" s="1" t="s">
         <v>118</v>
@@ -13167,7 +13175,7 @@
       </c>
       <c r="K144" s="1"/>
       <c r="L144" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="M144" s="1" t="s">
         <v>118</v>
@@ -13225,7 +13233,7 @@
       </c>
       <c r="K145" s="1"/>
       <c r="L145" s="1" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="M145" s="1" t="s">
         <v>98</v>
@@ -13339,7 +13347,7 @@
       </c>
       <c r="K147" s="1"/>
       <c r="L147" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M147" s="1" t="s">
         <v>396</v>
@@ -13397,7 +13405,7 @@
       </c>
       <c r="K148" s="1"/>
       <c r="L148" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M148" s="1" t="s">
         <v>118</v>
@@ -13455,7 +13463,7 @@
       </c>
       <c r="K149" s="1"/>
       <c r="L149" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M149" s="1" t="s">
         <v>118</v>
@@ -13513,7 +13521,7 @@
       </c>
       <c r="K150" s="1"/>
       <c r="L150" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M150" s="1" t="s">
         <v>118</v>
@@ -13571,7 +13579,7 @@
       </c>
       <c r="K151" s="1"/>
       <c r="L151" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M151" s="1" t="s">
         <v>118</v>
@@ -13629,7 +13637,7 @@
       </c>
       <c r="K152" s="1"/>
       <c r="L152" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="M152" s="1" t="s">
         <v>138</v>
@@ -13687,7 +13695,7 @@
       </c>
       <c r="K153" s="1"/>
       <c r="L153" s="1" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="M153" s="1" t="s">
         <v>98</v>
@@ -13745,7 +13753,7 @@
       </c>
       <c r="K154" s="1"/>
       <c r="L154" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M154" s="1" t="s">
         <v>118</v>
@@ -13803,7 +13811,7 @@
       </c>
       <c r="K155" s="1"/>
       <c r="L155" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M155" s="1" t="s">
         <v>143</v>
@@ -13917,7 +13925,7 @@
       </c>
       <c r="K157" s="1"/>
       <c r="L157" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="M157" s="1" t="s">
         <v>138</v>
@@ -14031,7 +14039,7 @@
       </c>
       <c r="K159" s="1"/>
       <c r="L159" s="1" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="M159" s="1" t="s">
         <v>133</v>
@@ -14145,7 +14153,7 @@
       </c>
       <c r="K161" s="1"/>
       <c r="L161" s="1" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="M161" s="1" t="s">
         <v>133</v>
@@ -14203,7 +14211,7 @@
       </c>
       <c r="K162" s="1"/>
       <c r="L162" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="M162" s="1" t="s">
         <v>143</v>
@@ -14359,13 +14367,13 @@
         <v>94</v>
       </c>
       <c r="G165" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="H165">
         <v>17</v>
       </c>
       <c r="I165" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="J165" t="s">
         <v>125</v>
@@ -14377,13 +14385,13 @@
         <v>99</v>
       </c>
       <c r="O165" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="P165" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="Q165" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="R165" t="s">
         <v>103</v>
@@ -14412,13 +14420,13 @@
         <v>104</v>
       </c>
       <c r="G166" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="H166">
         <v>14</v>
       </c>
       <c r="I166" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="J166" t="s">
         <v>125</v>
@@ -14430,13 +14438,13 @@
         <v>99</v>
       </c>
       <c r="O166" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="P166" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="Q166" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="R166" t="s">
         <v>103</v>
@@ -14465,13 +14473,13 @@
         <v>94</v>
       </c>
       <c r="G167" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="H167">
         <v>14</v>
       </c>
       <c r="I167" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="J167" t="s">
         <v>125</v>
@@ -14483,13 +14491,13 @@
         <v>99</v>
       </c>
       <c r="O167" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="P167" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="Q167" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="R167" t="s">
         <v>103</v>
@@ -14518,13 +14526,13 @@
         <v>104</v>
       </c>
       <c r="G168" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="H168">
         <v>14</v>
       </c>
       <c r="I168" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="J168" t="s">
         <v>125</v>
@@ -14536,13 +14544,13 @@
         <v>99</v>
       </c>
       <c r="O168" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="P168" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="Q168" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="R168" t="s">
         <v>103</v>
@@ -14571,13 +14579,13 @@
         <v>94</v>
       </c>
       <c r="G169" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="H169">
         <v>14</v>
       </c>
       <c r="I169" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="J169" t="s">
         <v>125</v>
@@ -14589,13 +14597,13 @@
         <v>99</v>
       </c>
       <c r="O169" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="P169" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="Q169" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="R169" t="s">
         <v>103</v>
@@ -14624,13 +14632,13 @@
         <v>104</v>
       </c>
       <c r="G170" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="H170">
         <v>15</v>
       </c>
       <c r="I170" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="J170" t="s">
         <v>125</v>
@@ -14642,13 +14650,13 @@
         <v>99</v>
       </c>
       <c r="O170" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="P170" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="Q170" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="R170" t="s">
         <v>103</v>
@@ -14677,13 +14685,13 @@
         <v>94</v>
       </c>
       <c r="G171" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="H171">
         <v>18</v>
       </c>
       <c r="I171" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="J171" t="s">
         <v>125</v>
@@ -14695,13 +14703,13 @@
         <v>99</v>
       </c>
       <c r="O171" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="P171" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="Q171" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="R171" t="s">
         <v>103</v>
@@ -14721,22 +14729,22 @@
         <v>9</v>
       </c>
       <c r="D172" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="E172" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="F172" t="s">
         <v>199</v>
       </c>
       <c r="G172" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="H172">
         <v>20</v>
       </c>
       <c r="I172" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="J172" t="s">
         <v>125</v>
@@ -14748,13 +14756,13 @@
         <v>99</v>
       </c>
       <c r="O172" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="P172" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="Q172" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="R172" t="s">
         <v>103</v>
@@ -15316,7 +15324,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="12.58203125" customWidth="1"/>
@@ -15363,7 +15371,7 @@
         <v>750</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>755</v>
@@ -15380,7 +15388,7 @@
         <v>750</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>756</v>
@@ -15397,16 +15405,16 @@
         <v>750</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>753</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="32">
@@ -15414,7 +15422,7 @@
         <v>750</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C6" s="1">
         <v>28</v>
@@ -15423,7 +15431,7 @@
         <v>757</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="32">
@@ -15431,7 +15439,7 @@
         <v>750</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
@@ -15440,7 +15448,7 @@
         <v>753</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="48">
@@ -15448,7 +15456,7 @@
         <v>750</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="C8" s="1">
         <v>7</v>
@@ -15457,7 +15465,7 @@
         <v>753</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="32">
@@ -15465,7 +15473,7 @@
         <v>750</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="C9" s="1">
         <v>84</v>
@@ -15474,7 +15482,7 @@
         <v>753</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -15518,14 +15526,14 @@
       <c r="B12" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="12" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>769</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>770</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="66" customHeight="1">
@@ -15533,13 +15541,13 @@
         <v>766</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>771</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>773</v>
       </c>
       <c r="E13" s="1"/>
     </row>
@@ -15548,403 +15556,405 @@
         <v>766</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>776</v>
-      </c>
       <c r="E14" s="1" t="s">
-        <v>777</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="66" customHeight="1">
       <c r="A15" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>779</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="66" customHeight="1">
       <c r="A16" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>786</v>
-      </c>
-      <c r="E16" s="1"/>
+      <c r="E16" s="1" t="s">
+        <v>1290</v>
+      </c>
     </row>
     <row r="17" spans="1:5" ht="66" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:5" ht="66" customHeight="1">
       <c r="A18" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>791</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>793</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="66" customHeight="1">
       <c r="A19" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>796</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>798</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="66" customHeight="1">
       <c r="A20" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>800</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>798</v>
-      </c>
       <c r="E20" s="1" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="66" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>803</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>804</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>805</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="66" customHeight="1">
       <c r="A22" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>808</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>809</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="66" customHeight="1">
       <c r="A23" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>812</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>810</v>
-      </c>
       <c r="E23" s="1" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="66" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>815</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>816</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>817</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="66" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>819</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>820</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="66" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="66" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="66" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="66" customHeight="1">
       <c r="A29" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>833</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>834</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>835</v>
-      </c>
       <c r="E29" s="1" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="66" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>836</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>837</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>838</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="66" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>840</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>841</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>842</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="66" customHeight="1">
       <c r="A32" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>845</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>846</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>847</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="66" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>849</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>850</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>851</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="66" customHeight="1">
       <c r="A34" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>854</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>855</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="66" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>858</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>859</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>860</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="66" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>862</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>863</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>864</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="66" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>866</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>868</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="66" customHeight="1">
@@ -15952,16 +15962,16 @@
         <v>641</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>867</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>869</v>
+      </c>
+      <c r="E38" s="4" t="s">
         <v>870</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>871</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>872</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="66" customHeight="1">
@@ -15969,16 +15979,16 @@
         <v>641</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C39" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="66" customHeight="1">
@@ -15986,16 +15996,16 @@
         <v>641</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="C40" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D40" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>875</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="66" customHeight="1">
@@ -16003,67 +16013,67 @@
         <v>641</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="66" customHeight="1">
       <c r="A42" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>882</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="E42" s="4" t="s">
         <v>883</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>884</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>885</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="66" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="E43" s="4" t="s">
         <v>887</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>888</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>889</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="66" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>891</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>892</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>893</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="66" customHeight="1">
@@ -16071,191 +16081,191 @@
         <v>36</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="C45" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="66" customHeight="1">
       <c r="A46" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>898</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>899</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>900</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>889</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="66" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>902</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>903</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>904</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="66" customHeight="1">
       <c r="A48" s="4" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="C48" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="66" customHeight="1">
       <c r="A49" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B49" s="4" t="s">
         <v>906</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>909</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>103</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="66" customHeight="1">
       <c r="A50" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="E50" s="4" t="s">
         <v>912</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>795</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="66" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>750</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="66" customHeight="1">
       <c r="A52" s="4" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B52" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="E52" s="4" t="s">
         <v>919</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>920</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>921</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="66" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>923</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>924</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>925</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="66" customHeight="1">
       <c r="A54" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>927</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>928</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>929</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="66" customHeight="1">
       <c r="A55" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>931</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>932</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>933</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>889</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="66" customHeight="1">
       <c r="A56" s="4" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>82</v>
@@ -16264,10 +16274,27 @@
         <v>1</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>937</v>
+        <v>934</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="66" customHeight="1">
+      <c r="A57" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>782</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>1293</v>
       </c>
     </row>
   </sheetData>
@@ -16278,7 +16305,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{216EACFD-C9FD-4000-8498-48312F82252B}">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="7.58203125" bestFit="1" customWidth="1"/>
@@ -16297,34 +16324,34 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="10" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>725</v>
       </c>
       <c r="C1" s="10" t="s">
+        <v>989</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>990</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>991</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>992</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>993</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>994</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>995</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>727</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="K1" s="10" t="s">
         <v>53</v>
@@ -16333,12 +16360,12 @@
         <v>728</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="B2" t="s">
         <v>729</v>
@@ -16347,39 +16374,39 @@
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="E2" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="F2" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="G2" t="s">
         <v>729</v>
       </c>
       <c r="H2" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="I2" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="K2" t="s">
         <v>730</v>
       </c>
       <c r="L2" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="M2" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B3" t="s">
         <v>731</v>
@@ -16388,33 +16415,33 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="E3" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="F3" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="G3" t="s">
         <v>731</v>
       </c>
       <c r="H3" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="K3" t="s">
         <v>732</v>
       </c>
       <c r="L3" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="M3" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B4" t="s">
         <v>733</v>
@@ -16423,68 +16450,68 @@
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="E4" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="F4" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="G4" t="s">
         <v>734</v>
       </c>
       <c r="H4" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="K4" t="s">
         <v>735</v>
       </c>
       <c r="L4" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="M4" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="B5" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="C5" t="s">
         <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="E5" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="F5" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="G5" t="s">
         <v>734</v>
       </c>
       <c r="H5" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="K5" t="s">
         <v>735</v>
       </c>
       <c r="L5" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="M5" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B6" t="s">
         <v>736</v>
@@ -16493,116 +16520,110 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="E6" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="F6" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="G6" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="H6" t="s">
         <v>695</v>
       </c>
       <c r="I6" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="J6" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="K6" t="s">
         <v>737</v>
       </c>
       <c r="L6" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="M6" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="B7" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="E7" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="F7" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="G7" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="H7" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="I7" t="s">
-        <v>988</v>
+        <v>1297</v>
       </c>
       <c r="J7" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="K7" t="s">
         <v>738</v>
       </c>
       <c r="L7" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="M7" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>1291</v>
+        <v>1019</v>
       </c>
       <c r="B8" t="s">
-        <v>1292</v>
+        <v>739</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="E8" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="F8" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="G8" t="s">
-        <v>1293</v>
+        <v>739</v>
       </c>
       <c r="H8" t="s">
+        <v>1020</v>
+      </c>
+      <c r="K8" t="s">
+        <v>740</v>
+      </c>
+      <c r="L8" t="s">
+        <v>1002</v>
+      </c>
+      <c r="M8" t="s">
         <v>1021</v>
-      </c>
-      <c r="I8" t="s">
-        <v>1298</v>
-      </c>
-      <c r="J8" t="s">
-        <v>1299</v>
-      </c>
-      <c r="K8" t="s">
-        <v>738</v>
-      </c>
-      <c r="L8" t="s">
-        <v>1005</v>
-      </c>
-      <c r="M8" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -16610,279 +16631,244 @@
         <v>1022</v>
       </c>
       <c r="B9" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="E9" t="s">
-        <v>1008</v>
+        <v>998</v>
       </c>
       <c r="F9" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G9" t="s">
-        <v>739</v>
-      </c>
-      <c r="H9" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I9" t="s">
         <v>1023</v>
       </c>
+      <c r="J9" t="s">
+        <v>1024</v>
+      </c>
       <c r="K9" t="s">
-        <v>740</v>
+        <v>1025</v>
       </c>
       <c r="L9" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="M9" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="B10" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="E10" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="F10" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="I10" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="J10" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="K10" t="s">
+        <v>1025</v>
+      </c>
+      <c r="L10" t="s">
+        <v>1002</v>
+      </c>
+      <c r="M10" t="s">
         <v>1028</v>
-      </c>
-      <c r="L10" t="s">
-        <v>1005</v>
-      </c>
-      <c r="M10" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B11" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C11" t="s">
         <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="E11" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="F11" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="I11" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="J11" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="K11" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="L11" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="M11" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B12" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="E12" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="F12" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="I12" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="J12" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="K12" t="s">
+        <v>1025</v>
+      </c>
+      <c r="L12" t="s">
+        <v>1002</v>
+      </c>
+      <c r="M12" t="s">
         <v>1028</v>
-      </c>
-      <c r="L12" t="s">
-        <v>1005</v>
-      </c>
-      <c r="M12" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B13" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="E13" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="F13" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="I13" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="J13" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="K13" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="L13" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="M13" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B14" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>1217</v>
       </c>
       <c r="D14" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="E14" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="F14" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="I14" t="s">
-        <v>1026</v>
+        <v>1015</v>
       </c>
       <c r="J14" t="s">
-        <v>1027</v>
+        <v>1016</v>
       </c>
       <c r="K14" t="s">
-        <v>1028</v>
+        <v>737</v>
       </c>
       <c r="L14" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="M14" t="s">
-        <v>1036</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B15" t="s">
-        <v>746</v>
+        <v>1222</v>
       </c>
       <c r="C15" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="D15" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="E15" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="F15" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="I15" t="s">
-        <v>1018</v>
+        <v>1287</v>
       </c>
       <c r="J15" t="s">
-        <v>1019</v>
+        <v>1288</v>
       </c>
       <c r="K15" t="s">
-        <v>737</v>
+        <v>1025</v>
       </c>
       <c r="L15" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="M15" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1225</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1219</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1008</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F16" t="s">
-        <v>1008</v>
-      </c>
-      <c r="I16" t="s">
-        <v>1300</v>
-      </c>
-      <c r="J16" t="s">
-        <v>1301</v>
-      </c>
-      <c r="K16" t="s">
-        <v>1028</v>
-      </c>
-      <c r="L16" t="s">
-        <v>1005</v>
-      </c>
-      <c r="M16" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
     </row>
   </sheetData>
@@ -16909,48 +16895,48 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="10" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>726</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="D1" s="10" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>1039</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>1040</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>1041</v>
       </c>
-      <c r="G1" s="10" t="s">
-        <v>1042</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>1043</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>1044</v>
-      </c>
       <c r="J1" s="10" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="B2" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="C2" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="D2" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F2">
         <v>12</v>
@@ -16959,24 +16945,24 @@
         <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="J2" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="B3" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="C3" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="D3" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F3">
         <v>12</v>
@@ -16985,21 +16971,21 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="B4" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="C4" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="D4" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F4">
         <v>12</v>
@@ -17008,21 +16994,21 @@
         <v>2</v>
       </c>
       <c r="H4" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="B5" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="C5" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="D5" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F5">
         <v>12</v>
@@ -17031,24 +17017,24 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="J5" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B6" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="C6" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="D6" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F6">
         <v>12</v>
@@ -17057,21 +17043,21 @@
         <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B7" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="C7" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="D7" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -17080,21 +17066,21 @@
         <v>2</v>
       </c>
       <c r="H7" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B8" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="C8" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="D8" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F8">
         <v>12</v>
@@ -17103,21 +17089,21 @@
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B9" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="C9" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="D9" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F9">
         <v>12</v>
@@ -17126,21 +17112,21 @@
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B10" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="C10" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="D10" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F10">
         <v>12</v>
@@ -17149,21 +17135,21 @@
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B11" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="C11" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="D11" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F11">
         <v>12</v>
@@ -17172,24 +17158,24 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="J11" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="B12" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="C12" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="D12" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F12">
         <v>12</v>
@@ -17198,24 +17184,24 @@
         <v>2</v>
       </c>
       <c r="H12" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="J12" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="B13" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="C13" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="D13" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -17224,24 +17210,24 @@
         <v>2</v>
       </c>
       <c r="H13" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="J13" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B14" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C14" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="D14" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F14">
         <v>12</v>
@@ -17250,24 +17236,24 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="J14" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B15" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="C15" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="D15" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F15">
         <v>12</v>
@@ -17276,21 +17262,21 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B16" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="C16" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="D16" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F16">
         <v>12</v>
@@ -17299,21 +17285,21 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B17" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="C17" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="D17" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F17">
         <v>12</v>
@@ -17322,21 +17308,21 @@
         <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B18" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="C18" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="D18" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F18">
         <v>12</v>
@@ -17345,21 +17331,21 @@
         <v>2</v>
       </c>
       <c r="H18" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B19" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="C19" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="D19" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F19">
         <v>12</v>
@@ -17368,21 +17354,21 @@
         <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B20" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="C20" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="D20" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F20">
         <v>12</v>
@@ -17391,21 +17377,21 @@
         <v>2</v>
       </c>
       <c r="H20" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B21" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="C21" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="D21" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F21">
         <v>12</v>
@@ -17414,24 +17400,24 @@
         <v>2</v>
       </c>
       <c r="H21" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="J21" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B22" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="C22" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="D22" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F22">
         <v>12</v>
@@ -17440,21 +17426,21 @@
         <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B23" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="C23" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="D23" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F23">
         <v>12</v>
@@ -17463,24 +17449,24 @@
         <v>2</v>
       </c>
       <c r="H23" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="J23" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B24" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="C24" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="D24" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F24">
         <v>12</v>
@@ -17489,24 +17475,24 @@
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="J24" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="B25" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="C25" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="D25" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F25">
         <v>12</v>
@@ -17515,24 +17501,24 @@
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="J25" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="B26" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="C26" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="D26" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F26">
         <v>12</v>
@@ -17541,24 +17527,24 @@
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="J26" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="B27" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="C27" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="D27" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F27">
         <v>12</v>
@@ -17567,21 +17553,21 @@
         <v>2</v>
       </c>
       <c r="H27" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="B28" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="C28" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="D28" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F28">
         <v>12</v>
@@ -17590,21 +17576,21 @@
         <v>2</v>
       </c>
       <c r="H28" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="B29" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="C29" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="D29" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F29">
         <v>12</v>
@@ -17613,21 +17599,21 @@
         <v>2</v>
       </c>
       <c r="H29" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="B30" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="C30" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="D30" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F30">
         <v>12</v>
@@ -17636,21 +17622,21 @@
         <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="B31" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="C31" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="D31" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F31">
         <v>12</v>
@@ -17659,24 +17645,24 @@
         <v>2</v>
       </c>
       <c r="H31" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="J31" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="B32" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="C32" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="D32" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F32">
         <v>12</v>
@@ -17685,177 +17671,177 @@
         <v>2</v>
       </c>
       <c r="H32" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="J32" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>1022</v>
+        <v>1294</v>
       </c>
       <c r="B33" t="s">
-        <v>1094</v>
+        <v>1075</v>
       </c>
       <c r="C33" t="s">
-        <v>1260</v>
+        <v>1248</v>
       </c>
       <c r="D33" t="s">
-        <v>1058</v>
+        <v>1043</v>
       </c>
       <c r="F33">
         <v>12</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="J33" t="s">
-        <v>1024</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>1022</v>
+        <v>1294</v>
       </c>
       <c r="B34" t="s">
-        <v>1095</v>
+        <v>1077</v>
       </c>
       <c r="C34" t="s">
-        <v>1261</v>
+        <v>1249</v>
       </c>
       <c r="D34" t="s">
-        <v>1058</v>
+        <v>1043</v>
       </c>
       <c r="F34">
         <v>12</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>1001</v>
+        <v>998</v>
+      </c>
+      <c r="J34" t="s">
+        <v>1078</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>1022</v>
+        <v>1294</v>
       </c>
       <c r="B35" t="s">
-        <v>1096</v>
+        <v>1079</v>
       </c>
       <c r="C35" t="s">
-        <v>1262</v>
+        <v>1250</v>
       </c>
       <c r="D35" t="s">
-        <v>1058</v>
+        <v>1043</v>
       </c>
       <c r="F35">
         <v>12</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>1001</v>
+        <v>998</v>
+      </c>
+      <c r="J35" t="s">
+        <v>1080</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="B36" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
       <c r="C36" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="D36" t="s">
-        <v>1098</v>
-      </c>
-      <c r="E36" t="s">
-        <v>1099</v>
+        <v>1055</v>
       </c>
       <c r="F36">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" t="s">
-        <v>1008</v>
+        <v>998</v>
       </c>
       <c r="J36" t="s">
-        <v>1100</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="B37" t="s">
-        <v>1101</v>
+        <v>1092</v>
       </c>
       <c r="C37" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
       <c r="D37" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" t="s">
-        <v>1008</v>
-      </c>
-      <c r="J37" t="s">
-        <v>1102</v>
+        <v>998</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="B38" t="s">
-        <v>1103</v>
+        <v>1093</v>
       </c>
       <c r="C38" t="s">
-        <v>1265</v>
+        <v>1259</v>
       </c>
       <c r="D38" t="s">
-        <v>1046</v>
+        <v>1055</v>
       </c>
       <c r="F38">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="s">
-        <v>1008</v>
-      </c>
-      <c r="J38" t="s">
-        <v>1102</v>
+        <v>998</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="B39" t="s">
-        <v>1104</v>
+        <v>1094</v>
       </c>
       <c r="C39" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="D39" t="s">
-        <v>1046</v>
+        <v>1095</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1096</v>
       </c>
       <c r="F39">
         <v>10</v>
@@ -17864,21 +17850,24 @@
         <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>1008</v>
+        <v>1005</v>
+      </c>
+      <c r="J39" t="s">
+        <v>1097</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="B40" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
       <c r="C40" t="s">
-        <v>1267</v>
+        <v>1261</v>
       </c>
       <c r="D40" t="s">
-        <v>1046</v>
+        <v>1055</v>
       </c>
       <c r="F40">
         <v>10</v>
@@ -17887,116 +17876,122 @@
         <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>1008</v>
+        <v>1005</v>
+      </c>
+      <c r="J40" t="s">
+        <v>1099</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="B41" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="C41" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="D41" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F41">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G41">
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J41" t="s">
-        <v>1107</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="B42" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="C42" t="s">
-        <v>1269</v>
+        <v>1263</v>
       </c>
       <c r="D42" t="s">
-        <v>1058</v>
+        <v>1043</v>
       </c>
       <c r="F42">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G42">
         <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="B43" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
       <c r="C43" t="s">
-        <v>1270</v>
+        <v>1264</v>
       </c>
       <c r="D43" t="s">
-        <v>1058</v>
+        <v>1043</v>
       </c>
       <c r="F43">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G43">
         <v>1</v>
       </c>
       <c r="H43" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="B44" t="s">
-        <v>1110</v>
+        <v>1103</v>
       </c>
       <c r="C44" t="s">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="D44" t="s">
-        <v>1058</v>
+        <v>1043</v>
       </c>
       <c r="F44">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
       <c r="H44" t="s">
-        <v>1008</v>
+        <v>1005</v>
+      </c>
+      <c r="J44" t="s">
+        <v>1104</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="B45" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
       <c r="C45" t="s">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="D45" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F45">
         <v>24</v>
@@ -18005,21 +18000,21 @@
         <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="B46" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="C46" t="s">
-        <v>1273</v>
+        <v>1267</v>
       </c>
       <c r="D46" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F46">
         <v>24</v>
@@ -18028,21 +18023,21 @@
         <v>1</v>
       </c>
       <c r="H46" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="B47" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="C47" t="s">
-        <v>1274</v>
+        <v>1268</v>
       </c>
       <c r="D47" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F47">
         <v>24</v>
@@ -18051,102 +18046,93 @@
         <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="B48" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="C48" t="s">
-        <v>1275</v>
+        <v>1269</v>
       </c>
       <c r="D48" t="s">
-        <v>1098</v>
-      </c>
-      <c r="E48" t="s">
-        <v>1115</v>
+        <v>1055</v>
       </c>
       <c r="F48">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G48">
         <v>1</v>
       </c>
       <c r="H48" t="s">
-        <v>1008</v>
-      </c>
-      <c r="J48" t="s">
-        <v>1116</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="B49" t="s">
-        <v>1117</v>
+        <v>1109</v>
       </c>
       <c r="C49" t="s">
-        <v>1276</v>
+        <v>1270</v>
       </c>
       <c r="D49" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F49">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G49">
         <v>1</v>
       </c>
       <c r="H49" t="s">
-        <v>1008</v>
-      </c>
-      <c r="J49" t="s">
-        <v>1118</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="B50" t="s">
-        <v>1119</v>
+        <v>1110</v>
       </c>
       <c r="C50" t="s">
-        <v>1120</v>
+        <v>1271</v>
       </c>
       <c r="D50" t="s">
-        <v>1046</v>
+        <v>1055</v>
       </c>
       <c r="F50">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G50">
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>1008</v>
-      </c>
-      <c r="J50" t="s">
-        <v>1120</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="B51" t="s">
-        <v>1121</v>
+        <v>1111</v>
       </c>
       <c r="C51" t="s">
-        <v>1122</v>
+        <v>1272</v>
       </c>
       <c r="D51" t="s">
-        <v>1058</v>
+        <v>1095</v>
+      </c>
+      <c r="E51" t="s">
+        <v>1112</v>
       </c>
       <c r="F51">
         <v>12</v>
@@ -18155,272 +18141,272 @@
         <v>1</v>
       </c>
       <c r="H51" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J51" t="s">
-        <v>1122</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="B52" t="s">
-        <v>1123</v>
+        <v>1114</v>
       </c>
       <c r="C52" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="D52" t="s">
-        <v>1098</v>
-      </c>
-      <c r="E52" t="s">
-        <v>1124</v>
+        <v>1055</v>
       </c>
       <c r="F52">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G52">
         <v>1</v>
       </c>
       <c r="H52" t="s">
-        <v>1008</v>
-      </c>
-      <c r="I52" t="s">
-        <v>1125</v>
+        <v>1005</v>
       </c>
       <c r="J52" t="s">
-        <v>1126</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="B53" t="s">
-        <v>1127</v>
+        <v>1116</v>
       </c>
       <c r="C53" t="s">
-        <v>1278</v>
+        <v>1117</v>
       </c>
       <c r="D53" t="s">
-        <v>1058</v>
+        <v>1043</v>
+      </c>
+      <c r="F53">
+        <v>12</v>
       </c>
       <c r="G53">
         <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J53" t="s">
-        <v>1128</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="B54" t="s">
-        <v>1129</v>
+        <v>1118</v>
       </c>
       <c r="C54" t="s">
-        <v>1279</v>
+        <v>1119</v>
       </c>
       <c r="D54" t="s">
-        <v>1058</v>
+        <v>1055</v>
+      </c>
+      <c r="F54">
+        <v>12</v>
       </c>
       <c r="G54">
         <v>1</v>
       </c>
       <c r="H54" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J54" t="s">
-        <v>1130</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="B55" t="s">
-        <v>1131</v>
+        <v>1120</v>
       </c>
       <c r="C55" t="s">
-        <v>1280</v>
+        <v>1274</v>
       </c>
       <c r="D55" t="s">
-        <v>1058</v>
+        <v>1095</v>
+      </c>
+      <c r="E55" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F55">
+        <v>6</v>
       </c>
       <c r="G55">
         <v>1</v>
       </c>
       <c r="H55" t="s">
-        <v>1008</v>
+        <v>1005</v>
+      </c>
+      <c r="I55" t="s">
+        <v>1122</v>
       </c>
       <c r="J55" t="s">
-        <v>1132</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="B56" t="s">
-        <v>1133</v>
+        <v>1124</v>
       </c>
       <c r="C56" t="s">
-        <v>1281</v>
+        <v>1275</v>
       </c>
       <c r="D56" t="s">
-        <v>1046</v>
+        <v>1055</v>
       </c>
       <c r="G56">
         <v>1</v>
       </c>
       <c r="H56" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J56" t="s">
-        <v>1134</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="B57" t="s">
-        <v>1135</v>
+        <v>1126</v>
       </c>
       <c r="C57" t="s">
-        <v>1282</v>
+        <v>1276</v>
       </c>
       <c r="D57" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="G57">
         <v>1</v>
       </c>
       <c r="H57" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J57" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="B58" t="s">
-        <v>1137</v>
+        <v>1128</v>
       </c>
       <c r="C58" t="s">
-        <v>1283</v>
+        <v>1277</v>
       </c>
       <c r="D58" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="G58">
         <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J58" t="s">
-        <v>1138</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="B59" t="s">
-        <v>1139</v>
+        <v>1130</v>
       </c>
       <c r="C59" t="s">
-        <v>1284</v>
+        <v>1278</v>
       </c>
       <c r="D59" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F59">
-        <v>12</v>
+        <v>1043</v>
       </c>
       <c r="G59">
         <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J59" t="s">
-        <v>1223</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>1295</v>
+        <v>1034</v>
       </c>
       <c r="B60" t="s">
-        <v>1078</v>
+        <v>1132</v>
       </c>
       <c r="C60" t="s">
-        <v>1251</v>
+        <v>1279</v>
       </c>
       <c r="D60" t="s">
-        <v>1046</v>
-      </c>
-      <c r="F60">
-        <v>12</v>
+        <v>1055</v>
       </c>
       <c r="G60">
         <v>1</v>
       </c>
       <c r="H60" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="J60" t="s">
-        <v>1079</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>1295</v>
+        <v>1034</v>
       </c>
       <c r="B61" t="s">
-        <v>1080</v>
+        <v>1134</v>
       </c>
       <c r="C61" t="s">
-        <v>1252</v>
+        <v>1280</v>
       </c>
       <c r="D61" t="s">
-        <v>1046</v>
-      </c>
-      <c r="F61">
-        <v>12</v>
+        <v>1055</v>
       </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="H61" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="J61" t="s">
-        <v>1081</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>1295</v>
+        <v>1035</v>
       </c>
       <c r="B62" t="s">
-        <v>1082</v>
+        <v>1136</v>
       </c>
       <c r="C62" t="s">
-        <v>1253</v>
+        <v>1281</v>
       </c>
       <c r="D62" t="s">
-        <v>1046</v>
+        <v>1219</v>
       </c>
       <c r="F62">
         <v>12</v>
@@ -18429,10 +18415,10 @@
         <v>1</v>
       </c>
       <c r="H62" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="J62" t="s">
-        <v>1083</v>
+        <v>1220</v>
       </c>
     </row>
   </sheetData>
@@ -18466,16 +18452,16 @@
         <v>18</v>
       </c>
       <c r="C1" s="10" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>1140</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>1141</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -18486,13 +18472,13 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="E2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F2" t="s">
         <v>1142</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -18503,16 +18489,16 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="D3" t="s">
         <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F3" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -18523,16 +18509,16 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="D4" t="s">
         <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F4" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -18543,16 +18529,16 @@
         <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F5" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -18563,16 +18549,16 @@
         <v>33</v>
       </c>
       <c r="C6" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D6" t="s">
         <v>1148</v>
       </c>
-      <c r="D6" t="s">
-        <v>1151</v>
-      </c>
       <c r="E6" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F6" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -18583,16 +18569,16 @@
         <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="D7" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="E7" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F7" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -18603,16 +18589,16 @@
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="D8" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="E8" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F8" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -18623,16 +18609,16 @@
         <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="D9" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="E9" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F9" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -18643,13 +18629,13 @@
         <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="E10" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F10" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -18660,16 +18646,16 @@
         <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="D11" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="E11" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F11" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -18680,16 +18666,16 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="D12" t="s">
         <v>52</v>
       </c>
       <c r="E12" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F12" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -18697,19 +18683,19 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="C13" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="D13" t="s">
-        <v>1296</v>
+        <v>1285</v>
       </c>
       <c r="E13" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F13" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -18720,13 +18706,13 @@
         <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="E14" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F14" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -18737,13 +18723,13 @@
         <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="E15" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F15" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -18754,13 +18740,13 @@
         <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="E16" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F16" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -18771,13 +18757,13 @@
         <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="E17" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F17" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -18788,16 +18774,16 @@
         <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="D18" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="E18" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F18" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -18808,16 +18794,16 @@
         <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="D19" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="E19" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F19" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -18828,446 +18814,446 @@
         <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="E20" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F20" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B21" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="C21" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="D21" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="E21" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F21" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B22" t="s">
         <v>725</v>
       </c>
       <c r="C22" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="E22" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F22" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B23" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="C23" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="D23" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="E23" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F23" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B24" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="C24" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="D24" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="E24" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F24" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B25" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="C25" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="D25" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="E25" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F25" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B26" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="C26" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="D26" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F26" t="s">
         <v>1180</v>
-      </c>
-      <c r="E26" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F26" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B27" t="s">
         <v>727</v>
       </c>
       <c r="C27" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="E27" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F27" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B28" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="C28" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="D28" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="E28" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F28" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B29" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="C29" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="D29" t="s">
-        <v>1297</v>
+        <v>1286</v>
       </c>
       <c r="E29" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F29" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B30" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="C30" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="E30" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F30" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B31" t="s">
         <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="E31" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F31" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B32" t="s">
         <v>728</v>
       </c>
       <c r="C32" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="D32" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="E32" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F32" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B33" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="C33" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="E33" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F33" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="B34" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="C34" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="D34" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="E34" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F34" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="B35" t="s">
         <v>726</v>
       </c>
       <c r="C35" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="D35" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="E35" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F35" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="B36" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="C36" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="E36" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F36" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="B37" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="D37" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="E37" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F37" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="B38" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="D38" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="E38" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F38" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="B39" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="E39" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F39" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="B40" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="E40" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F40" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="B41" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="D41" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="E41" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F41" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="B42" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="D42" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="E42" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F42" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="B43" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="C43" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="E43" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F43" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -19278,13 +19264,13 @@
         <v>78</v>
       </c>
       <c r="C44" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="D44" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="E44" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F44" t="s">
         <v>79</v>

--- a/outputs/mai-report-policy/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456F2916-CAF1-4D22-B466-C8D2708E71A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D8AB4B-04A0-4227-AFA4-A191D748CED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38370" yWindow="-4030" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3959" uniqueCount="1301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4034" uniqueCount="1320">
   <si>
     <t>maiReport 식이 참조·설정 데이터 v1.0.0 | 2026-09-22</t>
   </si>
@@ -2992,10 +2992,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>운영 문구 171개. 불필요한 보류 62개 삭제. 실서비스 노출은 설정값의 「전문의 출시 승인」 스위치 한 곳으로만 연다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>문구 상태와 출시 승인은 별개</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -3678,10 +3674,6 @@
     <t>행마다 다름</t>
   </si>
   <si>
-    <t>171개 운영 문구 · 문구 ID · 성격</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>8축 · 회전 문항 · 답 3개 · 질문 ID</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -3992,6 +3984,71 @@
   </si>
   <si>
     <t>12:00:00</t>
+  </si>
+  <si>
+    <t>하루 마신 음료 적어 보기</t>
+  </si>
+  <si>
+    <t>오늘 무엇을 얼마나 마셨는지 적어 두면 다음에 고를 때 눈에 들어와요.</t>
+  </si>
+  <si>
+    <t>WHO 당류 지침 · 식생활지침 수칙 2</t>
+  </si>
+  <si>
+    <t>신규 추가</t>
+  </si>
+  <si>
+    <t>감량·공복·증량 금지가 걸린 사용자에게 도전 단계 후보가 0이 되던 칸을 채우려고 추가. 성격은 비워 둔다</t>
+  </si>
+  <si>
+    <t>DIET-P-0234</t>
+  </si>
+  <si>
+    <t>음료는 당류 표시 보고 고르기</t>
+  </si>
+  <si>
+    <t>같은 종류라도 제품마다 당이 크게 달라요.</t>
+  </si>
+  <si>
+    <t>DIET-P-0235</t>
+  </si>
+  <si>
+    <t>단 음료 대신 마실 것 정해 두기</t>
+  </si>
+  <si>
+    <t>미리 정해 두면 고르는 순간에 헤매지 않아요.</t>
+  </si>
+  <si>
+    <t>DIET-P-0236</t>
+  </si>
+  <si>
+    <t>한 입마다 수저 내려놓기</t>
+  </si>
+  <si>
+    <t>입문 단계의 한 번을 매 입으로 늘린 것이에요.</t>
+  </si>
+  <si>
+    <t>식생활지침 수칙 4 · 식사 속도 메타분석(2014, 22건)</t>
+  </si>
+  <si>
+    <t>DIET-P-0237</t>
+  </si>
+  <si>
+    <t>세 끼 모두 서두르지 않고 먹기</t>
+  </si>
+  <si>
+    <t>한 끼에서 세 끼로 넓히는 단계예요.</t>
+  </si>
+  <si>
+    <t>DIET-P-0238</t>
+  </si>
+  <si>
+    <t>운영 문구 176개. 불필요한 보류 62개 삭제. 실서비스 노출은 설정값의 「전문의 출시 승인」 스위치 한 곳으로만 연다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>176개 운영 문구 · 문구 ID · 성격</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4465,7 +4522,7 @@
     </row>
     <row r="2" spans="1:3" ht="25.4" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>978</v>
+        <v>1318</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -4491,10 +4548,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1205</v>
+        <v>1319</v>
       </c>
       <c r="C5" s="1">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="25.4" customHeight="1">
@@ -4502,7 +4559,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="C6" s="1">
         <v>8</v>
@@ -4510,10 +4567,10 @@
     </row>
     <row r="7" spans="1:3" ht="25.4" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C7" s="1">
         <v>14</v>
@@ -4521,10 +4578,10 @@
     </row>
     <row r="8" spans="1:3" ht="25.4" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C8" s="1">
         <v>61</v>
@@ -4543,10 +4600,10 @@
     </row>
     <row r="10" spans="1:3" ht="25.4" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C10" s="11">
         <v>42</v>
@@ -4555,11 +4612,13 @@
     <row r="11" spans="1:3" ht="25.4" customHeight="1">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
+      <c r="C11" s="4">
+        <v>176</v>
+      </c>
     </row>
     <row r="12" spans="1:3" ht="25.4" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -4569,7 +4628,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C13" s="1">
         <v>171</v>
@@ -4957,7 +5016,7 @@
         <v>86</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C53" s="4"/>
     </row>
@@ -4969,7 +5028,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S172"/>
+  <dimension ref="A1:S177"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="5.58203125" customWidth="1"/>
@@ -5021,7 +5080,7 @@
         <v>50</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="M1" s="6" t="s">
         <v>53</v>
@@ -5079,7 +5138,7 @@
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>98</v>
@@ -5137,7 +5196,7 @@
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>98</v>
@@ -5193,7 +5252,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>98</v>
@@ -5303,7 +5362,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>118</v>
@@ -5359,7 +5418,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>118</v>
@@ -5525,7 +5584,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>133</v>
@@ -5581,7 +5640,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>138</v>
@@ -5639,7 +5698,7 @@
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>143</v>
@@ -5695,7 +5754,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>138</v>
@@ -5751,7 +5810,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>138</v>
@@ -6077,7 +6136,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>166</v>
@@ -6133,7 +6192,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>118</v>
@@ -6189,7 +6248,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>118</v>
@@ -6245,7 +6304,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>118</v>
@@ -6301,7 +6360,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>98</v>
@@ -6357,7 +6416,7 @@
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>118</v>
@@ -6469,7 +6528,7 @@
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>98</v>
@@ -6525,7 +6584,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>98</v>
@@ -6583,7 +6642,7 @@
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>98</v>
@@ -6807,7 +6866,7 @@
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>221</v>
@@ -6921,7 +6980,7 @@
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>98</v>
@@ -6979,7 +7038,7 @@
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>98</v>
@@ -7093,7 +7152,7 @@
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>118</v>
@@ -7151,7 +7210,7 @@
       </c>
       <c r="K39" s="1"/>
       <c r="L39" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>118</v>
@@ -7209,7 +7268,7 @@
       </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>118</v>
@@ -7379,7 +7438,7 @@
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>138</v>
@@ -7493,7 +7552,7 @@
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>143</v>
@@ -7551,7 +7610,7 @@
       </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>138</v>
@@ -7665,7 +7724,7 @@
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>143</v>
@@ -7723,7 +7782,7 @@
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>143</v>
@@ -7837,7 +7896,7 @@
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>138</v>
@@ -7951,7 +8010,7 @@
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>118</v>
@@ -8009,7 +8068,7 @@
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>221</v>
@@ -8123,7 +8182,7 @@
       </c>
       <c r="K56" s="1"/>
       <c r="L56" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>118</v>
@@ -8237,7 +8296,7 @@
       </c>
       <c r="K58" s="1"/>
       <c r="L58" s="1" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="M58" s="1" t="s">
         <v>143</v>
@@ -8295,7 +8354,7 @@
       </c>
       <c r="K59" s="1"/>
       <c r="L59" s="1" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="M59" s="1" t="s">
         <v>143</v>
@@ -8353,7 +8412,7 @@
       </c>
       <c r="K60" s="1"/>
       <c r="L60" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M60" s="1" t="s">
         <v>143</v>
@@ -8467,7 +8526,7 @@
       </c>
       <c r="K62" s="1"/>
       <c r="L62" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M62" s="1" t="s">
         <v>98</v>
@@ -8525,7 +8584,7 @@
       </c>
       <c r="K63" s="1"/>
       <c r="L63" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M63" s="1" t="s">
         <v>221</v>
@@ -8583,7 +8642,7 @@
       </c>
       <c r="K64" s="1"/>
       <c r="L64" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="M64" s="1" t="s">
         <v>138</v>
@@ -8641,7 +8700,7 @@
       </c>
       <c r="K65" s="1"/>
       <c r="L65" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M65" s="1" t="s">
         <v>98</v>
@@ -8699,7 +8758,7 @@
       </c>
       <c r="K66" s="1"/>
       <c r="L66" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M66" s="1" t="s">
         <v>98</v>
@@ -8757,7 +8816,7 @@
       </c>
       <c r="K67" s="1"/>
       <c r="L67" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M67" s="1" t="s">
         <v>98</v>
@@ -8871,7 +8930,7 @@
       </c>
       <c r="K69" s="1"/>
       <c r="L69" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M69" s="1" t="s">
         <v>98</v>
@@ -8929,7 +8988,7 @@
       </c>
       <c r="K70" s="1"/>
       <c r="L70" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M70" s="1" t="s">
         <v>118</v>
@@ -9043,7 +9102,7 @@
       </c>
       <c r="K72" s="1"/>
       <c r="L72" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M72" s="1" t="s">
         <v>118</v>
@@ -9101,7 +9160,7 @@
       </c>
       <c r="K73" s="1"/>
       <c r="L73" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M73" s="1" t="s">
         <v>194</v>
@@ -9215,7 +9274,7 @@
       </c>
       <c r="K75" s="1"/>
       <c r="L75" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>133</v>
@@ -9273,7 +9332,7 @@
       </c>
       <c r="K76" s="1"/>
       <c r="L76" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>133</v>
@@ -9331,7 +9390,7 @@
       </c>
       <c r="K77" s="1"/>
       <c r="L77" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M77" s="1" t="s">
         <v>98</v>
@@ -9389,7 +9448,7 @@
       </c>
       <c r="K78" s="1"/>
       <c r="L78" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M78" s="1" t="s">
         <v>143</v>
@@ -9447,7 +9506,7 @@
       </c>
       <c r="K79" s="1"/>
       <c r="L79" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M79" s="1" t="s">
         <v>98</v>
@@ -9505,7 +9564,7 @@
       </c>
       <c r="K80" s="1"/>
       <c r="L80" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M80" s="1" t="s">
         <v>98</v>
@@ -9563,7 +9622,7 @@
       </c>
       <c r="K81" s="1"/>
       <c r="L81" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M81" s="1" t="s">
         <v>98</v>
@@ -9677,7 +9736,7 @@
       </c>
       <c r="K83" s="1"/>
       <c r="L83" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M83" s="1" t="s">
         <v>143</v>
@@ -9735,7 +9794,7 @@
       </c>
       <c r="K84" s="1"/>
       <c r="L84" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M84" s="1" t="s">
         <v>143</v>
@@ -9849,7 +9908,7 @@
       </c>
       <c r="K86" s="1"/>
       <c r="L86" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M86" s="1" t="s">
         <v>391</v>
@@ -9907,7 +9966,7 @@
       </c>
       <c r="K87" s="1"/>
       <c r="L87" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M87" s="1" t="s">
         <v>396</v>
@@ -9965,7 +10024,7 @@
       </c>
       <c r="K88" s="1"/>
       <c r="L88" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M88" s="1" t="s">
         <v>396</v>
@@ -10023,7 +10082,7 @@
       </c>
       <c r="K89" s="1"/>
       <c r="L89" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M89" s="1" t="s">
         <v>166</v>
@@ -10081,7 +10140,7 @@
       </c>
       <c r="K90" s="1"/>
       <c r="L90" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M90" s="1" t="s">
         <v>166</v>
@@ -10139,7 +10198,7 @@
       </c>
       <c r="K91" s="1"/>
       <c r="L91" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M91" s="1" t="s">
         <v>118</v>
@@ -10197,7 +10256,7 @@
       </c>
       <c r="K92" s="1"/>
       <c r="L92" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M92" s="1" t="s">
         <v>118</v>
@@ -10255,7 +10314,7 @@
       </c>
       <c r="K93" s="1"/>
       <c r="L93" s="1" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="M93" s="1" t="s">
         <v>118</v>
@@ -10313,7 +10372,7 @@
       </c>
       <c r="K94" s="1"/>
       <c r="L94" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M94" s="1" t="s">
         <v>118</v>
@@ -10651,7 +10710,7 @@
       </c>
       <c r="K100" s="1"/>
       <c r="L100" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M100" s="1" t="s">
         <v>98</v>
@@ -10709,7 +10768,7 @@
       </c>
       <c r="K101" s="1"/>
       <c r="L101" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M101" s="1" t="s">
         <v>98</v>
@@ -10879,7 +10938,7 @@
       </c>
       <c r="K104" s="1"/>
       <c r="L104" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M104" s="1" t="s">
         <v>118</v>
@@ -10993,7 +11052,7 @@
       </c>
       <c r="K106" s="1"/>
       <c r="L106" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M106" s="1" t="s">
         <v>118</v>
@@ -11051,7 +11110,7 @@
       </c>
       <c r="K107" s="1"/>
       <c r="L107" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M107" s="1" t="s">
         <v>118</v>
@@ -11165,7 +11224,7 @@
       </c>
       <c r="K109" s="1"/>
       <c r="L109" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="M109" s="1" t="s">
         <v>133</v>
@@ -11223,7 +11282,7 @@
       </c>
       <c r="K110" s="1"/>
       <c r="L110" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M110" s="1" t="s">
         <v>98</v>
@@ -11337,7 +11396,7 @@
       </c>
       <c r="K112" s="1"/>
       <c r="L112" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="M112" s="1" t="s">
         <v>133</v>
@@ -11395,7 +11454,7 @@
       </c>
       <c r="K113" s="1"/>
       <c r="L113" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>138</v>
@@ -11453,7 +11512,7 @@
       </c>
       <c r="K114" s="1"/>
       <c r="L114" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M114" s="1" t="s">
         <v>143</v>
@@ -11623,7 +11682,7 @@
       </c>
       <c r="K117" s="1"/>
       <c r="L117" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>98</v>
@@ -11737,7 +11796,7 @@
       </c>
       <c r="K119" s="1"/>
       <c r="L119" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M119" s="1" t="s">
         <v>143</v>
@@ -11795,7 +11854,7 @@
       </c>
       <c r="K120" s="1"/>
       <c r="L120" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M120" s="1" t="s">
         <v>138</v>
@@ -11853,7 +11912,7 @@
       </c>
       <c r="K121" s="1"/>
       <c r="L121" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M121" s="1" t="s">
         <v>396</v>
@@ -12079,7 +12138,7 @@
       </c>
       <c r="K125" s="1"/>
       <c r="L125" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M125" s="1" t="s">
         <v>396</v>
@@ -12137,7 +12196,7 @@
       </c>
       <c r="K126" s="1"/>
       <c r="L126" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M126" s="1" t="s">
         <v>166</v>
@@ -12195,7 +12254,7 @@
       </c>
       <c r="K127" s="1"/>
       <c r="L127" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M127" s="1" t="s">
         <v>118</v>
@@ -12253,7 +12312,7 @@
       </c>
       <c r="K128" s="1"/>
       <c r="L128" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M128" s="1" t="s">
         <v>118</v>
@@ -12367,7 +12426,7 @@
       </c>
       <c r="K130" s="1"/>
       <c r="L130" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M130" s="1" t="s">
         <v>118</v>
@@ -12425,7 +12484,7 @@
       </c>
       <c r="K131" s="1"/>
       <c r="L131" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M131" s="1" t="s">
         <v>118</v>
@@ -12483,7 +12542,7 @@
       </c>
       <c r="K132" s="1"/>
       <c r="L132" s="1" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="M132" s="1" t="s">
         <v>194</v>
@@ -12541,7 +12600,7 @@
       </c>
       <c r="K133" s="1"/>
       <c r="L133" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M133" s="1" t="s">
         <v>98</v>
@@ -12655,7 +12714,7 @@
       </c>
       <c r="K135" s="1"/>
       <c r="L135" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M135" s="1" t="s">
         <v>98</v>
@@ -12713,7 +12772,7 @@
       </c>
       <c r="K136" s="1"/>
       <c r="L136" s="1" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="M136" s="1" t="s">
         <v>98</v>
@@ -12771,7 +12830,7 @@
       </c>
       <c r="K137" s="1"/>
       <c r="L137" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M137" s="1" t="s">
         <v>98</v>
@@ -12829,7 +12888,7 @@
       </c>
       <c r="K138" s="1"/>
       <c r="L138" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M138" s="1" t="s">
         <v>98</v>
@@ -12887,7 +12946,7 @@
       </c>
       <c r="K139" s="1"/>
       <c r="L139" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M139" s="1" t="s">
         <v>118</v>
@@ -12945,7 +13004,7 @@
       </c>
       <c r="K140" s="1"/>
       <c r="L140" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M140" s="1" t="s">
         <v>138</v>
@@ -13003,7 +13062,7 @@
       </c>
       <c r="K141" s="1"/>
       <c r="L141" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M141" s="1" t="s">
         <v>166</v>
@@ -13117,7 +13176,7 @@
       </c>
       <c r="K143" s="1"/>
       <c r="L143" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M143" s="1" t="s">
         <v>118</v>
@@ -13175,7 +13234,7 @@
       </c>
       <c r="K144" s="1"/>
       <c r="L144" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M144" s="1" t="s">
         <v>118</v>
@@ -13233,7 +13292,7 @@
       </c>
       <c r="K145" s="1"/>
       <c r="L145" s="1" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="M145" s="1" t="s">
         <v>98</v>
@@ -13347,7 +13406,7 @@
       </c>
       <c r="K147" s="1"/>
       <c r="L147" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M147" s="1" t="s">
         <v>396</v>
@@ -13405,7 +13464,7 @@
       </c>
       <c r="K148" s="1"/>
       <c r="L148" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M148" s="1" t="s">
         <v>118</v>
@@ -13463,7 +13522,7 @@
       </c>
       <c r="K149" s="1"/>
       <c r="L149" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M149" s="1" t="s">
         <v>118</v>
@@ -13521,7 +13580,7 @@
       </c>
       <c r="K150" s="1"/>
       <c r="L150" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M150" s="1" t="s">
         <v>118</v>
@@ -13579,7 +13638,7 @@
       </c>
       <c r="K151" s="1"/>
       <c r="L151" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M151" s="1" t="s">
         <v>118</v>
@@ -13637,7 +13696,7 @@
       </c>
       <c r="K152" s="1"/>
       <c r="L152" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M152" s="1" t="s">
         <v>138</v>
@@ -13695,7 +13754,7 @@
       </c>
       <c r="K153" s="1"/>
       <c r="L153" s="1" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="M153" s="1" t="s">
         <v>98</v>
@@ -13753,7 +13812,7 @@
       </c>
       <c r="K154" s="1"/>
       <c r="L154" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M154" s="1" t="s">
         <v>118</v>
@@ -13811,7 +13870,7 @@
       </c>
       <c r="K155" s="1"/>
       <c r="L155" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M155" s="1" t="s">
         <v>143</v>
@@ -13925,7 +13984,7 @@
       </c>
       <c r="K157" s="1"/>
       <c r="L157" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M157" s="1" t="s">
         <v>138</v>
@@ -14039,7 +14098,7 @@
       </c>
       <c r="K159" s="1"/>
       <c r="L159" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="M159" s="1" t="s">
         <v>133</v>
@@ -14153,7 +14212,7 @@
       </c>
       <c r="K161" s="1"/>
       <c r="L161" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="M161" s="1" t="s">
         <v>133</v>
@@ -14211,7 +14270,7 @@
       </c>
       <c r="K162" s="1"/>
       <c r="L162" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="M162" s="1" t="s">
         <v>143</v>
@@ -14768,6 +14827,271 @@
         <v>103</v>
       </c>
       <c r="S172" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173" t="s">
+        <v>26</v>
+      </c>
+      <c r="C173" t="s">
+        <v>9</v>
+      </c>
+      <c r="D173" t="s">
+        <v>92</v>
+      </c>
+      <c r="E173" t="s">
+        <v>130</v>
+      </c>
+      <c r="F173" t="s">
+        <v>111</v>
+      </c>
+      <c r="G173" t="s">
+        <v>1299</v>
+      </c>
+      <c r="H173">
+        <v>14</v>
+      </c>
+      <c r="I173" t="s">
+        <v>1300</v>
+      </c>
+      <c r="J173" t="s">
+        <v>198</v>
+      </c>
+      <c r="M173" t="s">
+        <v>1301</v>
+      </c>
+      <c r="N173" t="s">
+        <v>99</v>
+      </c>
+      <c r="O173" t="s">
+        <v>1302</v>
+      </c>
+      <c r="P173" t="s">
+        <v>1303</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>1304</v>
+      </c>
+      <c r="R173" t="s">
+        <v>103</v>
+      </c>
+      <c r="S173" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="174" spans="1:19">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174" t="s">
+        <v>26</v>
+      </c>
+      <c r="C174" t="s">
+        <v>9</v>
+      </c>
+      <c r="D174" t="s">
+        <v>92</v>
+      </c>
+      <c r="E174" t="s">
+        <v>130</v>
+      </c>
+      <c r="F174" t="s">
+        <v>111</v>
+      </c>
+      <c r="G174" t="s">
+        <v>1305</v>
+      </c>
+      <c r="H174">
+        <v>16</v>
+      </c>
+      <c r="I174" t="s">
+        <v>1306</v>
+      </c>
+      <c r="J174" t="s">
+        <v>198</v>
+      </c>
+      <c r="M174" t="s">
+        <v>1301</v>
+      </c>
+      <c r="N174" t="s">
+        <v>99</v>
+      </c>
+      <c r="O174" t="s">
+        <v>1302</v>
+      </c>
+      <c r="P174" t="s">
+        <v>1303</v>
+      </c>
+      <c r="Q174" t="s">
+        <v>1307</v>
+      </c>
+      <c r="R174" t="s">
+        <v>103</v>
+      </c>
+      <c r="S174" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="175" spans="1:19">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175" t="s">
+        <v>26</v>
+      </c>
+      <c r="C175" t="s">
+        <v>9</v>
+      </c>
+      <c r="D175" t="s">
+        <v>92</v>
+      </c>
+      <c r="E175" t="s">
+        <v>130</v>
+      </c>
+      <c r="F175" t="s">
+        <v>111</v>
+      </c>
+      <c r="G175" t="s">
+        <v>1308</v>
+      </c>
+      <c r="H175">
+        <v>18</v>
+      </c>
+      <c r="I175" t="s">
+        <v>1309</v>
+      </c>
+      <c r="J175" t="s">
+        <v>198</v>
+      </c>
+      <c r="M175" t="s">
+        <v>1301</v>
+      </c>
+      <c r="N175" t="s">
+        <v>99</v>
+      </c>
+      <c r="O175" t="s">
+        <v>1302</v>
+      </c>
+      <c r="P175" t="s">
+        <v>1303</v>
+      </c>
+      <c r="Q175" t="s">
+        <v>1310</v>
+      </c>
+      <c r="R175" t="s">
+        <v>103</v>
+      </c>
+      <c r="S175" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="176" spans="1:19">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176" t="s">
+        <v>26</v>
+      </c>
+      <c r="C176" t="s">
+        <v>9</v>
+      </c>
+      <c r="D176" t="s">
+        <v>92</v>
+      </c>
+      <c r="E176" t="s">
+        <v>163</v>
+      </c>
+      <c r="F176" t="s">
+        <v>111</v>
+      </c>
+      <c r="G176" t="s">
+        <v>1311</v>
+      </c>
+      <c r="H176">
+        <v>13</v>
+      </c>
+      <c r="I176" t="s">
+        <v>1312</v>
+      </c>
+      <c r="J176" t="s">
+        <v>198</v>
+      </c>
+      <c r="M176" t="s">
+        <v>1313</v>
+      </c>
+      <c r="N176" t="s">
+        <v>99</v>
+      </c>
+      <c r="O176" t="s">
+        <v>1302</v>
+      </c>
+      <c r="P176" t="s">
+        <v>1303</v>
+      </c>
+      <c r="Q176" t="s">
+        <v>1314</v>
+      </c>
+      <c r="R176" t="s">
+        <v>103</v>
+      </c>
+      <c r="S176" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="177" spans="1:19">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177" t="s">
+        <v>26</v>
+      </c>
+      <c r="C177" t="s">
+        <v>9</v>
+      </c>
+      <c r="D177" t="s">
+        <v>92</v>
+      </c>
+      <c r="E177" t="s">
+        <v>163</v>
+      </c>
+      <c r="F177" t="s">
+        <v>111</v>
+      </c>
+      <c r="G177" t="s">
+        <v>1315</v>
+      </c>
+      <c r="H177">
+        <v>17</v>
+      </c>
+      <c r="I177" t="s">
+        <v>1316</v>
+      </c>
+      <c r="J177" t="s">
+        <v>198</v>
+      </c>
+      <c r="M177" t="s">
+        <v>1313</v>
+      </c>
+      <c r="N177" t="s">
+        <v>99</v>
+      </c>
+      <c r="O177" t="s">
+        <v>1302</v>
+      </c>
+      <c r="P177" t="s">
+        <v>1303</v>
+      </c>
+      <c r="Q177" t="s">
+        <v>1317</v>
+      </c>
+      <c r="R177" t="s">
+        <v>103</v>
+      </c>
+      <c r="S177" t="s">
         <v>98</v>
       </c>
     </row>
@@ -15527,13 +15851,13 @@
         <v>767</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>768</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="66" customHeight="1">
@@ -15565,7 +15889,7 @@
         <v>774</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="66" customHeight="1">
@@ -15599,7 +15923,7 @@
         <v>783</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="66" customHeight="1">
@@ -16141,7 +16465,7 @@
         <v>905</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="66" customHeight="1">
@@ -16285,16 +16609,16 @@
         <v>766</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="C57" s="13" t="s">
         <v>782</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
     </row>
   </sheetData>
@@ -16324,34 +16648,34 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="10" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>725</v>
       </c>
       <c r="C1" s="10" t="s">
+        <v>988</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>989</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>990</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>991</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>992</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>727</v>
       </c>
       <c r="H1" s="10" t="s">
+        <v>992</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>993</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="J1" s="10" t="s">
         <v>994</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>995</v>
       </c>
       <c r="K1" s="10" t="s">
         <v>53</v>
@@ -16360,12 +16684,12 @@
         <v>728</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B2" t="s">
         <v>729</v>
@@ -16374,39 +16698,39 @@
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G2" t="s">
         <v>729</v>
       </c>
       <c r="H2" t="s">
+        <v>998</v>
+      </c>
+      <c r="I2" t="s">
         <v>999</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>1000</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1001</v>
       </c>
       <c r="K2" t="s">
         <v>730</v>
       </c>
       <c r="L2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="M2" t="s">
         <v>1002</v>
-      </c>
-      <c r="M2" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B3" t="s">
         <v>731</v>
@@ -16415,33 +16739,33 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E3" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F3" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G3" t="s">
         <v>731</v>
       </c>
       <c r="H3" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="K3" t="s">
         <v>732</v>
       </c>
       <c r="L3" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="M3" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B4" t="s">
         <v>733</v>
@@ -16450,68 +16774,68 @@
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E4" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F4" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G4" t="s">
         <v>734</v>
       </c>
       <c r="H4" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="K4" t="s">
         <v>735</v>
       </c>
       <c r="L4" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="M4" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B5" t="s">
         <v>1010</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1011</v>
       </c>
       <c r="C5" t="s">
         <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E5" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F5" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G5" t="s">
         <v>734</v>
       </c>
       <c r="H5" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="K5" t="s">
         <v>735</v>
       </c>
       <c r="L5" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="M5" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B6" t="s">
         <v>736</v>
@@ -16520,80 +16844,80 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E6" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F6" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G6" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="H6" t="s">
         <v>695</v>
       </c>
       <c r="I6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="J6" t="s">
         <v>1015</v>
-      </c>
-      <c r="J6" t="s">
-        <v>1016</v>
       </c>
       <c r="K6" t="s">
         <v>737</v>
       </c>
       <c r="L6" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="M6" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B7" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E7" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F7" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G7" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="H7" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="I7" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="J7" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="K7" t="s">
         <v>738</v>
       </c>
       <c r="L7" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="M7" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B8" t="s">
         <v>739</v>
@@ -16602,33 +16926,33 @@
         <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E8" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F8" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G8" t="s">
         <v>739</v>
       </c>
       <c r="H8" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="K8" t="s">
         <v>740</v>
       </c>
       <c r="L8" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="M8" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B9" t="s">
         <v>741</v>
@@ -16637,33 +16961,33 @@
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E9" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F9" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="I9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="J9" t="s">
         <v>1023</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>1024</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
+        <v>1001</v>
+      </c>
+      <c r="M9" t="s">
         <v>1025</v>
-      </c>
-      <c r="L9" t="s">
-        <v>1002</v>
-      </c>
-      <c r="M9" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B10" t="s">
         <v>742</v>
@@ -16672,33 +16996,33 @@
         <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E10" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F10" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="I10" t="s">
+        <v>1022</v>
+      </c>
+      <c r="J10" t="s">
         <v>1023</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>1024</v>
       </c>
-      <c r="K10" t="s">
-        <v>1025</v>
-      </c>
       <c r="L10" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="M10" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B11" t="s">
         <v>743</v>
@@ -16707,33 +17031,33 @@
         <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E11" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F11" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="I11" t="s">
+        <v>1022</v>
+      </c>
+      <c r="J11" t="s">
         <v>1023</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>1024</v>
       </c>
-      <c r="K11" t="s">
-        <v>1025</v>
-      </c>
       <c r="L11" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="M11" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B12" t="s">
         <v>744</v>
@@ -16742,33 +17066,33 @@
         <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E12" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F12" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="I12" t="s">
+        <v>1022</v>
+      </c>
+      <c r="J12" t="s">
         <v>1023</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>1024</v>
       </c>
-      <c r="K12" t="s">
-        <v>1025</v>
-      </c>
       <c r="L12" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="M12" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B13" t="s">
         <v>745</v>
@@ -16777,98 +17101,98 @@
         <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E13" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F13" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="I13" t="s">
+        <v>1022</v>
+      </c>
+      <c r="J13" t="s">
         <v>1023</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>1024</v>
       </c>
-      <c r="K13" t="s">
-        <v>1025</v>
-      </c>
       <c r="L13" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="M13" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B14" t="s">
         <v>746</v>
       </c>
       <c r="C14" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="D14" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E14" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F14" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="I14" t="s">
+        <v>1014</v>
+      </c>
+      <c r="J14" t="s">
         <v>1015</v>
-      </c>
-      <c r="J14" t="s">
-        <v>1016</v>
       </c>
       <c r="K14" t="s">
         <v>737</v>
       </c>
       <c r="L14" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="M14" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B15" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="C15" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="D15" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E15" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F15" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="I15" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="J15" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="K15" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="L15" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="M15" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
   </sheetData>
@@ -16895,48 +17219,48 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="10" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>726</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D1" s="10" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>1036</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>1037</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>1038</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>1039</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>1040</v>
       </c>
-      <c r="I1" s="10" t="s">
-        <v>1041</v>
-      </c>
       <c r="J1" s="10" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D2" t="s">
         <v>1042</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1225</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1043</v>
       </c>
       <c r="F2">
         <v>12</v>
@@ -16945,24 +17269,24 @@
         <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="J2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B3" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C3" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="D3" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F3">
         <v>12</v>
@@ -16971,21 +17295,21 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B4" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C4" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="D4" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F4">
         <v>12</v>
@@ -16994,21 +17318,21 @@
         <v>2</v>
       </c>
       <c r="H4" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C5" t="s">
         <v>1047</v>
       </c>
-      <c r="C5" t="s">
-        <v>1048</v>
-      </c>
       <c r="D5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F5">
         <v>12</v>
@@ -17017,24 +17341,24 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="J5" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B6" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C6" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="D6" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F6">
         <v>12</v>
@@ -17043,21 +17367,21 @@
         <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B7" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C7" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="D7" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -17066,21 +17390,21 @@
         <v>2</v>
       </c>
       <c r="H7" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B8" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C8" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="D8" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F8">
         <v>12</v>
@@ -17089,21 +17413,21 @@
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B9" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D9" t="s">
         <v>1054</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1055</v>
       </c>
       <c r="F9">
         <v>12</v>
@@ -17112,21 +17436,21 @@
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B10" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C10" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="D10" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F10">
         <v>12</v>
@@ -17135,21 +17459,21 @@
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B11" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C11" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="D11" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F11">
         <v>12</v>
@@ -17158,24 +17482,24 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="J11" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B12" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C12" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="D12" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F12">
         <v>12</v>
@@ -17184,24 +17508,24 @@
         <v>2</v>
       </c>
       <c r="H12" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="J12" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B13" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C13" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="D13" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -17210,24 +17534,24 @@
         <v>2</v>
       </c>
       <c r="H13" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="J13" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B14" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C14" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="D14" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F14">
         <v>12</v>
@@ -17236,24 +17560,24 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="J14" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B15" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C15" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="D15" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F15">
         <v>12</v>
@@ -17262,21 +17586,21 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B16" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C16" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="D16" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F16">
         <v>12</v>
@@ -17285,21 +17609,21 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B17" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C17" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="D17" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F17">
         <v>12</v>
@@ -17308,21 +17632,21 @@
         <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B18" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C18" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="D18" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F18">
         <v>12</v>
@@ -17331,21 +17655,21 @@
         <v>2</v>
       </c>
       <c r="H18" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B19" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C19" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="D19" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F19">
         <v>12</v>
@@ -17354,21 +17678,21 @@
         <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B20" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C20" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="D20" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F20">
         <v>12</v>
@@ -17377,21 +17701,21 @@
         <v>2</v>
       </c>
       <c r="H20" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B21" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C21" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="D21" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F21">
         <v>12</v>
@@ -17400,24 +17724,24 @@
         <v>2</v>
       </c>
       <c r="H21" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="J21" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B22" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C22" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="D22" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F22">
         <v>12</v>
@@ -17426,21 +17750,21 @@
         <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B23" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C23" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="D23" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F23">
         <v>12</v>
@@ -17449,24 +17773,24 @@
         <v>2</v>
       </c>
       <c r="H23" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="J23" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B24" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C24" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="D24" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F24">
         <v>12</v>
@@ -17475,24 +17799,24 @@
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="J24" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B25" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C25" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="D25" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F25">
         <v>12</v>
@@ -17501,24 +17825,24 @@
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="J25" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B26" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C26" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="D26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F26">
         <v>12</v>
@@ -17527,24 +17851,24 @@
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="J26" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B27" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C27" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="D27" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F27">
         <v>12</v>
@@ -17553,21 +17877,21 @@
         <v>2</v>
       </c>
       <c r="H27" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B28" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C28" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="D28" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F28">
         <v>12</v>
@@ -17576,21 +17900,21 @@
         <v>2</v>
       </c>
       <c r="H28" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B29" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C29" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D29" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F29">
         <v>12</v>
@@ -17599,21 +17923,21 @@
         <v>2</v>
       </c>
       <c r="H29" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B30" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C30" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="D30" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F30">
         <v>12</v>
@@ -17622,21 +17946,21 @@
         <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B31" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C31" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="D31" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F31">
         <v>12</v>
@@ -17645,24 +17969,24 @@
         <v>2</v>
       </c>
       <c r="H31" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="J31" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B32" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C32" t="s">
         <v>1089</v>
       </c>
-      <c r="C32" t="s">
-        <v>1090</v>
-      </c>
       <c r="D32" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F32">
         <v>12</v>
@@ -17671,24 +17995,24 @@
         <v>2</v>
       </c>
       <c r="H32" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="J32" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="B33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C33" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="D33" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F33">
         <v>12</v>
@@ -17697,24 +18021,24 @@
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="J33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="B34" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C34" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="D34" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F34">
         <v>12</v>
@@ -17723,24 +18047,24 @@
         <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="J34" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="B35" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C35" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="D35" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F35">
         <v>12</v>
@@ -17749,24 +18073,24 @@
         <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="J35" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B36" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C36" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="D36" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F36">
         <v>12</v>
@@ -17775,24 +18099,24 @@
         <v>2</v>
       </c>
       <c r="H36" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="J36" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B37" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C37" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="D37" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F37">
         <v>12</v>
@@ -17801,21 +18125,21 @@
         <v>2</v>
       </c>
       <c r="H37" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B38" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C38" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="D38" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F38">
         <v>12</v>
@@ -17824,24 +18148,24 @@
         <v>2</v>
       </c>
       <c r="H38" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B39" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D39" t="s">
         <v>1094</v>
       </c>
-      <c r="C39" t="s">
-        <v>1260</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>1095</v>
-      </c>
-      <c r="E39" t="s">
-        <v>1096</v>
       </c>
       <c r="F39">
         <v>10</v>
@@ -17850,24 +18174,24 @@
         <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="J39" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B40" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="C40" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="D40" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F40">
         <v>10</v>
@@ -17876,24 +18200,24 @@
         <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="J40" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B41" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="C41" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D41" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F41">
         <v>10</v>
@@ -17902,24 +18226,24 @@
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="J41" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B42" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C42" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="D42" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F42">
         <v>10</v>
@@ -17928,21 +18252,21 @@
         <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B43" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C43" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="D43" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F43">
         <v>10</v>
@@ -17951,21 +18275,21 @@
         <v>1</v>
       </c>
       <c r="H43" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B44" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C44" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="D44" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F44">
         <v>12</v>
@@ -17974,24 +18298,24 @@
         <v>1</v>
       </c>
       <c r="H44" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="J44" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B45" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C45" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="D45" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F45">
         <v>24</v>
@@ -18000,21 +18324,21 @@
         <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B46" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C46" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="D46" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F46">
         <v>24</v>
@@ -18023,21 +18347,21 @@
         <v>1</v>
       </c>
       <c r="H46" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B47" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="C47" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="D47" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F47">
         <v>24</v>
@@ -18046,21 +18370,21 @@
         <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B48" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C48" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="D48" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F48">
         <v>24</v>
@@ -18069,21 +18393,21 @@
         <v>1</v>
       </c>
       <c r="H48" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B49" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C49" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="D49" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F49">
         <v>24</v>
@@ -18092,21 +18416,21 @@
         <v>1</v>
       </c>
       <c r="H49" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B50" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C50" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="D50" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F50">
         <v>24</v>
@@ -18115,24 +18439,24 @@
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B51" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E51" t="s">
         <v>1111</v>
-      </c>
-      <c r="C51" t="s">
-        <v>1272</v>
-      </c>
-      <c r="D51" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E51" t="s">
-        <v>1112</v>
       </c>
       <c r="F51">
         <v>12</v>
@@ -18141,24 +18465,24 @@
         <v>1</v>
       </c>
       <c r="H51" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="J51" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B52" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C52" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="D52" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F52">
         <v>12</v>
@@ -18167,24 +18491,24 @@
         <v>1</v>
       </c>
       <c r="H52" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="J52" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B53" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C53" t="s">
         <v>1116</v>
       </c>
-      <c r="C53" t="s">
-        <v>1117</v>
-      </c>
       <c r="D53" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F53">
         <v>12</v>
@@ -18193,24 +18517,24 @@
         <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="J53" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B54" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C54" t="s">
         <v>1118</v>
       </c>
-      <c r="C54" t="s">
-        <v>1119</v>
-      </c>
       <c r="D54" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F54">
         <v>12</v>
@@ -18219,27 +18543,27 @@
         <v>1</v>
       </c>
       <c r="H54" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="J54" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B55" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E55" t="s">
         <v>1120</v>
-      </c>
-      <c r="C55" t="s">
-        <v>1274</v>
-      </c>
-      <c r="D55" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E55" t="s">
-        <v>1121</v>
       </c>
       <c r="F55">
         <v>6</v>
@@ -18248,165 +18572,165 @@
         <v>1</v>
       </c>
       <c r="H55" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="I55" t="s">
+        <v>1121</v>
+      </c>
+      <c r="J55" t="s">
         <v>1122</v>
-      </c>
-      <c r="J55" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B56" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="C56" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="D56" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="G56">
         <v>1</v>
       </c>
       <c r="H56" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="J56" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B57" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="C57" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="D57" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="G57">
         <v>1</v>
       </c>
       <c r="H57" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="J57" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B58" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="C58" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="D58" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="G58">
         <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="J58" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B59" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="C59" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="D59" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="G59">
         <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="J59" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B60" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C60" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="D60" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="G60">
         <v>1</v>
       </c>
       <c r="H60" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="J60" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B61" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="C61" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="D61" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="H61" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="J61" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B62" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C62" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="D62" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="F62">
         <v>12</v>
@@ -18415,10 +18739,10 @@
         <v>1</v>
       </c>
       <c r="H62" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="J62" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
   </sheetData>
@@ -18452,16 +18776,16 @@
         <v>18</v>
       </c>
       <c r="C1" s="10" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1137</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>1138</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>1139</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -18472,13 +18796,13 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F2" t="s">
         <v>1141</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -18489,16 +18813,16 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D3" t="s">
         <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="F3" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -18509,16 +18833,16 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D4" t="s">
         <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="F4" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -18529,16 +18853,16 @@
         <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="F5" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -18549,16 +18873,16 @@
         <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D6" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F6" t="s">
         <v>1148</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -18569,16 +18893,16 @@
         <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D7" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E7" t="s">
         <v>1150</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>1151</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -18589,16 +18913,16 @@
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D8" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F8" t="s">
         <v>1153</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -18609,16 +18933,16 @@
         <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="D9" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F9" t="s">
         <v>1155</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -18629,13 +18953,13 @@
         <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E10" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="F10" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -18646,16 +18970,16 @@
         <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D11" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F11" t="s">
         <v>1158</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F11" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -18666,16 +18990,16 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D12" t="s">
         <v>52</v>
       </c>
       <c r="E12" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F12" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -18683,19 +19007,19 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C13" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D13" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="E13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F13" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -18706,13 +19030,13 @@
         <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E14" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="F14" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -18723,13 +19047,13 @@
         <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E15" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F15" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -18740,13 +19064,13 @@
         <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E16" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F16" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -18757,13 +19081,13 @@
         <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E17" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F17" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -18774,16 +19098,16 @@
         <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D18" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F18" t="s">
         <v>1166</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F18" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -18794,16 +19118,16 @@
         <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D19" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F19" t="s">
         <v>1168</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F19" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -18814,446 +19138,446 @@
         <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E20" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F20" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B21" t="s">
+        <v>987</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D21" t="s">
         <v>1171</v>
       </c>
-      <c r="B21" t="s">
-        <v>988</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1143</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F21" t="s">
         <v>1172</v>
-      </c>
-      <c r="E21" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F21" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B22" t="s">
         <v>725</v>
       </c>
       <c r="C22" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E22" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="F22" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B23" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="C23" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D23" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F23" t="s">
         <v>1175</v>
-      </c>
-      <c r="E23" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F23" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B24" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C24" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D24" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F24" t="s">
         <v>1177</v>
-      </c>
-      <c r="E24" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F24" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B25" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="C25" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D25" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="E25" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="F25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B26" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="C26" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D26" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="E26" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="F26" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B27" t="s">
         <v>727</v>
       </c>
       <c r="C27" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E27" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F27" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B28" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="C28" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D28" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F28" t="s">
         <v>1182</v>
-      </c>
-      <c r="E28" t="s">
-        <v>1151</v>
-      </c>
-      <c r="F28" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B29" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C29" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="E29" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F29" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B30" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C30" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E30" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F30" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B31" t="s">
         <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E31" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="F31" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B32" t="s">
         <v>728</v>
       </c>
       <c r="C32" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D32" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F32" t="s">
         <v>1187</v>
-      </c>
-      <c r="E32" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F32" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B33" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C33" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E33" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F33" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B34" t="s">
+        <v>987</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F34" t="s">
         <v>1190</v>
-      </c>
-      <c r="B34" t="s">
-        <v>988</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1143</v>
-      </c>
-      <c r="D34" t="s">
-        <v>1172</v>
-      </c>
-      <c r="E34" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F34" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B35" t="s">
         <v>726</v>
       </c>
       <c r="C35" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D35" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F35" t="s">
         <v>1192</v>
-      </c>
-      <c r="E35" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F35" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B36" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="C36" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E36" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="F36" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B37" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="C37" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D37" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F37" t="s">
         <v>1194</v>
-      </c>
-      <c r="E37" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F37" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B38" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C38" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D38" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E38" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F38" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B39" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C39" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E39" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F39" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B40" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C40" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E40" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F40" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B41" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C41" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D41" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="E41" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F41" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B42" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C42" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D42" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E42" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F42" t="s">
         <v>1200</v>
-      </c>
-      <c r="E42" t="s">
-        <v>1151</v>
-      </c>
-      <c r="F42" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B43" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C43" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E43" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F43" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -19264,13 +19588,13 @@
         <v>78</v>
       </c>
       <c r="C44" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D44" t="s">
         <v>1203</v>
       </c>
-      <c r="D44" t="s">
-        <v>1204</v>
-      </c>
       <c r="E44" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="F44" t="s">
         <v>79</v>
